--- a/config/level_config.xlsx
+++ b/config/level_config.xlsx
@@ -219,7 +219,7 @@
     <t>[12]</t>
   </si>
   <si>
-    <t>[[THOSE_WORD_POINTING_379,FABLE_WORD_LEGENDS_291],[MYTH_WORD_LEGENDS_291,UNION_WORD_UNITE_126],[OILY_WORD_SKIN_380],[NORMAL_WORD_SKIN_380],[SUPPORT_WORD_HELP_183],[BURGER_WORD_FOOD_3],[BANANA_PIC_FRUITS_9],[NEW_YEAR_WORD_HOLIDAY_163],[FLAG_DAY_WORD_HOLIDAY_163],[SIGNPOST_WORD_NAVIGATE_230],[FORCE_WORD_STRENGTH_401],[DONATE_WORD_HELP_183],[ASSIST_WORD_HELP_183],[ORANGE_PIC_FRUITS_9],[FALSIFY_WORD_LIE_492],[THAT_WORD_POINTING_379],[APPLE_PIC_FRUITS_9],[EASTER_WORD_HOLIDAY_163],[HOT_DOG_WORD_FOOD_3],[LEAGUE_WORD_UNITE_126],[KIWI_PIC_FRUITS_9],[PIZZA_WORD_FOOD_3],[THIS_WORD_POINTING_379],[TALE_WORD_LEGENDS_291],[FRIES_WORD_FOOD_3]]</t>
+    <t>[[THOSE_WORD_POINTING_379,FABLE_WORD_LEGENDS_291],[MYTH_WORD_LEGENDS_291,KINGDOM_WORD_MEDIEVAL_228],[OILY_WORD_SKIN_380],[NORMAL_WORD_SKIN_380],[SUPPORT_WORD_HELP_183],[BURGER_WORD_FOOD_3],[BANANA_PIC_FRUITS_9],[NEW_YEAR_WORD_HOLIDAY_163],[FLAG_DAY_WORD_HOLIDAY_163],[LORD_WORD_MEDIEVAL_228],[FORCE_WORD_STRENGTH_401],[DONATE_WORD_HELP_183],[ASSIST_WORD_HELP_183],[ORANGE_PIC_FRUITS_9],[FALSIFY_WORD_LIE_492],[THAT_WORD_POINTING_379],[APPLE_PIC_FRUITS_9],[EASTER_WORD_HOLIDAY_163],[HOT_DOG_WORD_FOOD_3],[LEAGUE_WORD_UNITE_126],[KIWI_PIC_FRUITS_9],[PIZZA_WORD_FOOD_3],[THIS_WORD_POINTING_379],[TALE_WORD_LEGENDS_291],[FRIES_WORD_FOOD_3]]</t>
   </si>
   <si>
     <t>[WORD_HOLIDAY_163,WORD_HELP_183,PIC_FRUITS_9]</t>
@@ -288,7 +288,7 @@
     <t>SORT_GAME_LEVE_6_BOARD_1</t>
   </si>
   <si>
-    <t>[[HEATER_WORD_DEVICE_38,WINTER_WORD_SEASONS_18],[OPINION_WORD_ARTICLES_147],[ROAD_WORD_DRIVING_49,KNEE_WORD_LEGS_322],[SUCCESS_WORD_WREATH_544],[VIOLIN_PIC_PLAY_12],[ORGAN_PIC_PLAY_12],[ICEBERG_WORD_SNOW_77],[FLAKE_WORD_SNOW_77],[SIGN_WORD_DRIVING_49],[FLOWERS_WORD_DATE_87],[BOBBER_WORD_FISHING_20],[TRAFFIC_WORD_DRIVING_49],[SUMMER_WORD_SEASONS_18],[PIANO_PIC_PLAY_12],[VICTORY_WORD_WREATH_544],[UKULELE_PIC_PLAY_12],[FLUTE_PIC_PLAY_12],[ESSAY_WORD_ARTICLES_147],[SLEET_WORD_SNOW_77],[TRIUMPH_WORD_WREATH_544,SPRING_WORD_SEASONS_18],[CAR_WORD_DRIVING_49,AUTUMN_WORD_SEASONS_18],[CELLO_PIC_PLAY_12],[GUITAR_PIC_PLAY_12],[REVIEW_WORD_ARTICLES_147,LEMON_WORD_CITRUS_173],[DRUM_PIC_PLAY_12]]</t>
+    <t>[[SURF_WORD_COAST_969,BEACH_WORD_COAST_969],[OPINION_WORD_ARTICLES_147],[ROAD_WORD_DRIVING_49,KNEE_WORD_LEGS_322],[SUCCESS_WORD_WREATH_544],[VIOLIN_PIC_PLAY_12],[ORGAN_PIC_PLAY_12],[ICEBERG_WORD_SNOW_77],[FLAKE_WORD_SNOW_77],[SIGN_WORD_DRIVING_49],[CLIFF_WORD_COAST_969],[BOBBER_WORD_FISHING_20],[TRAFFIC_WORD_DRIVING_49],[SUMMER_WORD_SEASONS_18],[PIANO_PIC_PLAY_12],[VICTORY_WORD_WREATH_544],[UKULELE_PIC_PLAY_12],[FLUTE_PIC_PLAY_12],[ESSAY_WORD_ARTICLES_147],[SLEET_WORD_SNOW_77],[TRIUMPH_WORD_WREATH_544,SPRING_WORD_SEASONS_18],[CAR_WORD_DRIVING_49,AUTUMN_WORD_SEASONS_18],[CELLO_PIC_PLAY_12],[GUITAR_PIC_PLAY_12],[REVIEW_WORD_ARTICLES_147,LEMON_WORD_CITRUS_173],[DRUM_PIC_PLAY_12]]</t>
   </si>
   <si>
     <t>[WORD_WREATH_544,WORD_ARTICLES_147,WORD_DRIVING_49,PIC_PLAY_12,WORD_SNOW_77]</t>
@@ -342,7 +342,7 @@
     <t>[8,12]</t>
   </si>
   <si>
-    <t>[[VACUUM_PIC_CLEANING_13,SAVATE_WORD_COMBAT_121],[PATROL_WORD_DEFENSE_277,SILAT_WORD_COMBAT_121],[SPEEDWAY_WORD_RACING_182],[GUARD_WORD_DEFENSE_277,SKELETON_WORD_SLIDING_339],[PIT_STOP_WORD_RACING_182],[KING_WORD_CROWN_194,POLAR_BEAR_WORD_ARCTIC_180],[BROOM_PIC_CLEANING_13],[HAMMOCK_WORD_CAMPING_221],[CCTV_WORD_DEFENSE_277],[SECURITY_WORD_DEFENSE_277],[DUSTPAN_PIC_CLEANING_13],[CAMPFIRE_WORD_CAMPING_221],[BIN_PIC_CLEANING_13],[DUSTER_PIC_CLEANING_13,JUDO_WORD_COMBAT_121],[BUCKET_PIC_CLEANING_13],[EMPEROR_WORD_CROWN_194],[POPULAR_WORD_FAME_161],[MAHARAJA_WORD_CROWN_194],[ICONIC_WORD_FAME_161],[MOP_PIC_CLEANING_13,KARATE_WORD_COMBAT_121],[TENT_WORD_CAMPING_221,FINISH_WORD_RACING_182],[LUGE_WORD_SLIDING_339],[RENOWN_WORD_FAME_161],[FAMOUS_WORD_FAME_161],[SPONGE_PIC_CLEANING_13,KUNG_FU_WORD_COMBAT_121]]</t>
+    <t>[[VACUUM_PIC_CLEANING_13,TV_WORD_SCREEN_1030],[PATROL_WORD_DEFENSE_277,ATM_WORD_SCREEN_1030],[SPEEDWAY_WORD_RACING_182],[GUARD_WORD_DEFENSE_277,SKELETON_WORD_SLIDING_339],[PIT_STOP_WORD_RACING_182],[KING_WORD_CROWN_194,POLAR_BEAR_WORD_ARCTIC_180],[BROOM_PIC_CLEANING_13],[HAMMOCK_WORD_CAMPING_221],[CCTV_WORD_DEFENSE_277],[SECURITY_WORD_DEFENSE_277],[DUSTPAN_PIC_CLEANING_13],[CAMPFIRE_WORD_CAMPING_221],[BIN_PIC_CLEANING_13],[DUSTER_PIC_CLEANING_13,E_READER_WORD_SCREEN_1030],[BUCKET_PIC_CLEANING_13],[EMPEROR_WORD_CROWN_194],[POPULAR_WORD_FAME_161],[MAHARAJA_WORD_CROWN_194],[ICONIC_WORD_FAME_161],[MOP_PIC_CLEANING_13,BUZZER_WORD_ALARM_1031],[TENT_WORD_CAMPING_221,FINISH_WORD_RACING_182],[LUGE_WORD_SLIDING_339],[RENOWN_WORD_FAME_161],[FAMOUS_WORD_FAME_161],[SPONGE_PIC_CLEANING_13,BEEP_WORD_ALARM_1031]]</t>
   </si>
   <si>
     <t>[WORD_CAMPING_221,WORD_FAME_161,PIC_CLEANING_13,WORD_CROWN_194,WORD_DEFENSE_277,WORD_RACING_182]</t>
@@ -360,7 +360,7 @@
     <t>[2,3]</t>
   </si>
   <si>
-    <t>[[COMFY_WORD_COZY_58,BRICK_WORD_STREET_768],[ACE_OF_HEARTS_PIC_DECK_4,BIKE_WORD_STREET_768],[SKIING_WORD_SLIDING_339,CORNER_WORD_STREET_768],[JUDO_WORD_COMBAT_121,MYTH_WORD_LEGENDS_291],[AIR_BIKE_WORD_GYM_164,SAGA_WORD_LEGENDS_291],[YACHT_WORD_LUXURY_133],[DUMBBELL_WORD_GYM_164],[QUEEN_HEARTS_PIC_DECK_4],[SILAT_WORD_COMBAT_121],[LUGE_WORD_SLIDING_339,KUNG_FU_WORD_COMBAT_121],[KING_HEARTS_PIC_DECK_4,KARATE_WORD_COMBAT_121],[SLEDDING_WORD_SLIDING_339],[SAVATE_WORD_COMBAT_121],[SKATING_WORD_SLIDING_339,GAVEL_WORD_JUSTICE_310],[JEWELRY_WORD_LUXURY_133,SCALES_WORD_JUSTICE_310],[WARM_WORD_COZY_58,FALSIFY_WORD_LIE_492],[CAVIAR_WORD_LUXURY_133,MISLEAD_WORD_LIE_492],[COURT_WORD_JUSTICE_310,SEXTANT_WORD_NAVIGATE_230],[SKELETON_WORD_SLIDING_339],[COAL_WORD_FUELS_190],[SNUG_WORD_COZY_58],[SUMO_WORD_COMBAT_121],[LAW_WORD_JUSTICE_310],[BARBELL_WORD_GYM_164],[WATCH_WORD_LUXURY_133,GASOLINE_WORD_FUELS_190]]</t>
+    <t>[[COMFY_WORD_COZY_58,BRICK_WORD_STREET_768],[ACE_OF_HEARTS_PIC_DECK_4,DNA_WORD_GENETICS_1060],[SKIING_WORD_SLIDING_339,CORNER_WORD_STREET_768],[JUDO_WORD_COMBAT_121,MYTH_WORD_LEGENDS_291],[AIR_BIKE_WORD_GYM_164,SAGA_WORD_LEGENDS_291],[YACHT_WORD_LUXURY_133],[DUMBBELL_WORD_GYM_164],[QUEEN_HEARTS_PIC_DECK_4],[SILAT_WORD_COMBAT_121],[LUGE_WORD_SLIDING_339,KUNG_FU_WORD_COMBAT_121],[KING_HEARTS_PIC_DECK_4,KARATE_WORD_COMBAT_121],[SLEDDING_WORD_SLIDING_339],[SAVATE_WORD_COMBAT_121],[SKATING_WORD_SLIDING_339,GAVEL_WORD_JUSTICE_310],[JEWELRY_WORD_LUXURY_133,SCALES_WORD_JUSTICE_310],[WARM_WORD_COZY_58,FALSIFY_WORD_LIE_492],[CAVIAR_WORD_LUXURY_133,MISLEAD_WORD_LIE_492],[COURT_WORD_JUSTICE_310,SEXTANT_WORD_NAVIGATE_230],[SKELETON_WORD_SLIDING_339],[COAL_WORD_FUELS_190],[SNUG_WORD_COZY_58],[SUMO_WORD_COMBAT_121],[LAW_WORD_JUSTICE_310],[BARBELL_WORD_GYM_164],[WATCH_WORD_LUXURY_133,GASOLINE_WORD_FUELS_190]]</t>
   </si>
   <si>
     <t>[WORD_GYM_164,WORD_COZY_58,WORD_COMBAT_121,WORD_LUXURY_133,PIC_DECK_4,WORD_SLIDING_339,WORD_JUSTICE_310]</t>
@@ -387,7 +387,7 @@
     <t>[3,4]</t>
   </si>
   <si>
-    <t>[[MYTH_WORD_LEGENDS_291,JOGGING_WORD_FITNESS_110],[MISLEAD_WORD_LIE_492,WORM_WORD_NO_BONES_289],[FABLE_WORD_LEGENDS_291,SPIDER_WORD_NO_BONES_289],[HORROR_WORD_CINEMA_6,SPRAIN_WORD_INJURIES_249],[WRENCH_PIC_TOOLBOX_6,DRACO_WORD_PATTERN_188],[SIGNPOST_WORD_NAVIGATE_230],[SAGA_WORD_LEGENDS_291],[POPCORN_WORD_CINEMA_6],[WORKOUT_WORD_FITNESS_110],[TALE_WORD_LEGENDS_291],[FALSIFY_WORD_LIE_492],[LEAGUE_WORD_UNITE_126],[PLIERS_PIC_TOOLBOX_6],[SEXTANT_WORD_NAVIGATE_230],[COMPASS_WORD_NAVIGATE_230],[DRILL_PIC_TOOLBOX_6],[BROCCOLI_PIC_VEGGIE_8],[DECEIVE_WORD_LIE_492,UNION_WORD_UNITE_126],[EPIC_WORD_LEGENDS_291],[ADHESIVE_TAPE_PIC_TOOLBOX_6,ALLIANCE_WORD_UNITE_126],[SCORPIUS_WORD_PATTERN_188],[CABBAGE_PIC_VEGGIE_8],[ROSE_WORD_FLOWERS_4],[DELUDE_WORD_LIE_492],[POTATO_PIC_VEGGIE_8]]</t>
+    <t>[[MYTH_WORD_LEGENDS_291,JOGGING_WORD_FITNESS_110],[MISLEAD_WORD_LIE_492,WORM_WORD_NO_BONES_289],[FABLE_WORD_LEGENDS_291,SPIDER_WORD_NO_BONES_289],[HORROR_WORD_CINEMA_6,SPRAIN_WORD_INJURIES_249],[WRENCH_PIC_TOOLBOX_6,TIRE_WORD_WHEEL_890],[SIGNPOST_WORD_NAVIGATE_230],[SAGA_WORD_LEGENDS_291],[POPCORN_WORD_CINEMA_6],[WORKOUT_WORD_FITNESS_110],[TALE_WORD_LEGENDS_291],[FALSIFY_WORD_LIE_492],[LEAGUE_WORD_UNITE_126],[PLIERS_PIC_TOOLBOX_6],[SEXTANT_WORD_NAVIGATE_230],[COMPASS_WORD_NAVIGATE_230],[DRILL_PIC_TOOLBOX_6],[BROCCOLI_PIC_VEGGIE_8],[DECEIVE_WORD_LIE_492,UNION_WORD_UNITE_126],[EPIC_WORD_LEGENDS_291],[ADHESIVE_TAPE_PIC_TOOLBOX_6,ALLIANCE_WORD_UNITE_126],[SCORPIUS_WORD_PATTERN_188],[CABBAGE_PIC_VEGGIE_8],[ROSE_WORD_FLOWERS_4],[DELUDE_WORD_LIE_492],[POTATO_PIC_VEGGIE_8]]</t>
   </si>
   <si>
     <t>[WORD_NAVIGATE_230,WORD_LIE_492,PIC_TOOLBOX_6,WORD_LEGENDS_291,PIC_VEGGIE_8,WORD_UNITE_126]</t>
@@ -420,7 +420,7 @@
     <t>[4,8]</t>
   </si>
   <si>
-    <t>[[DANISH_WORD_LANGUAGE_70,HAMMER_WORD_AUCTION_215],[BEAGLE_PIC_DOGS_18,ZEN_WORD_MEDITATE_160],[TRIBECA_WORD_NEW_YORK_287,HUSKY_PIC_DOGS_18],[HEBREW_WORD_LANGUAGE_70,BREATH_WORD_MEDITATE_160],[CITY_WORD_DIVISION_242,FREEDOM_WORD_HIPPIE_349],[LATIN_WORD_LANGUAGE_70,SNEAKERS_WORD_FOOTWEAR_46],[STATE_WORD_DIVISION_242,LOAFERS_WORD_FOOTWEAR_46],[ITALIAN_WORD_LANGUAGE_70],[POODLE_PIC_DOGS_18,MULBERRY_WORD_BERRY_116],[SOHO_WORD_NEW_YORK_287,TERRIER_PIC_DOGS_18],[SPANIEL_PIC_DOGS_18,UGGS_WORD_FOOTWEAR_46],[BRONX_WORD_NEW_YORK_287,BISHOP_WORD_CHESS_17],[QUEENS_WORD_NEW_YORK_287],[BIBLE_WORD_PRIEST_1019,COLUMBUS_WORD_EXPLORER_51],[PREACHER_WORD_PRIEST_1019],[SAINT_WORD_PRIEST_1019,CACTUS_WORD_SPIKY_78],[ASTORIA_WORD_NEW_YORK_287],[HARLEM_WORD_NEW_YORK_287,BILBERRY_WORD_BERRY_116],[JAPANESE_WORD_LANGUAGE_70,DURIAN_WORD_SPIKY_78],[HINDI_WORD_LANGUAGE_70,HEDGEHOG_WORD_SPIKY_78],[POLISH_WORD_LANGUAGE_70],[REGION_WORD_DIVISION_242],[CLERIC_WORD_PRIEST_1019,BARBERRY_WORD_BERRY_116],[COUNTRY_WORD_DIVISION_242,LOT_WORD_AUCTION_215],[ENGLISH_WORD_LANGUAGE_70]]</t>
+    <t>[[DANISH_WORD_LANGUAGE_70,HAMMER_WORD_AUCTION_215],[BEAGLE_PIC_DOGS_18,ZEN_WORD_MEDITATE_160],[TRIBECA_WORD_NEW_YORK_287,HUSKY_PIC_DOGS_18],[HEBREW_WORD_LANGUAGE_70,BREATH_WORD_MEDITATE_160],[CITY_WORD_DIVISION_242,FREEDOM_WORD_HIPPIE_349],[LATIN_WORD_LANGUAGE_70,SNEAKERS_WORD_FOOTWEAR_46],[STATE_WORD_DIVISION_242,LOAFERS_WORD_FOOTWEAR_46],[ITALIAN_WORD_LANGUAGE_70],[POODLE_PIC_DOGS_18,MULBERRY_WORD_BERRY_116],[SOHO_WORD_NEW_YORK_287,TERRIER_PIC_DOGS_18],[SPANIEL_PIC_DOGS_18,UGGS_WORD_FOOTWEAR_46],[BRONX_WORD_NEW_YORK_287,AUTUMN_WORD_SEASONS_18],[QUEENS_WORD_NEW_YORK_287],[BIBLE_WORD_PRIEST_1019,COLUMBUS_WORD_EXPLORER_51],[PREACHER_WORD_PRIEST_1019],[SAINT_WORD_PRIEST_1019,CACTUS_WORD_SPIKY_78],[ASTORIA_WORD_NEW_YORK_287],[HARLEM_WORD_NEW_YORK_287,BILBERRY_WORD_BERRY_116],[JAPANESE_WORD_LANGUAGE_70,DURIAN_WORD_SPIKY_78],[HINDI_WORD_LANGUAGE_70,HEDGEHOG_WORD_SPIKY_78],[POLISH_WORD_LANGUAGE_70],[REGION_WORD_DIVISION_242],[CLERIC_WORD_PRIEST_1019,BARBERRY_WORD_BERRY_116],[COUNTRY_WORD_DIVISION_242,LOT_WORD_AUCTION_215],[ENGLISH_WORD_LANGUAGE_70]]</t>
   </si>
   <si>
     <t>[WORD_NEW_YORK_287,WORD_LANGUAGE_70,WORD_DIVISION_242,WORD_PRIEST_1019,PIC_DOGS_18,WORD_SPIKY_78,WORD_BERRY_116]</t>
@@ -432,7 +432,7 @@
     <t>[11]</t>
   </si>
   <si>
-    <t>[[FRIES_PIC_EATS_19,TUGBOAT_WORD_SHIP_62],[ZEN_WORD_MEDITATE_160,LOAFERS_WORD_FOOTWEAR_46],[BICEPS_WORD_MUSCLES_112,COLOSSEUM_WORD_LANDMARK_948],[VANS_WORD_HIPPIE_349,PYRAMIDS_WORD_LANDMARK_948],[FRIGATE_WORD_SHIP_62,PAWN_WORD_CHESS_17],[PEACE_WORD_MEDITATE_160,BISHOP_WORD_CHESS_17],[DELTOIDS_WORD_MUSCLES_112,TACO_PIC_EATS_19],[FREEDOM_WORD_HIPPIE_349,LOZENGES_WORD_PILLS_99],[CARAVEL_WORD_SHIP_62,CAPSULES_WORD_PILLS_99],[HAMMER_WORD_AUCTION_215,VESPUCCI_WORD_EXPLORER_51],[LOT_WORD_AUCTION_215,ICELAND_WORD_ISLANDS_21],[ABS_WORD_MUSCLES_112,IBIZA_WORD_ISLANDS_21],[COMMUNE_WORD_HIPPIE_349],[CATALOG_WORD_AUCTION_215,JAMAICA_WORD_ISLANDS_21],[MANTRA_WORD_MEDITATE_160,SICILY_WORD_ISLANDS_21],[BID_WORD_AUCTION_215,WHARF_WORD_HARBOR_764],[PIZZA_PIC_EATS_19,COAST_WORD_HARBOR_764],[TANKER_WORD_SHIP_62,POINTE_WORD_BALLET_125],[RUNWAY_WORD_AIRPORT_29,GALLEON_WORD_SHIP_62],[PRICE_WORD_AUCTION_215,TORNADO_WORD_DISASTER_148],[TRICEPS_WORD_MUSCLES_112],[BREATH_WORD_MEDITATE_160,SANDALS_WORD_FOOTWEAR_46],[GATE_WORD_AIRPORT_29],[BIDDER_WORD_AUCTION_215],[TERMINAL_WORD_AIRPORT_29,BRIG_WORD_SHIP_62]]</t>
+    <t>[[FRIES_PIC_EATS_19,TUGBOAT_WORD_SHIP_62],[ZEN_WORD_MEDITATE_160,TRIUMPH_WORD_WREATH_544],[BICEPS_WORD_MUSCLES_112,COLOSSEUM_WORD_LANDMARK_948],[VANS_WORD_HIPPIE_349,PYRAMIDS_WORD_LANDMARK_948],[FRIGATE_WORD_SHIP_62,PAWN_WORD_CHESS_17],[PEACE_WORD_MEDITATE_160,BISHOP_WORD_CHESS_17],[DELTOIDS_WORD_MUSCLES_112,TACO_PIC_EATS_19],[FREEDOM_WORD_HIPPIE_349,LOZENGES_WORD_PILLS_99],[CARAVEL_WORD_SHIP_62,CAPSULES_WORD_PILLS_99],[HAMMER_WORD_AUCTION_215,VICTORY_WORD_WREATH_544],[LOT_WORD_AUCTION_215,ICELAND_WORD_ISLANDS_21],[ABS_WORD_MUSCLES_112,IBIZA_WORD_ISLANDS_21],[COMMUNE_WORD_HIPPIE_349],[CATALOG_WORD_AUCTION_215,JAMAICA_WORD_ISLANDS_21],[MANTRA_WORD_MEDITATE_160,SICILY_WORD_ISLANDS_21],[BID_WORD_AUCTION_215,WHARF_WORD_HARBOR_764],[PIZZA_PIC_EATS_19,COAST_WORD_HARBOR_764],[TANKER_WORD_SHIP_62,POINTE_WORD_BALLET_125],[RUNWAY_WORD_AIRPORT_29,GALLEON_WORD_SHIP_62],[PRICE_WORD_AUCTION_215,TORNADO_WORD_DISASTER_148],[TRICEPS_WORD_MUSCLES_112],[BREATH_WORD_MEDITATE_160,SANDALS_WORD_FOOTWEAR_46],[GATE_WORD_AIRPORT_29],[BIDDER_WORD_AUCTION_215],[TERMINAL_WORD_AIRPORT_29,BRIG_WORD_SHIP_62]]</t>
   </si>
   <si>
     <t>[WORD_MEDITATE_160,WORD_AUCTION_215,WORD_AIRPORT_29,WORD_MUSCLES_112,WORD_SHIP_62,PIC_EATS_19,WORD_HIPPIE_349]</t>
@@ -444,7 +444,7 @@
     <t>[4,6]</t>
   </si>
   <si>
-    <t>[[LIBRARY_PIC_BUILD_20],[SPHINX_WORD_LANDMARK_948,SICILY_WORD_ISLANDS_21],[HOTEL_PIC_BUILD_20,JAMAICA_WORD_ISLANDS_21],[TIRE_WORD_WHEEL_890,PIER_WORD_HARBOR_764],[VESPUCCI_WORD_EXPLORER_51,AXLE_WORD_WHEEL_890],[MUSEUM_PIC_BUILD_20,SNEAKERS_WORD_FOOTWEAR_46],[PAWN_WORD_CHESS_17,REAGAN_WORD_LEADER_196],[OGRE_PIC_FOLKLORE_21,KENNEDY_WORD_LEADER_196],[STADIUM_PIC_BUILD_20,SERUM_WORD_MAKEUP_120],[COLOSSEUM_WORD_LANDMARK_948,SPONGE_WORD_MAKEUP_120],[FACTORY_PIC_BUILD_20,PYRAMIDS_WORD_LANDMARK_948],[LOZENGES_WORD_PILLS_99,PEEL_WORD_MAKEUP_120],[MALL_PIC_BUILD_20,SHINOBI_WORD_WARRIORS_491],[HOSPITAL_PIC_BUILD_20,RONIN_WORD_WARRIORS_491],[CAPSULES_WORD_PILLS_99,FIGURINE_WORD_SCULPT_64],[SCHOOL_BUILDING_PIC_BUILD_20,SLIPPERS_WORD_FOOTWEAR_46],[MAGELLAN_WORD_EXPLORER_51],[QUEEN_WORD_CHESS_17,CLOGS_WORD_FOOTWEAR_46],[GOBLIN_PIC_FOLKLORE_21,SANDALS_WORD_FOOTWEAR_46],[ROOK_WORD_CHESS_17,UGGS_WORD_FOOTWEAR_46],[COLUMBUS_WORD_EXPLORER_51,LOAFERS_WORD_FOOTWEAR_46],[BIG_BEN_WORD_LANDMARK_948,DEGREE_WORD_PHD_296],[TABLETS_WORD_PILLS_99],[TROLL_PIC_FOLKLORE_21],[BISHOP_WORD_CHESS_17]]</t>
+    <t>[[LIBRARY_PIC_BUILD_20],[SPHINX_WORD_LANDMARK_948,SICILY_WORD_ISLANDS_21],[HOTEL_PIC_BUILD_20,JAMAICA_WORD_ISLANDS_21],[TIRE_WORD_WHEEL_890,PIER_WORD_HARBOR_764],[VESPUCCI_WORD_EXPLORER_51,AXLE_WORD_WHEEL_890],[MUSEUM_PIC_BUILD_20,SNEAKERS_WORD_FOOTWEAR_46],[PAWN_WORD_CHESS_17,REAGAN_WORD_LEADER_196],[OGRE_PIC_FOLKLORE_21,KENNEDY_WORD_LEADER_196],[STADIUM_PIC_BUILD_20,SERUM_WORD_MAKEUP_120],[COLOSSEUM_WORD_LANDMARK_948,SPONGE_WORD_MAKEUP_120],[FACTORY_PIC_BUILD_20,PYRAMIDS_WORD_LANDMARK_948],[LOZENGES_WORD_PILLS_99,PEEL_WORD_MAKEUP_120],[MALL_PIC_BUILD_20,CURRENT_WORD_PRESENT_470],[HOSPITAL_PIC_BUILD_20,NOW_WORD_PRESENT_470],[CAPSULES_WORD_PILLS_99,FIGURINE_WORD_SCULPT_64],[SCHOOL_BUILDING_PIC_BUILD_20,SLIPPERS_WORD_FOOTWEAR_46],[MAGELLAN_WORD_EXPLORER_51],[QUEEN_WORD_CHESS_17,CLOGS_WORD_FOOTWEAR_46],[GOBLIN_PIC_FOLKLORE_21,SANDALS_WORD_FOOTWEAR_46],[ROOK_WORD_CHESS_17,UGGS_WORD_FOOTWEAR_46],[COLUMBUS_WORD_EXPLORER_51,LOAFERS_WORD_FOOTWEAR_46],[BIG_BEN_WORD_LANDMARK_948,DEGREE_WORD_PHD_296],[TABLETS_WORD_PILLS_99],[TROLL_PIC_FOLKLORE_21],[BISHOP_WORD_CHESS_17]]</t>
   </si>
   <si>
     <t>[WORD_PILLS_99,WORD_EXPLORER_51,PIC_FOLKLORE_21,PIC_BUILD_20,WORD_CHESS_17,WORD_LANDMARK_948,WORD_FOOTWEAR_46]</t>
@@ -495,13 +495,13 @@
     <t>SORT_GAME_LEVE_22_BOARD_1</t>
   </si>
   <si>
-    <t>[5,10]</t>
-  </si>
-  <si>
-    <t>[[DAISY_PIC_FLOWERS_29,BREEZE_WORD_COASTAL_882,TIDE_WORD_COASTAL_882],[UK_WORD_MAP_32,SHINGLE_WORD_COASTAL_882,JETTY_WORD_COASTAL_882],[CYBORG_WORD_ROBOT_354,FLAMENCO_WORD_DANCES_24,RUMBA_WORD_DANCES_24],[LIZARD_PIC_REPTILES_30,SAMBA_WORD_DANCES_24,HURON_WORD_LAKES_365],[DRONE_WORD_ROBOT_354,MACHINE_WORD_ROBOT_354],[JAPAN_WORD_MAP_32,SUPERIOR_WORD_LAKES_365,PENALTY_WORD_HOCKEY_86],[USA_WORD_MAP_32,GOAL_WORD_HOCKEY_86],[ROME_WORD_ITALY_376,STRINGS_WORD_GUITAR_122],[FLORENCE_WORD_ITALY_376,AMAZON_WORD_RIVERS_959],[ITALY_WORD_MAP_32,TENOR_WORD_VOICES_439],[AUSTRALIA_WORD_MAP_32,DICAPRIO_WORD_ACTOR_89],[SIGMA_WORD_GREECE_359,OLDMAN_WORD_ACTOR_89],[KAPPA_WORD_GREECE_359,WAHLBERG_WORD_ACTOR_89],[ROBOVAC_WORD_ROBOT_354,CAPTAIN_WORD_ARMY_156],[SNAKE_PIC_REPTILES_30,ALTO_WORD_VOICES_439],[CYPRUS_WORD_MAP_32,RANK_WORD_ARMY_156],[ANDROID_WORD_ROBOT_354,SERGEANT_WORD_ARMY_156],[FRANCE_WORD_MAP_32,EXPOSURE_WORD_CAMERA_73],[ALLIGATOR_PIC_REPTILES_30,SYNTAX_WORD_LINGUIST_162],[INDIA_WORD_MAP_32,VENICE_WORD_ITALY_376],[BASS_WORD_VOICES_439,SHOOTER_WORD_GAMER_36],[DELTA_WORD_GREECE_359,ARCADE_WORD_GAMER_36],[SCORE_WORD_GAMER_36,LILY_PIC_FLOWERS_29,STRATEGY_WORD_GAMER_36],[NANOBOT_WORD_ROBOT_354,TULIP_PIC_FLOWERS_29,SOPRANO_WORD_VOICES_439],[MILAN_WORD_ITALY_376,BARITONE_WORD_VOICES_439]]</t>
-  </si>
-  <si>
-    <t>[WORD_GREECE_359,PIC_REPTILES_30,WORD_MAP_32,WORD_ROBOT_354,WORD_ITALY_376,PIC_FLOWERS_29,WORD_GAMER_36,WORD_VOICES_439]</t>
+    <t>[10,11]</t>
+  </si>
+  <si>
+    <t>[[SNAKE_PIC_REPTILES_30,NANOBOT_WORD_ROBOT_354,SOPRANO_WORD_VOICES_439],[ROME_WORD_ITALY_376,CREST_WORD_COASTAL_882,BAIKAL_WORD_LAKES_365],[FLORENCE_WORD_ITALY_376,ONTARIO_WORD_LAKES_365,TITICACA_WORD_LAKES_365],[VENICE_WORD_ITALY_376,PUCK_WORD_HOCKEY_86,GOLDFISH_WORD_FISH_31],[SATURN_WORD_PLANET_90,DAISY_PIC_FLOWERS_29],[DELTA_WORD_GREECE_359,TUNA_WORD_FISH_31,HANKS_WORD_ACTOR_89],[DRONE_WORD_ROBOT_354,SHOOTER_WORD_GAMER_36],[STRATEGY_WORD_GAMER_36,CAPTAIN_WORD_ARMY_156,GENERAL_WORD_ARMY_156],[MACHINE_WORD_ROBOT_354,SERGEANT_WORD_ARMY_156],[NEPTUNE_WORD_PLANET_90,ARCADE_WORD_GAMER_36,BARITONE_WORD_VOICES_439],[MARS_WORD_PLANET_90,LENS_WORD_CAMERA_73],[CYBORG_WORD_ROBOT_354,ZOOM_WORD_CAMERA_73],[ANDROID_WORD_ROBOT_354,MILAN_WORD_ITALY_376],[URANUS_WORD_PLANET_90,POLYGLOT_WORD_LINGUIST_162],[LILY_PIC_FLOWERS_29,TENOR_WORD_VOICES_439],[LIZARD_PIC_REPTILES_30,SYNTAX_WORD_LINGUIST_162],[ALLIGATOR_PIC_REPTILES_30,SCHOLAR_WORD_LINGUIST_162],[MERCURY_WORD_PLANET_90,DUALISM_WORD_VIEWS_410],[KAPPA_WORD_GREECE_359,ALTO_WORD_VOICES_439],[JUPITER_WORD_PLANET_90,SCORE_WORD_GAMER_36],[EARTH_WORD_PLANET_90,STOICISM_WORD_VIEWS_410],[VENUS_WORD_PLANET_90,TAIGA_WORD_BIOMES_135],[SIGMA_WORD_GREECE_359,TUNDRA_WORD_BIOMES_135],[ROBOVAC_WORD_ROBOT_354,SAVANNA_WORD_BIOMES_135],[BASS_WORD_VOICES_439,TULIP_PIC_FLOWERS_29]]</t>
+  </si>
+  <si>
+    <t>[WORD_GREECE_359,PIC_REPTILES_30,WORD_PLANET_90,WORD_ROBOT_354,WORD_ITALY_376,PIC_FLOWERS_29,WORD_GAMER_36,WORD_VOICES_439]</t>
   </si>
   <si>
     <t>SORT_GAME_LEVE_23_BOARD_1</t>
@@ -519,193 +519,193 @@
     <t>SORT_GAME_LEVE_24_BOARD_1</t>
   </si>
   <si>
-    <t>[3,7,11]</t>
-  </si>
-  <si>
-    <t>[[WAHLBERG_WORD_ACTOR_89,GENERAL_WORD_ARMY_156,SCHOLAR_WORD_LINGUIST_162],[HANKS_WORD_ACTOR_89,SERGEANT_WORD_ARMY_156,MARMOT_PIC_RODENTS_33],[LADYBUG_WORD_INSECTS_25,MUSTANG_WORD_EQUIDAE_475,MULE_WORD_EQUIDAE_475],[MAJOR_WORD_ARMY_156,ZEBRA_WORD_EQUIDAE_475,DONKEY_WORD_EQUIDAE_475],[OLDMAN_WORD_ACTOR_89,LYRICS_WORD_RAP_151,PUNCH_WORD_RAP_151],[DICAPRIO_WORD_ACTOR_89,RHYME_WORD_RAP_151,LIBERICA_WORD_BEANS_219],[CRUISE_WORD_ACTOR_89,RANK_WORD_ARMY_156],[SAVANNA_WORD_BIOMES_135,NEUTRON_WORD_PARTICLE_281,ATOM_WORD_PARTICLE_281],[DUALISM_WORD_VIEWS_410,VIOLIN_WORD_PLAY_223,ORGAN_WORD_PLAY_223],[ROBUSTA_WORD_BEANS_219,PIANO_WORD_PLAY_223,WASP_WORD_INSECTS_25],[COLONEL_WORD_ARMY_156,NIHILISM_WORD_VIEWS_410,COWBOY_BOOTS_PIC_WESTERN_34],[BEAVER_PIC_RODENTS_33,PRIVATE_WORD_ARMY_156],[CORPORAL_WORD_ARMY_156,SYNTAX_WORD_LINGUIST_162],[STOICISM_WORD_VIEWS_410,SQUIRREL_PIC_RODENTS_33,LENS_WORD_CAMERA_73],[PITT_WORD_ACTOR_89,COWBOY_HAT_PIC_WESTERN_34,NUTRIA_PIC_RODENTS_33],[FLASH_WORD_CAMERA_73,DRAGONFLY_WORD_INSECTS_25,ASSESS_WORD_EVALUATE_651],[CROWE_WORD_ACTOR_89,FILTER_WORD_CAMERA_73,LASSO_PIC_WESTERN_34],[MOSQUITO_WORD_INSECTS_25,ANALYZE_WORD_EVALUATE_651],[TUNDRA_WORD_BIOMES_135,SHUTTER_WORD_CAMERA_73],[IMPORT_WORD_CUSTOMS_592,MATE_WORD_ANAGRAM_511],[ACROSTIC_WORD_POETRY_440,TEAM_WORD_ANAGRAM_511],[TAIGA_WORD_BIOMES_135,EXPOSURE_WORD_CAMERA_73,POLYGLOT_WORD_LINGUIST_162],[ZOOM_WORD_CAMERA_73,MINE_WORD_SHAFT_331],[CAPTAIN_WORD_ARMY_156,PICKAXE_WORD_SHAFT_331],[EASTWOOD_WORD_ACTOR_89,GRAMMAR_WORD_LINGUIST_162]]</t>
-  </si>
-  <si>
-    <t>[WORD_BIOMES_135,WORD_ARMY_156,WORD_ACTOR_89,WORD_VIEWS_410,PIC_RODENTS_33,WORD_CAMERA_73,WORD_LINGUIST_162,PIC_WESTERN_34]</t>
+    <t>[5,7,12]</t>
+  </si>
+  <si>
+    <t>[[WAHLBERG_WORD_ACTOR_89,MULE_WORD_EQUIDAE_475,MOSQUITO_WORD_INSECTS_25],[FOOL_PIC_TAROT_48,SERGEANT_WORD_ARMY_156],[EXPOSURE_WORD_CAMERA_73,LADYBUG_WORD_INSECTS_25,PUNCH_WORD_RAP_151],[FLASH_WORD_CAMERA_73,LYRICS_WORD_RAP_151,WALTZ_WORD_DANCES_24],[MAJOR_WORD_ARMY_156,CORPORAL_WORD_ARMY_156,SYNTAX_WORD_LINGUIST_162],[GUITAR_WORD_PLAY_223,LIBERICA_WORD_BEANS_219,ATOM_WORD_PARTICLE_281],[CRUISE_WORD_ACTOR_89,NIHILISM_WORD_VIEWS_410],[DRUM_WORD_PLAY_223,VIOLIN_WORD_PLAY_223,UKULELE_WORD_PLAY_223],[OLDMAN_WORD_ACTOR_89,RANK_WORD_ARMY_156,MAGICIAN_PIC_TAROT_48],[MEAT_WORD_ANAGRAM_511,ORGAN_WORD_PLAY_223,POPLAR_WORD_LEAVES_1055],[PIANO_WORD_PLAY_223,CHESTNUT_WORD_LEAVES_1055,ASH_WORD_LEAVES_1055],[SAVANNA_WORD_BIOMES_135,GENERAL_WORD_ARMY_156],[TUNDRA_WORD_BIOMES_135,MOON_PIC_TAROT_48,EMPRESS_PIC_TAROT_48],[CAPTAIN_WORD_ARMY_156,OAK_WORD_LEAVES_1055,EXPORT_WORD_CUSTOMS_592],[TANGO_WORD_DANCES_24,SAMBA_WORD_DANCES_24],[DUALISM_WORD_VIEWS_410,ESTIMATE_WORD_EVALUATE_651],[PRIVATE_WORD_ARMY_156,COLONEL_WORD_ARMY_156,COWBOY_BOOTS_PIC_WESTERN_34],[LENS_WORD_CAMERA_73,TEAM_WORD_ANAGRAM_511],[PITT_WORD_ACTOR_89,PICKAXE_WORD_SHAFT_331],[DICAPRIO_WORD_ACTOR_89,CART_WORD_SHAFT_331],[EASTWOOD_WORD_ACTOR_89,SCHOLAR_WORD_LINGUIST_162,GRAMMAR_WORD_LINGUIST_162],[STOICISM_WORD_VIEWS_410,ZOOM_WORD_CAMERA_73],[CROWE_WORD_ACTOR_89,LASSO_PIC_WESTERN_34,COWBOY_HAT_PIC_WESTERN_34],[TAIGA_WORD_BIOMES_135,SHUTTER_WORD_CAMERA_73],[HANKS_WORD_ACTOR_89,POLYGLOT_WORD_LINGUIST_162,FILTER_WORD_CAMERA_73]]</t>
+  </si>
+  <si>
+    <t>[WORD_BIOMES_135,WORD_ARMY_156,WORD_ACTOR_89,WORD_VIEWS_410,PIC_TAROT_48,WORD_CAMERA_73,WORD_LINGUIST_162,PIC_WESTERN_34]</t>
   </si>
   <si>
     <t>SORT_GAME_LEVE_25_BOARD_1</t>
   </si>
   <si>
+    <t>[2,7,12]</t>
+  </si>
+  <si>
+    <t>[[ODE_WORD_POETRY_440,DRUM_WORD_PLAY_223,PIANO_WORD_PLAY_223],[LION_WORD_CHIMERA_795,ACROSTIC_WORD_POETRY_440,ROBUSTA_WORD_BEANS_219],[ATOM_WORD_PARTICLE_281,ORGAN_WORD_PLAY_223,UKULELE_WORD_PLAY_223],[GUITAR_WORD_PLAY_223,CELLO_WORD_PLAY_223,VIOLIN_WORD_PLAY_223],[VERSE_WORD_RAP_151,SONNET_WORD_POETRY_440,CIRCLE_PIC_ICONS_79],[SERPENT_WORD_CHIMERA_795,LIBERICA_WORD_BEANS_219,LOCK_ICON_PIC_ICONS_79],[ZEBRA_WORD_EQUIDAE_475,CROSS_PIC_ICONS_79,CHECKMARK_PIC_ICONS_79],[DONKEY_WORD_EQUIDAE_475,SHELLS_PIC_BEACH_36,ARROW_PIC_ICONS_79],[BALLAD_WORD_POETRY_440,STAR_PIC_ICONS_79,ENVELOPE_ICON_PIC_ICONS_79],[MUSTANG_WORD_EQUIDAE_475,SAND_PIC_BEACH_36,HEART_PIC_ICONS_79],[RUDDER_WORD_PLANE_139,CHESTNUT_WORD_LEAVES_1055,MEAT_WORD_ANAGRAM_511],[ELECTRON_WORD_PARTICLE_281,WAVES_PIC_BEACH_36,BUOY_PIC_BEACH_36],[HORSE_WORD_EQUIDAE_475,BAY_PIC_BEACH_36],[DIVA_WORD_OPERA_760,CART_WORD_SHAFT_331,PICKAXE_WORD_SHAFT_331],[HAIKU_WORD_POETRY_440,FUSELAGE_WORD_PLANE_139,ENGINE_WORD_PLANE_139],[ANALYZE_WORD_EVALUATE_651,MONOCLE_WORD_OPTICS_229,SPYGLASS_WORD_OPTICS_229],[LYRICS_WORD_RAP_151,ARABICA_WORD_BEANS_219],[CAR_WORD_DRIVING_49,GLASSES_WORD_OPTICS_229,LENS_WORD_OPTICS_229],[PUNCH_WORD_RAP_151,KINETIC_WORD_ENERGY_145,NUCLEAR_WORD_ENERGY_145],[BEACH_CHAIR_PIC_BEACH_36,SOLAR_WORD_ENERGY_145,THERMAL_WORD_ENERGY_145],[GOAT_WORD_CHIMERA_795,EXCELSA_WORD_BEANS_219],[NEUTRON_WORD_PARTICLE_281,SEAGULL_PIC_BEACH_36,BEACH_UMBRELLA_PIC_BEACH_36],[MULE_WORD_EQUIDAE_475,YOGA_WORD_ZEN_549,ACT_WORD_OPERA_760],[RHYME_WORD_RAP_151,DUCKTAIL_WORD_BEARDS_681],[PONY_WORD_EQUIDAE_475,GOATEE_WORD_BEARDS_681]]</t>
+  </si>
+  <si>
+    <t>[WORD_POETRY_440,WORD_EQUIDAE_475,WORD_PARTICLE_281,WORD_CHIMERA_795,WORD_RAP_151,PIC_BEACH_36,PIC_ICONS_79,WORD_BEANS_219]</t>
+  </si>
+  <si>
+    <t>SORT_GAME_LEVE_26_BOARD_1</t>
+  </si>
+  <si>
+    <t>[2,5]</t>
+  </si>
+  <si>
+    <t>[[ROCKET_PIC_SPACE_38,AILERON_WORD_PLANE_139,COCKPIT_WORD_PLANE_139],[GUITAR_WORD_PLAY_223,ENGINE_WORD_PLANE_139,ICELAND_WORD_ISLANDS_21],[ASTRONAUT_PIC_SPACE_38,JAMAICA_WORD_ISLANDS_21,THERMAL_WORD_ENERGY_145],[ORGAN_WORD_PLAY_223,ACT_WORD_OPERA_760,DIVA_WORD_OPERA_760],[NOTEBOOK_PIC_SUPPLIES_70,MACBETH_WORD_WILLIAM_165,HENRY_V_WORD_WILLIAM_165],[MAPLE_WORD_LEAVES_1055,RUBBER_STAMP_PIC_SUPPLIES_70],[DUTY_WORD_CUSTOMS_592,VIOLIN_WORD_PLAY_223],[PIANO_WORD_PLAY_223,FILE_FOLDER_PIC_SUPPLIES_70],[CHESTNUT_WORD_LEAVES_1055,DRUM_WORD_PLAY_223],[BORDER_WORD_CUSTOMS_592,FLUTE_WORD_PLAY_223],[ASH_WORD_LEAVES_1055,TEMPEST_WORD_WILLIAM_165],[UFO_PIC_SPACE_38,ARMOR_WORD_KNIGHT_34],[ESTIMATE_WORD_EVALUATE_651,WEAPON_WORD_KNIGHT_34],[UKULELE_WORD_PLAY_223,ANGORA_WORD_BREEDS_940],[CELLO_WORD_PLAY_223,ENCODE_WORD_CIPHER_208],[POPLAR_WORD_LEAVES_1055,CRETE_WORD_ISLANDS_21],[IMPORT_WORD_CUSTOMS_592,HAWAII_WORD_ISLANDS_21],[ALIEN_PIC_SPACE_38,RUSH_WORD_ALARM_1031],[PAPERCLIP_PIC_SUPPLIES_70,BUZZER_WORD_ALARM_1031],[ANALYZE_WORD_EVALUATE_651,BEEP_WORD_ALARM_1031],[STAPLER_PIC_SUPPLIES_70,ASSESS_WORD_EVALUATE_651],[OAK_WORD_LEAVES_1055,PICKAXE_WORD_SHAFT_331,GAS_WORD_PHASE_57],[PALM_WORD_LEAVES_1055,SOLID_WORD_PHASE_57,LIQUID_WORD_PHASE_57],[EXPORT_WORD_CUSTOMS_592,CART_WORD_SHAFT_331],[TAPE_DISPENSER_PIC_SUPPLIES_70,MINE_WORD_SHAFT_331]]</t>
+  </si>
+  <si>
+    <t>[WORD_CUSTOMS_592,WORD_LEAVES_1055,WORD_PLAY_223,PIC_SUPPLIES_70,WORD_EVALUATE_651,PIC_SPACE_38,WORD_PHASE_57,WORD_SHAFT_331]</t>
+  </si>
+  <si>
+    <t>SORT_GAME_LEVE_27_BOARD_1</t>
+  </si>
+  <si>
+    <t>[7,12]</t>
+  </si>
+  <si>
+    <t>[[SPYGLASS_WORD_OPTICS_229,POWER_WORD_STRENGTH_401,FORCE_WORD_STRENGTH_401],[DHARMA_WORD_ZEN_549,RINZAI_WORD_ZEN_549],[ACT_WORD_OPERA_760,MIGHT_WORD_STRENGTH_401,TEXT_WORD_MESSAGE_407],[GOATEE_WORD_BEARDS_681,CHIVALRY_WORD_KNIGHT_34,BIRMAN_WORD_BREEDS_940],[LENS_WORD_OPTICS_229,ROLE_WORD_OPERA_760],[CLOWNFISH_PIC_SEA_FISH_39,SIAMESE_WORD_BREEDS_940,BENGAL_WORD_BREEDS_940],[SARDINE_PIC_SEA_FISH_39,COCKPIT_WORD_PLANE_139,AILERON_WORD_PLANE_139],[COD_PIC_SEA_FISH_39,DECODE_WORD_CIPHER_208,ATM_WORD_SCREEN_1030],[BOX_PIC_BIRTHDAY_40,WINGS_WORD_PLANE_139],[CANDLE_PIC_BIRTHDAY_40,E_READER_WORD_SCREEN_1030,TV_WORD_SCREEN_1030],[BIRTHDAY_HAT_PIC_BIRTHDAY_40,BEEP_WORD_ALARM_1031,NITROGEN_WORD_ELEMENTS_107],[DUCKTAIL_WORD_BEARDS_681,THERMAL_WORD_ENERGY_145],[SOLAR_WORD_ENERGY_145,TUNA_PIC_SEA_FISH_39,FUSELAGE_WORD_PLANE_139],[CAKE_PIC_BIRTHDAY_40,DIVA_WORD_OPERA_760,IODINE_WORD_ELEMENTS_107],[SAWFISH_PIC_SEA_FISH_39,DISHES_WORD_FOODIE_726],[BALLOON_PIC_BIRTHDAY_40,SYBARITE_WORD_FOODIE_726],[STINGRAY_PIC_SEA_FISH_39,MARLIN_PIC_SEA_FISH_39,SEATBELT_WORD_PLANE_139],[BALBO_WORD_BEARDS_681,EPICURE_WORD_FOODIE_726],[YOGA_WORD_ZEN_549,PLATE_WORD_DISHWARE_829],[CONFETTI_PIC_BIRTHDAY_40,GLUCAGON_WORD_HORMONES_259],[NUCLEAR_WORD_ENERGY_145,RUDDER_WORD_PLANE_139],[MONOCLE_WORD_OPTICS_229,FLY_WORD_PLANE_139,ENGINE_WORD_PLANE_139],[SHARK_PIC_SEA_FISH_39,INSULIN_WORD_HORMONES_259],[KINETIC_WORD_ENERGY_145,GASTRIN_WORD_HORMONES_259],[GLASSES_WORD_OPTICS_229,REED_WORD_POND_830]]</t>
+  </si>
+  <si>
+    <t>[WORD_ZEN_549,PIC_BIRTHDAY_40,WORD_BEARDS_681,WORD_OPERA_760,WORD_ENERGY_145,WORD_OPTICS_229,PIC_SEA_FISH_39,WORD_PLANE_139]</t>
+  </si>
+  <si>
+    <t>SORT_GAME_LEVE_28_BOARD_1</t>
+  </si>
+  <si>
+    <t>[7,10,12]</t>
+  </si>
+  <si>
+    <t>[[ELECTRIC_TOOTHBRUSH_PIC_CHARGER_41,NITROGEN_WORD_ELEMENTS_107,TASTE_WORD_FOODIE_726],[SMARTWATCH_PIC_CHARGER_41,KAYAK_PIC_AQUATICS_78,ATM_WORD_SCREEN_1030],[PADDLEBOARD_PIC_AQUATICS_78,EPICURE_WORD_FOODIE_726,FALLOUT_WORD_RADIATE_257],[BIRMAN_WORD_BREEDS_940,CURIE_WORD_RADIATE_257,GLUCAGON_WORD_HORMONES_259],[BUZZER_WORD_ALARM_1031,SURFBOARD_PIC_AQUATICS_78,E_READER_WORD_SCREEN_1030],[LIFE_RING_PIC_AQUATICS_78,GASTRIN_WORD_HORMONES_259,CAULDRON_WORD_ALCHEMY_445],[PASSWORD_WORD_CIPHER_208,WETSUIT_PIC_AQUATICS_78,CHIVALRY_WORD_KNIGHT_34],[MELODY_WORD_SINGING_1054,POTION_WORD_ALCHEMY_445,HARMONY_WORD_YINYANG_721],[ANGORA_WORD_BREEDS_940,TV_WORD_SCREEN_1030,DESTRIER_WORD_KNIGHT_34],[SAILBOAT_PIC_AQUATICS_78,HELMET_WORD_KNIGHT_34,HAMLET_WORD_WILLIAM_165],[ELECTRIC_CAR_PIC_CHARGER_41,DOVE_WORD_BIRDS_80,HERON_WORD_BIRDS_80],[BLUETOOTH_HEADPHONES_PIC_CHARGER_41,POWER_BANK_PIC_CHARGER_41,ROMEO_WORD_WILLIAM_165],[SIAMESE_WORD_BREEDS_940,DIGITAL_CAMERA_PIC_CHARGER_41,PERICLES_WORD_WILLIAM_165],[LIFE_JACKET_PIC_AQUATICS_78,TONER_WORD_SKINCARE_984,CLEANSER_WORD_SKINCARE_984],[DECODE_WORD_CIPHER_208,TEMPEST_WORD_WILLIAM_165,JULIET_WORD_WILLIAM_165],[GOURMET_WORD_FOODIE_726,RELIC_WORD_ARTIFACT_276,AMULET_WORD_ARTIFACT_276],[DRONE_PIC_CHARGER_41,ARMOR_WORD_KNIGHT_34],[GENE_WORD_GENETICS_1060,TOTEM_WORD_ARTIFACT_276,DJEMBE_WORD_DRUM_518],[BENGAL_WORD_BREEDS_940,TABLA_WORD_DRUM_518,GENOME_WORD_GENETICS_1060],[KEYWORD_WORD_CIPHER_208,HENRY_V_WORD_WILLIAM_165,OTHELLO_WORD_WILLIAM_165],[RUSH_WORD_ALARM_1031,DIVING_MASK_PIC_AQUATICS_78],[BEEP_WORD_ALARM_1031,SHIELD_WORD_KNIGHT_34],[LAPTOP_PIC_CHARGER_41,DNA_WORD_GENETICS_1060,PALACE_WORD_HOUSE_40],[SPHYNX_WORD_BREEDS_940,MANSION_WORD_HOUSE_40],[ENCODE_WORD_CIPHER_208,WEAPON_WORD_KNIGHT_34,MACBETH_WORD_WILLIAM_165]]</t>
+  </si>
+  <si>
+    <t>[PIC_AQUATICS_78,WORD_BREEDS_940,WORD_ALARM_1031,WORD_CIPHER_208,PIC_CHARGER_41,WORD_WILLIAM_165,WORD_SCREEN_1030,WORD_KNIGHT_34]</t>
+  </si>
+  <si>
+    <t>SORT_GAME_LEVE_29_BOARD_1</t>
+  </si>
+  <si>
+    <t>[1,4,9]</t>
+  </si>
+  <si>
+    <t>[[SYNERGY_WORD_YINYANG_721,CARBON_WORD_ELEMENTS_107,GASTRIN_WORD_HORMONES_259],[SILICON_WORD_ELEMENTS_107,SAUCE_PIC_BURGER_44,SYBARITE_WORD_FOODIE_726],[FROG_WORD_POND_830,TOMATO_PIC_BURGER_44,DISHES_WORD_FOODIE_726],[IODINE_WORD_ELEMENTS_107,HYDROGEN_WORD_ELEMENTS_107,TASTE_WORD_FOODIE_726],[CATFISH_PIC_WHISKERS_43,WALRUS_PIC_WHISKERS_43,MANTLE_WORD_EARTH_831],[HARMONY_WORD_YINYANG_721,ARIA_WORD_SINGING_1054,SOLOIST_WORD_SINGING_1054],[SERUM_WORD_SKINCARE_984,TIMBRE_WORD_SINGING_1054,PITCH_WORD_SINGING_1054],[CORTISOL_WORD_HORMONES_259,MELODY_WORD_SINGING_1054,DOVE_WORD_BIRDS_80],[DUALITY_WORD_YINYANG_721,GLUCAGON_WORD_HORMONES_259,INSULIN_WORD_HORMONES_259],[REED_WORD_POND_830,OWL_WORD_BIRDS_80,ROBIN_WORD_BIRDS_80],[CAT_PIC_WHISKERS_43,FINCH_WORD_BIRDS_80,TEXTURE_WORD_SKINCARE_984],[SQUIRREL_PIC_WHISKERS_43,AMULET_WORD_ARTIFACT_276,TOTEM_WORD_ARTIFACT_276],[PLATE_WORD_DISHWARE_829,INSIGNIA_WORD_ARTIFACT_276,HORSE_WORD_EQUIDAE_475],[SAUCER_WORD_DISHWARE_829,BEEF_PIC_BURGER_44,CHEESE_PIC_BURGER_44],[PHYSICS_WORD_LESSONS_94,BONGO_WORD_DRUM_518,DNA_WORD_GENETICS_1060],[NITROGEN_WORD_ELEMENTS_107,LION_PIC_WHISKERS_43,HEDONISM_WORD_FOODIE_726],[GOURMET_WORD_FOODIE_726,CRUST_WORD_EARTH_831],[OXYGEN_WORD_ELEMENTS_107,DOG_PIC_WHISKERS_43,CORE_WORD_EARTH_831],[LETTUCE_PIC_BURGER_44,BUN_PIC_BURGER_44,SEAL_PIC_WHISKERS_43],[BOWL_WORD_DISHWARE_829,SODIUM_WORD_ELEMENTS_107,OTTER_PIC_WHISKERS_43],[SULFUR_WORD_ELEMENTS_107,STOMACH_WORD_ORGANS_412,PANCREAS_WORD_ORGANS_412],[DUCK_WORD_POND_830,BIOLOGY_WORD_LESSONS_94,OSIRIS_WORD_PYRAMIDS_330],[SONG_WORD_SINGING_1054,CANTER_WORD_GAITS_810,CORE_WORD_EARTH_831],[CUP_WORD_DISHWARE_829,EPICURE_WORD_FOODIE_726],[ASHIKO_WORD_DRUM_518,MANTLE_WORD_EARTH_831]]</t>
+  </si>
+  <si>
+    <t>[WORD_DISHWARE_829,WORD_EARTH_831,WORD_POND_830,WORD_YINYANG_721,WORD_ELEMENTS_107,PIC_BURGER_44,PIC_WHISKERS_43,WORD_HORMONES_259,WORD_FOODIE_726]</t>
+  </si>
+  <si>
+    <t>SORT_GAME_LEVE_30_BOARD_1</t>
+  </si>
+  <si>
+    <t>[1,2,11]</t>
+  </si>
+  <si>
+    <t>[[VILLA_WORD_HOUSE_40,ARIA_WORD_SINGING_1054,MELODY_WORD_SINGING_1054],[MANSION_WORD_HOUSE_40,HUMMING_WORD_SINGING_1054,SOLOIST_WORD_SINGING_1054],[TABLA_WORD_DRUM_518,CHOIR_WORD_SINGING_1054,INSIGNIA_WORD_ARTIFACT_276],[CIRCLE_PIC_SHAPES_46,VULTURE_WORD_BIRDS_80,GENE_WORD_GENETICS_1060],[EAGLE_WORD_BIRDS_80,SWAN_WORD_BIRDS_80,CLEANSER_WORD_SKINCARE_984],[PALACE_WORD_HOUSE_40,SONG_WORD_SINGING_1054,PITCH_WORD_SINGING_1054],[OVAL_PIC_SHAPES_46,OWL_WORD_BIRDS_80,TEXTURE_WORD_SKINCARE_984],[HERON_WORD_BIRDS_80,DNA_WORD_GENETICS_1060,TONER_WORD_SKINCARE_984],[TIMBRE_WORD_SINGING_1054,PEPTIDES_WORD_SKINCARE_984,VASE_WORD_ARTIFACT_276],[PORES_WORD_SKINCARE_984,RELIC_WORD_ARTIFACT_276,SIGIL_WORD_ARTIFACT_276],[ESPRESSO_PIC_DRINKS_45,LUNGS_WORD_ORGANS_412,HEART_WORD_ORGANS_412],[ASHIKO_WORD_DRUM_518,BLADDER_WORD_ORGANS_412,STOMACH_WORD_ORGANS_412],[GENOME_WORD_GENETICS_1060,ROBIN_WORD_BIRDS_80,AMULET_WORD_ARTIFACT_276],[DJEMBE_WORD_DRUM_518,ALGEBRA_WORD_LESSONS_94,OSIRIS_WORD_PYRAMIDS_330],[SODA_PIC_DRINKS_45,RA_WORD_PYRAMIDS_330,TROT_WORD_GAITS_810],[BONGO_WORD_DRUM_518,CANTER_WORD_GAITS_810,HARNESS_WORD_CARRIAGE_800],[JUICE_PIC_DRINKS_45,CORE_WORD_EARTH_831,CRUST_WORD_EARTH_831],[SPLEEN_WORD_ORGANS_412,RAMPART_WORD_CASTLE_485,TOWER_WORD_CASTLE_485],[LEMONADE_PIC_DRINKS_45,RETINOL_WORD_SKINCARE_984,SERUM_WORD_SKINCARE_984],[TURRET_WORD_CASTLE_485,PARAPET_WORD_CASTLE_485,MOAT_WORD_CASTLE_485],[DOVE_WORD_BIRDS_80,COYOTE_WORD_CANINES_168,WOLF_WORD_CANINES_168],[SQUARE_PIC_SHAPES_46,DHOLE_WORD_CANINES_168,FRET_WORD_VIOLINS_845],[DUNGEON_WORD_CASTLE_485,PAGANINI_WORD_VIOLINS_845,MIX_WORD_CONCRETE_601],[HISTORY_WORD_LESSONS_94,TEETH_WORD_SAW_88,NOTCH_WORD_SAW_88],[FINCH_WORD_BIRDS_80,TOTEM_WORD_ARTIFACT_276,BLEMISH_WORD_SKINCARE_984]]</t>
+  </si>
+  <si>
+    <t>[WORD_SINGING_1054,PIC_SHAPES_46,WORD_DRUM_518,WORD_BIRDS_80,PIC_DRINKS_45,WORD_HOUSE_40,WORD_GENETICS_1060,WORD_SKINCARE_984,WORD_ARTIFACT_276]</t>
+  </si>
+  <si>
+    <t>SORT_GAME_LEVE_31_BOARD_1</t>
+  </si>
+  <si>
+    <t>[8,9]</t>
+  </si>
+  <si>
+    <t>[[OSIRIS_WORD_PYRAMIDS_330,PARAPET_WORD_CASTLE_485,CITADEL_WORD_CASTLE_485],[LIVER_WORD_ORGANS_412,FOX_WORD_CANINES_168,COYOTE_WORD_CANINES_168],[CANTER_WORD_GAITS_810,HEART_WORD_ORGANS_412],[HARNESS_WORD_CARRIAGE_800,STOMACH_WORD_ORGANS_412],[ALGEBRA_WORD_LESSONS_94,PROTON_WORD_NUCLEAR_366,PAGANINI_WORD_VIOLINS_845],[BLADDER_WORD_ORGANS_412,BLADE_WORD_SAW_88,NOTCH_WORD_SAW_88],[CALCULUS_WORD_LESSONS_94,MACAQUE_WORD_PRIMATES_149,MANDRILL_WORD_PRIMATES_149],[GALLOP_WORD_GAITS_810,MARMOT_PIC_RODENTS_33,CLASSIC_HANDBAG_PIC_LUXURY_47],[CRUST_WORD_EARTH_831,BEAVER_PIC_RODENTS_33,SUPERCAR_PIC_LUXURY_47],[KIDNEY_WORD_ORGANS_412,GORILLA_WORD_PRIMATES_149],[BIOLOGY_WORD_LESSONS_94,SQL_WORD_CODING_150],[LUNGS_WORD_ORGANS_412,JAVA_WORD_CODING_150],[TROT_WORD_GAITS_810,PANCREAS_WORD_ORGANS_412],[YACHT_PIC_LUXURY_47,WATCH_PIC_LUXURY_47],[COACHMAN_WORD_CARRIAGE_800,PHP_WORD_CODING_150],[PHYSICS_WORD_LESSONS_94,PYTHON_WORD_CODING_150],[GEOMETRY_WORD_LESSONS_94,KANT_WORD_MINDS_82],[RA_WORD_PYRAMIDS_330,JEWELRY_PIC_LUXURY_47],[ANUBIS_WORD_PYRAMIDS_330,PRIVATE_JET_PIC_LUXURY_47],[RAMSES_WORD_PYRAMIDS_330,SOCRATES_WORD_MINDS_82],[CORE_WORD_EARTH_831,EXPENSE_WORD_FINANCE_227],[REINS_WORD_CARRIAGE_800,INCOME_WORD_FINANCE_227],[SQUIRREL_PIC_RODENTS_33,NUTRIA_PIC_RODENTS_33],[MANTLE_WORD_EARTH_831,SPLEEN_WORD_ORGANS_412],[HISTORY_WORD_LESSONS_94,VERB_WORD_GRAMMAR_861]]</t>
+  </si>
+  <si>
+    <t>[WORD_CARRIAGE_800,WORD_PYRAMIDS_330,WORD_EARTH_831,WORD_GAITS_810,PIC_RODENTS_33,WORD_ORGANS_412,PIC_LUXURY_47,WORD_LESSONS_94]</t>
+  </si>
+  <si>
+    <t>SORT_GAME_LEVE_32_BOARD_1</t>
+  </si>
+  <si>
+    <t>[3,4,7]</t>
+  </si>
+  <si>
+    <t>[[LEMUR_WORD_PRIMATES_149,TARSIER_WORD_PRIMATES_149,BABOON_WORD_PRIMATES_149],[ATOM_WORD_NUCLEAR_366,ROPE_PIC_SAILOR_50],[ELECTRON_WORD_NUCLEAR_366,SIMIAN_WORD_PRIMATES_149,PYTHON_WORD_CODING_150],[NOTCH_WORD_SAW_88,PHP_WORD_CODING_150,JAVA_WORD_CODING_150],[FRET_WORD_VIOLINS_845,SARTRE_WORD_MINDS_82,KANT_WORD_MINDS_82],[COWBOY_WORD_WESTERN_317,BANK_WORD_FINANCE_227,VERB_WORD_GRAMMAR_861],[BLADE_WORD_SAW_88,DHOLE_WORD_CANINES_168,FOX_WORD_CANINES_168],[BASTION_WORD_CASTLE_485,SALOON_WORD_WESTERN_317,RODEO_WORD_WESTERN_317],[MIX_WORD_CONCRETE_601,LASSO_WORD_WESTERN_317],[FOOL_WORD_TAROT_417,YALE_WORD_STUDIES_169],[MOAT_WORD_CASTLE_485,STROLLER_PIC_BABIES_49],[PARAPET_WORD_CASTLE_485,JACKAL_WORD_CANINES_168],[PAGANINI_WORD_VIOLINS_845,DIAPER_PIC_BABIES_49,PACIFIER_PIC_BABIES_49],[NEUTRON_WORD_NUCLEAR_366,CITADEL_WORD_CASTLE_485,CAR_SEAT_PIC_BABIES_49],[DUNGEON_WORD_CASTLE_485,KNOT_PIC_SAILOR_50,RATTLE_PIC_BABIES_49],[LUTHIER_WORD_VIOLINS_845,CRIB_PIC_BABIES_49],[RAMPART_WORD_CASTLE_485,STORM_PIC_SAILOR_50],[SCREED_WORD_CONCRETE_601,COYOTE_WORD_CANINES_168],[PROTON_WORD_NUCLEAR_366,FLAG_PIC_SAILOR_50,BABY_BOWL_AND_SOFT_TIP_SPOON_PIC_BABIES_49],[TOWER_WORD_CASTLE_485,DINGO_WORD_CANINES_168,BOTTLE_PIC_BABIES_49],[TOTEM_WORD_PAGANISM_469,SORBONNE_WORD_STUDIES_169],[TEETH_WORD_SAW_88,WOLF_WORD_CANINES_168],[STANFORD_WORD_STUDIES_169,RITUAL_WORD_PAGANISM_469],[TROWEL_WORD_CONCRETE_601,SRIRACHA_WORD_SPICY_136],[TURRET_WORD_CASTLE_485,YO_YO_WORD_TOYS_154]]</t>
+  </si>
+  <si>
+    <t>[WORD_SAW_88,WORD_VIOLINS_845,WORD_CONCRETE_601,WORD_NUCLEAR_366,WORD_CASTLE_485,PIC_BABIES_49,PIC_SAILOR_50,WORD_CANINES_168]</t>
+  </si>
+  <si>
+    <t>SORT_GAME_LEVE_33_BOARD_1</t>
+  </si>
+  <si>
+    <t>[3,4,9]</t>
+  </si>
+  <si>
+    <t>[[CIABATTA_WORD_BREADS_102,FOCACCIA_WORD_BREADS_102,RODEO_WORD_WESTERN_317],[BABOON_WORD_PRIMATES_149,SORBONNE_WORD_STUDIES_169,HARVARD_WORD_STUDIES_169],[DANTE_WORD_MINDS_82,IDOL_WORD_PAGANISM_469,RITUAL_WORD_PAGANISM_469],[GIBBON_WORD_PRIMATES_149,CHOCO_PIC_CANDY_51],[VIRGO_WORD_ZODIAC_59,ALTAR_WORD_PAGANISM_469,DOLL_WORD_TOYS_154],[VERB_WORD_GRAMMAR_861,YO_YO_WORD_TOYS_154,SPINNER_WORD_TOYS_154],[LEMUR_WORD_PRIMATES_149,PISCES_WORD_ZODIAC_59,GEMINI_WORD_ZODIAC_59],[MONEY_WORD_FINANCE_227,PORCINE_WORD_FAMILIES_234,AZURITE_WORD_MINERALS_253],[FUDGE_PIC_CANDY_51,GUM_PIC_CANDY_51],[TORTILLA_WORD_BREADS_102,GYPSUM_WORD_MINERALS_253,SHIRAZ_WORD_GRAPE_177],[MANDRILL_WORD_PRIMATES_149,CAR_PIC_KEYS_52],[LOLLIPOP_PIC_CANDY_51,INCOME_WORD_FINANCE_227,ETHERNET_WORD_NETWORK_588],[TARSIER_WORD_PRIMATES_149,GALILEO_WORD_MINDS_82],[SARTRE_WORD_MINDS_82,BUGS_WORD_CODING_150,SERVER_WORD_NETWORK_588],[SOCRATES_WORD_MINDS_82,PACKET_WORD_NETWORK_588,ROUTER_WORD_NETWORK_588],[PLATO_WORD_MINDS_82,JAVA_WORD_CODING_150],[ADVERB_WORD_GRAMMAR_861,GATEWAY_WORD_NETWORK_588,PYTHON_WORD_CODING_150],[GORILLA_WORD_PRIMATES_149,KANT_WORD_MINDS_82,SQL_WORD_CODING_150],[NOUN_WORD_GRAMMAR_861,EXPENSE_WORD_FINANCE_227,PHP_WORD_CODING_150],[SIMIAN_WORD_PRIMATES_149,SCRIPT_WORD_CODING_150,SWIFT_WORD_CODING_150],[SHERIFF_WORD_WESTERN_317,RIESLING_WORD_GRAPE_177,MUSCAT_WORD_GRAPE_177],[DOOR_PIC_KEYS_52,KETCHUP_WORD_HOT_DOG_201],[PADLOCK_PIC_KEYS_52,MEGA_WORD_PREFIX_922],[MACAQUE_WORD_PRIMATES_149,BANK_WORD_FINANCE_227,RUBY_WORD_CODING_150],[FOOL_WORD_TAROT_417,NANO_WORD_PREFIX_922]]</t>
+  </si>
+  <si>
+    <t>[PIC_CANDY_51,WORD_PRIMATES_149,PIC_KEYS_52,WORD_FINANCE_227,WORD_GRAMMAR_861,WORD_MINDS_82,WORD_NETWORK_588,WORD_CODING_150]</t>
+  </si>
+  <si>
+    <t>SORT_GAME_LEVE_34_BOARD_1</t>
+  </si>
+  <si>
+    <t>[2,7,9]</t>
+  </si>
+  <si>
+    <t>[[CUBE_PIC_3D_54,ARIES_WORD_ZODIAC_59,LIBRA_WORD_ZODIAC_59],[FOCACCIA_WORD_BREADS_102,BAGUETTE_WORD_BREADS_102,SORBONNE_WORD_STUDIES_169],[VIKINGS_WORD_CULTURES_487,TAURUS_WORD_ZODIAC_59,MURINE_WORD_FAMILIES_234],[WASABI_WORD_SPICY_136,GRASS_PIC_LAWN_53,RODEO_WORD_WESTERN_317],[MICA_WORD_MINERALS_253,CANINE_WORD_FAMILIES_234,OVINE_WORD_FAMILIES_234],[FOOL_WORD_TAROT_417,FRISBEE_PIC_LAWN_53,MIT_WORD_STUDIES_169],[BRIOCHE_WORD_BREADS_102,MOWER_PIC_LAWN_53,OXFORD_WORD_STUDIES_169],[EMPRESS_WORD_TAROT_417,PICNIC_BLANKET_PIC_LAWN_53],[YO_YO_WORD_TOYS_154,FOUR_LEAF_CLOVER_PIC_LAWN_53,SALOON_WORD_WESTERN_317],[CHALLAH_WORD_BREADS_102,MOON_WORD_TAROT_417,IDOL_WORD_PAGANISM_469],[TORTILLA_WORD_BREADS_102,MERLOT_WORD_GRAPE_177,GRENACHE_WORD_GRAPE_177],[DOLL_WORD_TOYS_154,COWBOY_WORD_WESTERN_317],[SPINNER_WORD_TOYS_154,SHIRAZ_WORD_GRAPE_177,RIESLING_WORD_GRAPE_177],[CONE_PIC_3D_54,GAMBLER_WORD_WESTERN_317,LASSO_WORD_WESTERN_317],[GARDENING_GLOVES_PIC_LAWN_53,STADIUM_WORD_BUILD_384,HOSPITAL_WORD_BUILD_384],[MAGICIAN_WORD_TAROT_417,SCHOOL_BUILDING_WORD_BUILD_384,LIBRARY_WORD_BUILD_384],[SPRINKLER_PIC_LAWN_53,YALE_WORD_STUDIES_169,STANFORD_WORD_STUDIES_169],[MUSEUM_WORD_BUILD_384,PORCINI_WORD_MUSHROOM_178,TRUFFLE_WORD_MUSHROOM_178],[PITA_WORD_BREADS_102,HABANERO_WORD_SPICY_136,ALTAR_WORD_PAGANISM_469],[SRIRACHA_WORD_SPICY_136,ENOKI_WORD_MUSHROOM_178,CELTS_WORD_CULTURES_487],[AREPA_WORD_BREADS_102,AZTECS_WORD_CULTURES_487,MAYANS_WORD_CULTURES_487],[LEAF_RAKE_PIC_LAWN_53,SHERIFF_WORD_WESTERN_317,HARVARD_WORD_STUDIES_169],[CIABATTA_WORD_BREADS_102,PRODUCE_WORD_INDUSTRY_921,PACIFIER_WORD_TODDLER_231],[SPHERE_PIC_3D_54,TOTEM_WORD_PAGANISM_469,RITUAL_WORD_PAGANISM_469],[GREEKS_WORD_CULTURES_487,PLAYPEN_WORD_TODDLER_231]]</t>
+  </si>
+  <si>
+    <t>[WORD_TOYS_154,PIC_LAWN_53,WORD_BREADS_102,PIC_3D_54,WORD_TAROT_417,WORD_WESTERN_317,WORD_SPICY_136,WORD_PAGANISM_469,WORD_STUDIES_169]</t>
+  </si>
+  <si>
+    <t>SORT_GAME_LEVE_35_BOARD_1</t>
+  </si>
+  <si>
+    <t>[3,10,11]</t>
+  </si>
+  <si>
+    <t>[[BIG_BEN_PIC_LANDMARK_56,MARBLE_WORD_MINERALS_253,BUTANE_WORD_ALKANES_641],[MICA_WORD_MINERALS_253,FACTORY_WORD_BUILD_384,LIBRARY_WORD_BUILD_384],[PORCINI_WORD_MUSHROOM_178,STADIUM_WORD_BUILD_384,RUSSULA_WORD_MUSHROOM_178],[MUSCAT_WORD_GRAPE_177,ROMANS_WORD_CULTURES_487,CELTS_WORD_CULTURES_487],[BERYL_WORD_MINERALS_253,GEMINI_WORD_ZODIAC_59,PROPANE_WORD_ALKANES_641],[LEO_WORD_ZODIAC_59,MAYANS_WORD_CULTURES_487,VIKINGS_WORD_CULTURES_487],[LIME_WORD_MINERALS_253,VIRGO_WORD_ZODIAC_59,EQUINE_WORD_FAMILIES_234],[STATUE_OF_LIBERTY_PIC_LANDMARK_56,CLARINET_WORD_VIOLIN_508,PRODUCE_WORD_INDUSTRY_921],[HOSPITAL_WORD_BUILD_384,NAP_TIME_WORD_TODDLER_231,PACIFIER_WORD_TODDLER_231],[GYPSUM_WORD_MINERALS_253,COFFIN_PIC_VAMPIRE_55,SOFT_BUN_WORD_HOT_DOG_201],[GRENACHE_WORD_GRAPE_177,METHANE_WORD_ALKANES_641,OVINE_WORD_FAMILIES_234],[MERLOT_WORD_GRAPE_177,PORCINE_WORD_FAMILIES_234,ETHANE_WORD_ALKANES_641],[MEGA_WORD_PREFIX_922,SCORPIO_WORD_ZODIAC_59,TAURUS_WORD_ZODIAC_59],[MALBEC_WORD_GRAPE_177,KETCHUP_WORD_HOT_DOG_201,FELINE_WORD_FAMILIES_234],[SHIRAZ_WORD_GRAPE_177,PISCES_WORD_ZODIAC_59,CANINE_WORD_FAMILIES_234],[AZURITE_WORD_MINERALS_253,BRASS_WORD_ALLOY_264,ALNICO_WORD_ALLOY_264],[DECA_WORD_PREFIX_922,NICHROME_WORD_ALLOY_264,BRONZE_WORD_ALLOY_264],[NANO_WORD_PREFIX_922,CHEDDAR_WORD_CHEESE_108,BRIE_WORD_CHEESE_108],[CALCITE_WORD_MINERALS_253,FANGS_PIC_VAMPIRE_55,BOVINE_WORD_FAMILIES_234],[RIESLING_WORD_GRAPE_177,CAPRINE_WORD_FAMILIES_234,ARIES_WORD_ZODIAC_59],[QUARTZ_WORD_MINERALS_253,PARMESAN_WORD_CHEESE_108,ENVELOPE_WORD_MAILMAN_63],[COLOSSEUM_PIC_LANDMARK_56,MAIL_WORD_MAILMAN_63,LETTER_WORD_MAILMAN_63],[LIBRA_WORD_ZODIAC_59,DIALOGUE_WORD_SPEAK_244,CURLY_WORD_HAIR_245],[GARLIC_PIC_VAMPIRE_55,COILY_WORD_HAIR_245,COUGH_WORD_FLU_251],[BATS_PIC_VAMPIRE_55,SAUSAGE_WORD_HOT_DOG_201,MURINE_WORD_FAMILIES_234]]</t>
+  </si>
+  <si>
+    <t>[WORD_MINERALS_253,WORD_PREFIX_922,WORD_GRAPE_177,PIC_VAMPIRE_55,PIC_LANDMARK_56,WORD_ZODIAC_59,WORD_FAMILIES_234,WORD_ALKANES_641,WORD_HOT_DOG_201]</t>
+  </si>
+  <si>
+    <t>SORT_GAME_LEVE_36_BOARD_1</t>
+  </si>
+  <si>
+    <t>[1,2,3]</t>
+  </si>
+  <si>
+    <t>[[ENOKI_WORD_MUSHROOM_178,TRUFFLE_WORD_MUSHROOM_178],[FACTORY_WORD_BUILD_384,MALL_WORD_BUILD_384],[LIBRARY_WORD_BUILD_384,MUSEUM_WORD_BUILD_384],[SCHOOL_BUILDING_WORD_BUILD_384,MAYANS_WORD_CULTURES_487],[SPHINX_PIC_EGYPT_37,VIKINGS_WORD_CULTURES_487],[SHIITAKE_WORD_MUSHROOM_178,GOODS_WORD_INDUSTRY_921],[HOTEL_WORD_BUILD_384,DUNES_PIC_DESERT_57],[FLUTE_WORD_VIOLIN_508,PACIFIER_WORD_TODDLER_231,PRODUCE_WORD_INDUSTRY_921],[AMANITA_WORD_MUSHROOM_178,CACTI_PIC_DESERT_57],[CELLO_WORD_VIOLIN_508,STEEL_WORD_INDUSTRY_921,GREEKS_WORD_CULTURES_487],[HOSPITAL_WORD_BUILD_384,NAP_TIME_WORD_TODDLER_231,AZTECS_WORD_CULTURES_487],[PHARAOH_S_MASK_PIC_EGYPT_37,CAMEL_PIC_DESERT_57],[STADIUM_WORD_BUILD_384,PLAYPEN_WORD_TODDLER_231],[OBOE_WORD_VIOLIN_508,ROMANS_WORD_CULTURES_487,OASIS_PIC_DESERT_57],[PORCINI_WORD_MUSHROOM_178,CELTS_WORD_CULTURES_487],[DOCTOR_WORD_JOBS_42,TUNGSTEN_WORD_ALLOY_264,NITINOL_WORD_ALLOY_264],[WAVY_WORD_HAIR_245,BRONZE_WORD_ALLOY_264,DORBLU_WORD_CHEESE_108],[PYRAMID_PIC_EGYPT_37,EDAM_WORD_CHEESE_108,MAIL_WORD_MAILMAN_63],[AMALGAM_WORD_ALLOY_264,STAMP_WORD_MAILMAN_63],[RUSSULA_WORD_MUSHROOM_178,NURSE_WORD_JOBS_42],[CLARINET_WORD_VIOLIN_508,OSLO_WORD_CAPITALS_119],[RIYADH_WORD_CAPITALS_119,PRAGUE_WORD_CAPITALS_119],[ALGEBRA_WORD_LESSONS_94,GEOMETRY_WORD_LESSONS_94],[BRASS_WORD_ALLOY_264,KINGDOM_WORD_MEDIEVAL_228],[RETINA_WORD_EYE_260,DIG_WORD_SHOVEL_261]]</t>
+  </si>
+  <si>
+    <t>[WORD_VIOLIN_508,PIC_EGYPT_37,WORD_MUSHROOM_178,WORD_BUILD_384,WORD_TODDLER_231,WORD_CULTURES_487,WORD_INDUSTRY_921,PIC_DESERT_57]</t>
+  </si>
+  <si>
+    <t>SORT_GAME_LEVE_37_BOARD_1</t>
+  </si>
+  <si>
+    <t>[5,9,11]</t>
+  </si>
+  <si>
+    <t>[[COUGH_WORD_FLU_251,AMALGAM_WORD_ALLOY_264,RUG_PIC_DECOR_77],[DOG_WORD_PETS_2,GAS_WORD_PHASE_57,RIYADH_WORD_CAPITALS_119],[RICOTTA_WORD_CHEESE_108,CAIRO_WORD_CAPITALS_119,MADRID_WORD_CAPITALS_119],[PILLS_WORD_FLU_251,BRONZE_WORD_ALLOY_264],[OPAL_WORD_GEMSTONE_186,KENNEDY_WORD_DYNASTY_991,IRIS_WORD_EYE_260],[GOUDA_WORD_CHEESE_108,DIG_WORD_SHOVEL_261,EXCAVATE_WORD_SHOVEL_261],[DORBLU_WORD_CHEESE_108,BRASS_WORD_ALLOY_264,DEBATE_WORD_SPEAK_244],[ATHENS_WORD_CAPITALS_119,JAPAN_WORD_MAP_32,SAPPHIRE_WORD_GEMSTONE_186],[STELLITE_WORD_ALLOY_264,TUNGSTEN_WORD_ALLOY_264],[PARMESAN_WORD_CHEESE_108,AGATE_WORD_GEMSTONE_186,CORTEX_WORD_AI_238],[SEAL_WORD_MAILMAN_63,CHATBOT_WORD_AI_238,AGENT_WORD_AI_238],[STAMP_WORD_MAILMAN_63,MATRIX_WORD_AI_238],[HEADACHE_WORD_FLU_251,NITINOL_WORD_ALLOY_264],[LETTER_WORD_MAILMAN_63,ARGUMENT_WORD_SPEAK_244,EGGPLANT_PIC_PURPLE_59],[NICHROME_WORD_ALLOY_264,SIRIUS_WORD_STARS_236],[MAIL_WORD_MAILMAN_63,POLARIS_WORD_STARS_236],[ENVELOPE_WORD_MAILMAN_63,ALTAIR_WORD_STARS_236],[FETA_WORD_CHEESE_108,SAUCE_WORD_BURGER_8],[ALNICO_WORD_ALLOY_264,VIOLET_PIC_PURPLE_59],[INK_WORD_MAILMAN_63,DETAINEE_WORD_PRISONER_312],[COILY_WORD_HAIR_245,PHOTO_FRAME_PIC_DECOR_77],[CHEDDAR_WORD_CHEESE_108,EDAM_WORD_CHEESE_108,VASE_PIC_DECOR_77],[WAVY_WORD_HAIR_245,WALL_CLOCK_PIC_DECOR_77],[BRIE_WORD_CHEESE_108,LAVENDER_PIC_PURPLE_59,PLUM_PIC_PURPLE_59],[CURLY_WORD_HAIR_245,DIALOGUE_WORD_SPEAK_244]]</t>
+  </si>
+  <si>
+    <t>[WORD_MAILMAN_63,WORD_FLU_251,WORD_ALLOY_264,WORD_HAIR_245,WORD_CHEESE_108,PIC_PURPLE_59,WORD_SPEAK_244,PIC_DECOR_77]</t>
+  </si>
+  <si>
+    <t>SORT_GAME_LEVE_38_BOARD_1</t>
+  </si>
+  <si>
+    <t>[3,5,6]</t>
+  </si>
+  <si>
+    <t>[[KETTLEBELL_PIC_GYM_62,PUDDLE_PIC_RAIN_61],[PLASMA_WORD_DISPLAY_486,SATURN_WORD_PLANET_90,SAPPHIRE_WORD_GEMSTONE_186],[EARTH_WORD_PLANET_90,TOPAZ_WORD_GEMSTONE_186,OPAL_WORD_GEMSTONE_186],[RETINA_WORD_EYE_260,CORTEX_WORD_AI_238,ALTAIR_WORD_STARS_236],[LIGHTNING_PIC_RAIN_61,PARROT_WORD_PETS_2,HAMSTER_WORD_PETS_2],[ROME_WORD_CAPITALS_119,UMBRELLA_PIC_RAIN_61,KINGDOM_WORD_MEDIEVAL_228],[DIAMOND_WORD_GEMSTONE_186,CHEESE_WORD_BURGER_8,SAUCE_WORD_BURGER_8],[CLOUD_PIC_RAIN_61,BEEF_WORD_BURGER_8,FELON_WORD_PRISONER_312],[UNEARTH_WORD_SHOVEL_261,DETAINEE_WORD_PRISONER_312,NEBULA_WORD_SPACE_314],[INMATE_WORD_PRISONER_312,YTTRIUM_WORD_METAL_272,LUTETIUM_WORD_METAL_272],[BARBELL_PIC_GYM_62,NURSE_WORD_JOBS_42,ENGINEER_WORD_JOBS_42],[OSLO_WORD_CAPITALS_119,ROMANOV_WORD_DYNASTY_991],[RAINCOAT_PIC_RAIN_61,LORD_WORD_MEDIEVAL_228,KENNEDY_WORD_DYNASTY_991],[MADRID_WORD_CAPITALS_119,CAIRO_WORD_CAPITALS_119,PILOT_WORD_JOBS_42],[TREADMILL_PIC_GYM_62,RIYADH_WORD_CAPITALS_119,KNIGHT_WORD_MEDIEVAL_228],[CASTLE_WORD_MEDIEVAL_228,ACTOR_WORD_JOBS_42],[AIR_BIKE_PIC_GYM_62,THULIUM_WORD_METAL_272,LED_WORD_DISPLAY_486],[JOURNEY_WORD_MAPS_1022,AMOLED_WORD_DISPLAY_486],[DUMBBELL_PIC_GYM_62,JUICE_WORD_DRINKS_16],[RAIN_BOOTS_PIC_RAIN_61,OVERTURE_WORD_SYMPHONY_210],[IRIS_WORD_EYE_260,PRAGUE_WORD_CAPITALS_119,WELDER_WORD_JOBS_42],[EXCAVATE_WORD_SHOVEL_261,TUDOR_WORD_DYNASTY_991],[PUPIL_WORD_EYE_260,OTTAWA_WORD_CAPITALS_119,BOURBON_WORD_DYNASTY_991],[ATHENS_WORD_CAPITALS_119,DOCTOR_WORD_JOBS_42],[DIG_WORD_SHOVEL_261,MAILMAN_WORD_JOBS_42,PLUMBER_WORD_JOBS_42]]</t>
+  </si>
+  <si>
+    <t>[WORD_SHOVEL_261,WORD_EYE_260,PIC_GYM_62,PIC_RAIN_61,WORD_CAPITALS_119,WORD_MEDIEVAL_228,WORD_DYNASTY_991,WORD_JOBS_42]</t>
+  </si>
+  <si>
+    <t>SORT_GAME_LEVE_39_BOARD_1</t>
+  </si>
+  <si>
     <t>[3,7,12]</t>
   </si>
   <si>
-    <t>[[KINETIC_WORD_ENERGY_145,ORGAN_WORD_PLAY_223,PIANO_WORD_PLAY_223],[BALLAD_WORD_POETRY_440,ODE_WORD_POETRY_440,ARABICA_WORD_BEANS_219],[MULE_WORD_EQUIDAE_475,DRUM_WORD_PLAY_223,CELLO_WORD_PLAY_223],[MOTION_WORD_DYNAMICS_360,BORDER_WORD_CUSTOMS_592,EXPORT_WORD_CUSTOMS_592],[MUSTANG_WORD_EQUIDAE_475,HAIKU_WORD_POETRY_440,RUM_PIC_PIRATE_35],[NUCLEAR_WORD_ENERGY_145,DUTY_WORD_CUSTOMS_592,TEAM_WORD_ANAGRAM_511],[ATOM_WORD_PARTICLE_281,ROBUSTA_WORD_BEANS_219,SEAGULL_PIC_BEACH_36],[RHYME_WORD_RAP_151,MEAT_WORD_ANAGRAM_511,PICKAXE_WORD_SHAFT_331],[HORSE_WORD_EQUIDAE_475,BEACH_CHAIR_PIC_BEACH_36,JOLLY_ROGER_PIC_PIRATE_35],[ENGINE_WORD_PLANE_139,COCKPIT_WORD_PLANE_139,FLY_WORD_PLANE_139],[BUOY_PIC_BEACH_36,TREASURE_CHEST_PIC_PIRATE_35,WOODEN_SHIP_S_WHEEL_PIC_PIRATE_35],[PUNCH_WORD_RAP_151,CANNON_PIC_PIRATE_35],[SERPENT_WORD_CHIMERA_795,BAY_PIC_BEACH_36,SHELLS_PIC_BEACH_36],[SONNET_WORD_POETRY_440,EXCELSA_WORD_BEANS_219,WAVES_PIC_BEACH_36],[ACROSTIC_WORD_POETRY_440,LIBERICA_WORD_BEANS_219,SAND_PIC_BEACH_36],[PONY_WORD_EQUIDAE_475,FUSELAGE_WORD_PLANE_139,SEATBELT_WORD_PLANE_139],[NEUTRON_WORD_PARTICLE_281,PARROT_PIC_PIRATE_35],[LION_WORD_CHIMERA_795,WINGS_WORD_PLANE_139,RUDDER_WORD_PLANE_139],[VERSE_WORD_RAP_151,SPYGLASS_WORD_OPTICS_229,SOLAR_WORD_ENERGY_145],[LYRICS_WORD_RAP_151,THERMAL_WORD_ENERGY_145,DHARMA_WORD_ZEN_549],[DONKEY_WORD_EQUIDAE_475,CUTLASS_PIC_PIRATE_35],[ELECTRON_WORD_PARTICLE_281,TREASURE_MAP_PIC_PIRATE_35,BEACH_UMBRELLA_PIC_BEACH_36],[GOAT_WORD_CHIMERA_795,YOGA_WORD_ZEN_549,INERTIA_WORD_DYNAMICS_360],[ZEBRA_WORD_EQUIDAE_475,GOATEE_WORD_BEARDS_681],[FLUTE_WORD_PLAY_223,DUCKTAIL_WORD_BEARDS_681]]</t>
-  </si>
-  <si>
-    <t>[WORD_POETRY_440,WORD_EQUIDAE_475,WORD_PARTICLE_281,WORD_CHIMERA_795,WORD_RAP_151,PIC_BEACH_36,PIC_PIRATE_35,WORD_BEANS_219]</t>
-  </si>
-  <si>
-    <t>SORT_GAME_LEVE_26_BOARD_1</t>
-  </si>
-  <si>
-    <t>[3,7]</t>
-  </si>
-  <si>
-    <t>[[ALIEN_PIC_SPACE_38,SEATBELT_WORD_PLANE_139,MONOCLE_WORD_OPTICS_229],[EXPORT_WORD_CUSTOMS_592,UKULELE_WORD_PLAY_223],[NILE_RIVER_PIC_EGYPT_37,LENS_WORD_OPTICS_229,NUCLEAR_WORD_ENERGY_145],[UFO_PIC_SPACE_38,KINETIC_WORD_ENERGY_145,YOGA_WORD_ZEN_549],[PYRAMID_PIC_EGYPT_37,RINZAI_WORD_ZEN_549,MOTION_WORD_DYNAMICS_360],[PHARAOH_S_MASK_PIC_EGYPT_37,BALBO_WORD_BEARDS_681,OTHELLO_WORD_WILLIAM_165],[ROCKET_PIC_SPACE_38,SPHINX_PIC_EGYPT_37],[DUTY_WORD_CUSTOMS_592,ROMEO_WORD_WILLIAM_165],[ASTRONAUT_PIC_SPACE_38,MACBETH_WORD_WILLIAM_165],[ESTIMATE_WORD_EVALUATE_651,CHIVALRY_WORD_KNIGHT_34],[MOTH_WORD_INSECTS_25,SCARAB_PIC_EGYPT_37],[DRUM_WORD_PLAY_223,FLUTE_WORD_PLAY_223],[VIOLIN_WORD_PLAY_223,ORGAN_WORD_PLAY_223],[MOSQUITO_WORD_INSECTS_25,MEAT_WORD_ANAGRAM_511,TEAM_WORD_ANAGRAM_511],[GUITAR_WORD_PLAY_223,ANALYZE_WORD_EVALUATE_651],[DRAGONFLY_WORD_INSECTS_25,MINE_WORD_SHAFT_331],[WASP_WORD_INSECTS_25,CART_WORD_SHAFT_331],[CELLO_WORD_PLAY_223,BENGAL_WORD_BREEDS_940],[PIANO_WORD_PLAY_223,BIRMAN_WORD_BREEDS_940],[MUMMY_PIC_EGYPT_37,PASSWORD_WORD_CIPHER_208],[IMPORT_WORD_CUSTOMS_592,DECODE_WORD_CIPHER_208],[BORDER_WORD_CUSTOMS_592,MATE_WORD_ANAGRAM_511,PICKAXE_WORD_SHAFT_331],[ANT_WORD_INSECTS_25,DIVA_WORD_OPERA_760],[LADYBUG_WORD_INSECTS_25,ANARCHY_WORD_POLICIES_394],[ASSESS_WORD_EVALUATE_651,MONARCHY_WORD_POLICIES_394]]</t>
-  </si>
-  <si>
-    <t>[WORD_CUSTOMS_592,WORD_INSECTS_25,WORD_PLAY_223,PIC_EGYPT_37,WORD_EVALUATE_651,PIC_SPACE_38,WORD_ANAGRAM_511,WORD_SHAFT_331]</t>
-  </si>
-  <si>
-    <t>SORT_GAME_LEVE_27_BOARD_1</t>
-  </si>
-  <si>
-    <t>[6,8]</t>
-  </si>
-  <si>
-    <t>[[SAWFISH_PIC_SEA_FISH_39,INERTIA_WORD_DYNAMICS_360],[THERMAL_WORD_ENERGY_145,JULIET_WORD_WILLIAM_165,ROMEO_WORD_WILLIAM_165],[RINZAI_WORD_ZEN_549,VELOCITY_WORD_DYNAMICS_360],[GOATEE_WORD_BEARDS_681,HAMLET_WORD_WILLIAM_165,WEAPON_WORD_KNIGHT_34],[SPYGLASS_WORD_OPTICS_229,ARMOR_WORD_KNIGHT_34,CHIVALRY_WORD_KNIGHT_34],[KINETIC_WORD_ENERGY_145,AILERON_WORD_PLANE_139,SEATBELT_WORD_PLANE_139],[GLASSES_WORD_OPTICS_229,ANGORA_WORD_BREEDS_940,SPHYNX_WORD_BREEDS_940],[TUNA_PIC_SEA_FISH_39,CLOWNFISH_PIC_SEA_FISH_39,WINGS_WORD_PLANE_139],[SOLAR_WORD_ENERGY_145,DECODE_WORD_CIPHER_208,ACT_WORD_OPERA_760],[BALLOON_PIC_BIRTHDAY_40,DIVA_WORD_OPERA_760,TYRANNY_WORD_POLICIES_394],[BALBO_WORD_BEARDS_681,SHARK_PIC_SEA_FISH_39,COCKPIT_WORD_PLANE_139],[CAKE_PIC_BIRTHDAY_40,ANARCHY_WORD_POLICIES_394,OXYGEN_WORD_ELEMENTS_107],[BIRTHDAY_HAT_PIC_BIRTHDAY_40,RUDDER_WORD_PLANE_139],[CANDLE_PIC_BIRTHDAY_40,SODIUM_WORD_ELEMENTS_107,GOURMET_WORD_FOODIE_726],[YOGA_WORD_ZEN_549,HEDONISM_WORD_FOODIE_726],[DHARMA_WORD_ZEN_549,NUCLEAR_WORD_ENERGY_145],[MOTION_WORD_DYNAMICS_360,GLUCAGON_WORD_HORMONES_259],[BOX_PIC_BIRTHDAY_40,FLY_WORD_PLANE_139],[STINGRAY_PIC_SEA_FISH_39,GASTRIN_WORD_HORMONES_259],[COD_PIC_SEA_FISH_39,INSULIN_WORD_HORMONES_259],[CONFETTI_PIC_BIRTHDAY_40,ENGINE_WORD_PLANE_139],[MARLIN_PIC_SEA_FISH_39,INTEREST_WORD_MORTGAGE_595],[MONOCLE_WORD_OPTICS_229,FUSELAGE_WORD_PLANE_139,SARDINE_PIC_SEA_FISH_39],[LENS_WORD_OPTICS_229,PAYMENT_WORD_MORTGAGE_595],[DUCKTAIL_WORD_BEARDS_681,HARMONY_WORD_YINYANG_721]]</t>
-  </si>
-  <si>
-    <t>[WORD_ZEN_549,PIC_BIRTHDAY_40,WORD_BEARDS_681,WORD_DYNAMICS_360,WORD_ENERGY_145,WORD_OPTICS_229,PIC_SEA_FISH_39,WORD_PLANE_139]</t>
-  </si>
-  <si>
-    <t>SORT_GAME_LEVE_28_BOARD_1</t>
-  </si>
-  <si>
-    <t>[7,10,12]</t>
-  </si>
-  <si>
-    <t>[[ELECTRIC_TOOTHBRUSH_PIC_CHARGER_41,NITROGEN_WORD_ELEMENTS_107,TASTE_WORD_FOODIE_726],[SMARTWATCH_PIC_CHARGER_41,KAYAK_PIC_AQUATICS_78,ATM_WORD_SCREEN_1030],[PADDLEBOARD_PIC_AQUATICS_78,EPICURE_WORD_FOODIE_726,FALLOUT_WORD_RADIATE_257],[BIRMAN_WORD_BREEDS_940,CURIE_WORD_RADIATE_257,GLUCAGON_WORD_HORMONES_259],[BUZZER_WORD_ALARM_1031,SURFBOARD_PIC_AQUATICS_78,E_READER_WORD_SCREEN_1030],[LIFE_RING_PIC_AQUATICS_78,GASTRIN_WORD_HORMONES_259,CAULDRON_WORD_ALCHEMY_445],[PASSWORD_WORD_CIPHER_208,WETSUIT_PIC_AQUATICS_78,CHIVALRY_WORD_KNIGHT_34],[MELODY_WORD_SINGING_1054,POTION_WORD_ALCHEMY_445,HARMONY_WORD_YINYANG_721],[ANGORA_WORD_BREEDS_940,TV_WORD_SCREEN_1030,DESTRIER_WORD_KNIGHT_34],[SAILBOAT_PIC_AQUATICS_78,HELMET_WORD_KNIGHT_34,HAMLET_WORD_WILLIAM_165],[ELECTRIC_CAR_PIC_CHARGER_41,DOVE_WORD_BIRDS_80,HERON_WORD_BIRDS_80],[BLUETOOTH_HEADPHONES_PIC_CHARGER_41,POWER_BANK_PIC_CHARGER_41,ROMEO_WORD_WILLIAM_165],[SIAMESE_WORD_BREEDS_940,DIGITAL_CAMERA_PIC_CHARGER_41,PERICLES_WORD_WILLIAM_165],[LIFE_JACKET_PIC_AQUATICS_78,TONER_WORD_SKINCARE_984,CLEANSER_WORD_SKINCARE_984],[DECODE_WORD_CIPHER_208,TEMPEST_WORD_WILLIAM_165,JULIET_WORD_WILLIAM_165],[GOURMET_WORD_FOODIE_726,RELIC_WORD_ARTIFACT_276,AMULET_WORD_ARTIFACT_276],[DRONE_PIC_CHARGER_41,ARMOR_WORD_KNIGHT_34],[GENE_WORD_GENETICS_1060,TOTEM_WORD_ARTIFACT_276,DJEMBE_WORD_DRUM_518],[BENGAL_WORD_BREEDS_940,TABLA_WORD_DRUM_518,GENOME_WORD_GENETICS_1060],[KEYWORD_WORD_CIPHER_208,HENRY_V_WORD_WILLIAM_165,OTHELLO_WORD_WILLIAM_165],[RUSH_WORD_ALARM_1031,DIVING_MASK_PIC_AQUATICS_78],[BEEP_WORD_ALARM_1031,SHIELD_WORD_KNIGHT_34],[LAPTOP_PIC_CHARGER_41,DNA_WORD_GENETICS_1060,PALACE_WORD_HOUSE_40],[SPHYNX_WORD_BREEDS_940,MANSION_WORD_HOUSE_40],[ENCODE_WORD_CIPHER_208,WEAPON_WORD_KNIGHT_34,MACBETH_WORD_WILLIAM_165]]</t>
-  </si>
-  <si>
-    <t>[PIC_AQUATICS_78,WORD_BREEDS_940,WORD_ALARM_1031,WORD_CIPHER_208,PIC_CHARGER_41,WORD_WILLIAM_165,WORD_SCREEN_1030,WORD_KNIGHT_34]</t>
-  </si>
-  <si>
-    <t>SORT_GAME_LEVE_29_BOARD_1</t>
-  </si>
-  <si>
-    <t>[3,9,11]</t>
-  </si>
-  <si>
-    <t>[[HARMONY_WORD_YINYANG_721,CHEESE_PIC_BURGER_44,CATFISH_PIC_WHISKERS_43],[ELIXIR_WORD_ALCHEMY_445,CHOIR_WORD_SINGING_1054,PITCH_WORD_SINGING_1054],[INTEREST_WORD_MORTGAGE_595,ARIA_WORD_SINGING_1054,ROBIN_WORD_BIRDS_80],[SEAL_PIC_WHISKERS_43,BUN_PIC_BURGER_44,SQUIRREL_PIC_WHISKERS_43],[OXYGEN_WORD_ELEMENTS_107,SWAN_WORD_BIRDS_80,OWL_WORD_BIRDS_80],[RA_WORD_PYRAMIDS_330,RETINOL_WORD_SKINCARE_984,PORES_WORD_SKINCARE_984],[CORTISOL_WORD_HORMONES_259,SODIUM_WORD_ELEMENTS_107],[EAGLE_WORD_BIRDS_80,PEPTIDES_WORD_SKINCARE_984,VASE_WORD_ARTIFACT_276],[CURIE_WORD_RADIATE_257,HYDROGEN_WORD_ELEMENTS_107,LION_PIC_WHISKERS_43],[CAULDRON_WORD_ALCHEMY_445,DJEMBE_WORD_DRUM_518,TABLA_WORD_DRUM_518],[SULFUR_WORD_ELEMENTS_107,DOG_PIC_WHISKERS_43,LETTUCE_PIC_BURGER_44],[X_RAYS_WORD_RADIATE_257,HEDONISM_WORD_FOODIE_726,EPICURE_WORD_FOODIE_726],[DECAY_WORD_RADIATE_257,BEEF_PIC_BURGER_44,OTTER_PIC_WHISKERS_43],[INSULIN_WORD_HORMONES_259,SILICON_WORD_ELEMENTS_107,TASTE_WORD_FOODIE_726],[POTION_WORD_ALCHEMY_445,GOURMET_WORD_FOODIE_726,DISHES_WORD_FOODIE_726],[CARBON_WORD_ELEMENTS_107,DNA_WORD_GENETICS_1060,MANSION_WORD_HOUSE_40],[SAUCE_PIC_BURGER_44,VILLA_WORD_HOUSE_40,STOMACH_WORD_ORGANS_412],[PAYMENT_WORD_MORTGAGE_595,KIDNEY_WORD_ORGANS_412,HEART_WORD_ORGANS_412],[CAT_PIC_WHISKERS_43,TOMATO_PIC_BURGER_44,SYBARITE_WORD_FOODIE_726],[DUALITY_WORD_YINYANG_721,LIVER_WORD_ORGANS_412,GEOMETRY_WORD_LESSONS_94],[GLUCAGON_WORD_HORMONES_259,RAMSES_WORD_PYRAMIDS_330,TROT_WORD_GAITS_810],[SYNERGY_WORD_YINYANG_721,MANTLE_WORD_EARTH_831,CRUST_WORD_EARTH_831],[IODINE_WORD_ELEMENTS_107,CORE_WORD_EARTH_831],[RATE_WORD_MORTGAGE_595,GASTRIN_WORD_HORMONES_259],[FALLOUT_WORD_RADIATE_257,NITROGEN_WORD_ELEMENTS_107,WALRUS_PIC_WHISKERS_43]]</t>
-  </si>
-  <si>
-    <t>[WORD_RADIATE_257,WORD_ALCHEMY_445,WORD_MORTGAGE_595,WORD_YINYANG_721,WORD_ELEMENTS_107,PIC_BURGER_44,PIC_WHISKERS_43,WORD_HORMONES_259,WORD_FOODIE_726]</t>
-  </si>
-  <si>
-    <t>SORT_GAME_LEVE_30_BOARD_1</t>
-  </si>
-  <si>
-    <t>[1,2,11]</t>
-  </si>
-  <si>
-    <t>[[VILLA_WORD_HOUSE_40,ARIA_WORD_SINGING_1054,MELODY_WORD_SINGING_1054],[MANSION_WORD_HOUSE_40,HUMMING_WORD_SINGING_1054,SOLOIST_WORD_SINGING_1054],[TABLA_WORD_DRUM_518,CHOIR_WORD_SINGING_1054,INSIGNIA_WORD_ARTIFACT_276],[CIRCLE_PIC_SHAPES_46,VULTURE_WORD_BIRDS_80,GENE_WORD_GENETICS_1060],[EAGLE_WORD_BIRDS_80,SWAN_WORD_BIRDS_80,CLEANSER_WORD_SKINCARE_984],[PALACE_WORD_HOUSE_40,SONG_WORD_SINGING_1054,PITCH_WORD_SINGING_1054],[OVAL_PIC_SHAPES_46,OWL_WORD_BIRDS_80,TEXTURE_WORD_SKINCARE_984],[HERON_WORD_BIRDS_80,DNA_WORD_GENETICS_1060,TONER_WORD_SKINCARE_984],[TIMBRE_WORD_SINGING_1054,PEPTIDES_WORD_SKINCARE_984,VASE_WORD_ARTIFACT_276],[PORES_WORD_SKINCARE_984,RELIC_WORD_ARTIFACT_276,SIGIL_WORD_ARTIFACT_276],[ESPRESSO_PIC_DRINKS_45,LUNGS_WORD_ORGANS_412,HEART_WORD_ORGANS_412],[ASHIKO_WORD_DRUM_518,BLADDER_WORD_ORGANS_412,STOMACH_WORD_ORGANS_412],[GENOME_WORD_GENETICS_1060,ROBIN_WORD_BIRDS_80,AMULET_WORD_ARTIFACT_276],[DJEMBE_WORD_DRUM_518,ALGEBRA_WORD_LESSONS_94,OSIRIS_WORD_PYRAMIDS_330],[SODA_PIC_DRINKS_45,RA_WORD_PYRAMIDS_330,TROT_WORD_GAITS_810],[BONGO_WORD_DRUM_518,CANTER_WORD_GAITS_810,HARNESS_WORD_CARRIAGE_800],[JUICE_PIC_DRINKS_45,CORE_WORD_EARTH_831,CRUST_WORD_EARTH_831],[SPLEEN_WORD_ORGANS_412,RAMPART_WORD_CASTLE_485,TOWER_WORD_CASTLE_485],[LEMONADE_PIC_DRINKS_45,RETINOL_WORD_SKINCARE_984,SERUM_WORD_SKINCARE_984],[TURRET_WORD_CASTLE_485,PARAPET_WORD_CASTLE_485,MOAT_WORD_CASTLE_485],[DOVE_WORD_BIRDS_80,COYOTE_WORD_CANINES_168,WOLF_WORD_CANINES_168],[SQUARE_PIC_SHAPES_46,DHOLE_WORD_CANINES_168,FRET_WORD_VIOLINS_845],[DUNGEON_WORD_CASTLE_485,PAGANINI_WORD_VIOLINS_845,MIX_WORD_CONCRETE_601],[HISTORY_WORD_LESSONS_94,TEETH_WORD_SAW_88,NOTCH_WORD_SAW_88],[FINCH_WORD_BIRDS_80,TOTEM_WORD_ARTIFACT_276,BLEMISH_WORD_SKINCARE_984]]</t>
-  </si>
-  <si>
-    <t>[WORD_SINGING_1054,PIC_SHAPES_46,WORD_DRUM_518,WORD_BIRDS_80,PIC_DRINKS_45,WORD_HOUSE_40,WORD_GENETICS_1060,WORD_SKINCARE_984,WORD_ARTIFACT_276]</t>
-  </si>
-  <si>
-    <t>SORT_GAME_LEVE_31_BOARD_1</t>
-  </si>
-  <si>
-    <t>[1,11]</t>
-  </si>
-  <si>
-    <t>[[CORE_WORD_EARTH_831,FOOL_PIC_TAROT_48],[CANTER_WORD_GAITS_810,MAGICIAN_PIC_TAROT_48,JEWELRY_PIC_LUXURY_47],[GEOMETRY_WORD_LESSONS_94,MOON_PIC_TAROT_48],[WATCH_PIC_LUXURY_47,CLASSIC_HANDBAG_PIC_LUXURY_47],[MANTLE_WORD_EARTH_831,PRIVATE_JET_PIC_LUXURY_47],[RA_WORD_PYRAMIDS_330,DUNGEON_WORD_CASTLE_485,MOAT_WORD_CASTLE_485],[COACHMAN_WORD_CARRIAGE_800,BLADDER_WORD_ORGANS_412],[CRUST_WORD_EARTH_831,DINGO_WORD_CANINES_168,JACKAL_WORD_CANINES_168],[ALGEBRA_WORD_LESSONS_94,PROTON_WORD_NUCLEAR_366,ATOM_WORD_NUCLEAR_366],[HEART_WORD_ORGANS_412,FRET_WORD_VIOLINS_845,PAGANINI_WORD_VIOLINS_845],[BIOLOGY_WORD_LESSONS_94,NOTCH_WORD_SAW_88,TEETH_WORD_SAW_88],[LIVER_WORD_ORGANS_412,TARSIER_WORD_PRIMATES_149],[OSIRIS_WORD_PYRAMIDS_330,SPLEEN_WORD_ORGANS_412],[HISTORY_WORD_LESSONS_94,BUGS_WORD_CODING_150],[RAMSES_WORD_PYRAMIDS_330,PYTHON_WORD_CODING_150],[CALCULUS_WORD_LESSONS_94,DANTE_WORD_MINDS_82],[GALLOP_WORD_GAITS_810,GATEWAY_WORD_NETWORK_588],[HARNESS_WORD_CARRIAGE_800,SERVER_WORD_NETWORK_588],[STOMACH_WORD_ORGANS_412,PANCREAS_WORD_ORGANS_412,YACHT_PIC_LUXURY_47],[ANUBIS_WORD_PYRAMIDS_330,INCOME_WORD_FINANCE_227],[PHYSICS_WORD_LESSONS_94,EXPENSE_WORD_FINANCE_227],[TROT_WORD_GAITS_810,VERB_WORD_GRAMMAR_861],[REINS_WORD_CARRIAGE_800,KIDNEY_WORD_ORGANS_412],[EMPRESS_PIC_TAROT_48,ADVERB_WORD_GRAMMAR_861],[LUNGS_WORD_ORGANS_412,SUPERCAR_PIC_LUXURY_47]]</t>
-  </si>
-  <si>
-    <t>[WORD_CARRIAGE_800,WORD_PYRAMIDS_330,WORD_EARTH_831,WORD_GAITS_810,PIC_TAROT_48,WORD_ORGANS_412,PIC_LUXURY_47,WORD_LESSONS_94]</t>
-  </si>
-  <si>
-    <t>SORT_GAME_LEVE_32_BOARD_1</t>
-  </si>
-  <si>
-    <t>[3,4,7]</t>
-  </si>
-  <si>
-    <t>[[LEMUR_WORD_PRIMATES_149,TARSIER_WORD_PRIMATES_149,BABOON_WORD_PRIMATES_149],[ATOM_WORD_NUCLEAR_366,ROPE_PIC_SAILOR_50],[ELECTRON_WORD_NUCLEAR_366,SIMIAN_WORD_PRIMATES_149,PYTHON_WORD_CODING_150],[NOTCH_WORD_SAW_88,PHP_WORD_CODING_150,JAVA_WORD_CODING_150],[FRET_WORD_VIOLINS_845,SARTRE_WORD_MINDS_82,KANT_WORD_MINDS_82],[COWBOY_WORD_WESTERN_317,BANK_WORD_FINANCE_227,VERB_WORD_GRAMMAR_861],[BLADE_WORD_SAW_88,DHOLE_WORD_CANINES_168,FOX_WORD_CANINES_168],[BASTION_WORD_CASTLE_485,SALOON_WORD_WESTERN_317,RODEO_WORD_WESTERN_317],[MIX_WORD_CONCRETE_601,LASSO_WORD_WESTERN_317],[FOOL_WORD_TAROT_417,YALE_WORD_STUDIES_169],[MOAT_WORD_CASTLE_485,STROLLER_PIC_BABIES_49],[PARAPET_WORD_CASTLE_485,JACKAL_WORD_CANINES_168],[PAGANINI_WORD_VIOLINS_845,DIAPER_PIC_BABIES_49,PACIFIER_PIC_BABIES_49],[NEUTRON_WORD_NUCLEAR_366,CITADEL_WORD_CASTLE_485,CAR_SEAT_PIC_BABIES_49],[DUNGEON_WORD_CASTLE_485,KNOT_PIC_SAILOR_50,RATTLE_PIC_BABIES_49],[LUTHIER_WORD_VIOLINS_845,CRIB_PIC_BABIES_49],[RAMPART_WORD_CASTLE_485,STORM_PIC_SAILOR_50],[SCREED_WORD_CONCRETE_601,COYOTE_WORD_CANINES_168],[PROTON_WORD_NUCLEAR_366,FLAG_PIC_SAILOR_50,BABY_BOWL_AND_SOFT_TIP_SPOON_PIC_BABIES_49],[TOWER_WORD_CASTLE_485,DINGO_WORD_CANINES_168,BOTTLE_PIC_BABIES_49],[TOTEM_WORD_PAGANISM_469,SORBONNE_WORD_STUDIES_169],[TEETH_WORD_SAW_88,WOLF_WORD_CANINES_168],[STANFORD_WORD_STUDIES_169,RITUAL_WORD_PAGANISM_469],[TROWEL_WORD_CONCRETE_601,SRIRACHA_WORD_SPICY_136],[TURRET_WORD_CASTLE_485,YO_YO_WORD_TOYS_154]]</t>
-  </si>
-  <si>
-    <t>[WORD_SAW_88,WORD_VIOLINS_845,WORD_CONCRETE_601,WORD_NUCLEAR_366,WORD_CASTLE_485,PIC_BABIES_49,PIC_SAILOR_50,WORD_CANINES_168]</t>
-  </si>
-  <si>
-    <t>SORT_GAME_LEVE_33_BOARD_1</t>
-  </si>
-  <si>
-    <t>[3,4,9]</t>
-  </si>
-  <si>
-    <t>[[CIABATTA_WORD_BREADS_102,FOCACCIA_WORD_BREADS_102,RODEO_WORD_WESTERN_317],[BABOON_WORD_PRIMATES_149,SORBONNE_WORD_STUDIES_169,HARVARD_WORD_STUDIES_169],[DANTE_WORD_MINDS_82,IDOL_WORD_PAGANISM_469,RITUAL_WORD_PAGANISM_469],[GIBBON_WORD_PRIMATES_149,CHOCO_PIC_CANDY_51],[VIRGO_WORD_ZODIAC_59,ALTAR_WORD_PAGANISM_469,DOLL_WORD_TOYS_154],[VERB_WORD_GRAMMAR_861,YO_YO_WORD_TOYS_154,SPINNER_WORD_TOYS_154],[LEMUR_WORD_PRIMATES_149,PISCES_WORD_ZODIAC_59,GEMINI_WORD_ZODIAC_59],[MONEY_WORD_FINANCE_227,PORCINE_WORD_FAMILIES_234,AZURITE_WORD_MINERALS_253],[FUDGE_PIC_CANDY_51,GUM_PIC_CANDY_51],[TORTILLA_WORD_BREADS_102,GYPSUM_WORD_MINERALS_253,SHIRAZ_WORD_GRAPE_177],[MANDRILL_WORD_PRIMATES_149,CAR_PIC_KEYS_52],[LOLLIPOP_PIC_CANDY_51,INCOME_WORD_FINANCE_227,ETHERNET_WORD_NETWORK_588],[TARSIER_WORD_PRIMATES_149,GALILEO_WORD_MINDS_82],[SARTRE_WORD_MINDS_82,BUGS_WORD_CODING_150,SERVER_WORD_NETWORK_588],[SOCRATES_WORD_MINDS_82,PACKET_WORD_NETWORK_588,ROUTER_WORD_NETWORK_588],[PLATO_WORD_MINDS_82,JAVA_WORD_CODING_150],[ADVERB_WORD_GRAMMAR_861,GATEWAY_WORD_NETWORK_588,PYTHON_WORD_CODING_150],[GORILLA_WORD_PRIMATES_149,KANT_WORD_MINDS_82,SQL_WORD_CODING_150],[NOUN_WORD_GRAMMAR_861,EXPENSE_WORD_FINANCE_227,PHP_WORD_CODING_150],[SIMIAN_WORD_PRIMATES_149,SCRIPT_WORD_CODING_150,SWIFT_WORD_CODING_150],[SHERIFF_WORD_WESTERN_317,RIESLING_WORD_GRAPE_177,MUSCAT_WORD_GRAPE_177],[DOOR_PIC_KEYS_52,KETCHUP_WORD_HOT_DOG_201],[PADLOCK_PIC_KEYS_52,MEGA_WORD_PREFIX_922],[MACAQUE_WORD_PRIMATES_149,BANK_WORD_FINANCE_227,RUBY_WORD_CODING_150],[FOOL_WORD_TAROT_417,NANO_WORD_PREFIX_922]]</t>
-  </si>
-  <si>
-    <t>[PIC_CANDY_51,WORD_PRIMATES_149,PIC_KEYS_52,WORD_FINANCE_227,WORD_GRAMMAR_861,WORD_MINDS_82,WORD_NETWORK_588,WORD_CODING_150]</t>
-  </si>
-  <si>
-    <t>SORT_GAME_LEVE_34_BOARD_1</t>
-  </si>
-  <si>
-    <t>[2,7,9]</t>
-  </si>
-  <si>
-    <t>[[CUBE_PIC_3D_54,ARIES_WORD_ZODIAC_59,LIBRA_WORD_ZODIAC_59],[FOCACCIA_WORD_BREADS_102,BAGUETTE_WORD_BREADS_102,SORBONNE_WORD_STUDIES_169],[VIKINGS_WORD_CULTURES_487,TAURUS_WORD_ZODIAC_59,MURINE_WORD_FAMILIES_234],[WASABI_WORD_SPICY_136,GRASS_PIC_LAWN_53,RODEO_WORD_WESTERN_317],[MICA_WORD_MINERALS_253,CANINE_WORD_FAMILIES_234,OVINE_WORD_FAMILIES_234],[FOOL_WORD_TAROT_417,FRISBEE_PIC_LAWN_53,MIT_WORD_STUDIES_169],[BRIOCHE_WORD_BREADS_102,MOWER_PIC_LAWN_53,OXFORD_WORD_STUDIES_169],[EMPRESS_WORD_TAROT_417,PICNIC_BLANKET_PIC_LAWN_53],[YO_YO_WORD_TOYS_154,FOUR_LEAF_CLOVER_PIC_LAWN_53,SALOON_WORD_WESTERN_317],[CHALLAH_WORD_BREADS_102,MOON_WORD_TAROT_417,IDOL_WORD_PAGANISM_469],[TORTILLA_WORD_BREADS_102,MERLOT_WORD_GRAPE_177,GRENACHE_WORD_GRAPE_177],[DOLL_WORD_TOYS_154,COWBOY_WORD_WESTERN_317],[SPINNER_WORD_TOYS_154,SHIRAZ_WORD_GRAPE_177,RIESLING_WORD_GRAPE_177],[CONE_PIC_3D_54,GAMBLER_WORD_WESTERN_317,LASSO_WORD_WESTERN_317],[GARDENING_GLOVES_PIC_LAWN_53,STADIUM_WORD_BUILD_384,HOSPITAL_WORD_BUILD_384],[MAGICIAN_WORD_TAROT_417,SCHOOL_BUILDING_WORD_BUILD_384,LIBRARY_WORD_BUILD_384],[SPRINKLER_PIC_LAWN_53,YALE_WORD_STUDIES_169,STANFORD_WORD_STUDIES_169],[MUSEUM_WORD_BUILD_384,PORCINI_WORD_MUSHROOM_178,TRUFFLE_WORD_MUSHROOM_178],[PITA_WORD_BREADS_102,HABANERO_WORD_SPICY_136,ALTAR_WORD_PAGANISM_469],[SRIRACHA_WORD_SPICY_136,ENOKI_WORD_MUSHROOM_178,CELTS_WORD_CULTURES_487],[AREPA_WORD_BREADS_102,AZTECS_WORD_CULTURES_487,MAYANS_WORD_CULTURES_487],[LEAF_RAKE_PIC_LAWN_53,SHERIFF_WORD_WESTERN_317,HARVARD_WORD_STUDIES_169],[CIABATTA_WORD_BREADS_102,PRODUCE_WORD_INDUSTRY_921,PACIFIER_WORD_TODDLER_231],[SPHERE_PIC_3D_54,TOTEM_WORD_PAGANISM_469,RITUAL_WORD_PAGANISM_469],[GREEKS_WORD_CULTURES_487,PLAYPEN_WORD_TODDLER_231]]</t>
-  </si>
-  <si>
-    <t>[WORD_TOYS_154,PIC_LAWN_53,WORD_BREADS_102,PIC_3D_54,WORD_TAROT_417,WORD_WESTERN_317,WORD_SPICY_136,WORD_PAGANISM_469,WORD_STUDIES_169]</t>
-  </si>
-  <si>
-    <t>SORT_GAME_LEVE_35_BOARD_1</t>
-  </si>
-  <si>
-    <t>[3,10,11]</t>
-  </si>
-  <si>
-    <t>[[BIG_BEN_PIC_LANDMARK_56,MARBLE_WORD_MINERALS_253,BUTANE_WORD_ALKANES_641],[MICA_WORD_MINERALS_253,FACTORY_WORD_BUILD_384,LIBRARY_WORD_BUILD_384],[PORCINI_WORD_MUSHROOM_178,STADIUM_WORD_BUILD_384,RUSSULA_WORD_MUSHROOM_178],[MUSCAT_WORD_GRAPE_177,ROMANS_WORD_CULTURES_487,CELTS_WORD_CULTURES_487],[BERYL_WORD_MINERALS_253,GEMINI_WORD_ZODIAC_59,PROPANE_WORD_ALKANES_641],[LEO_WORD_ZODIAC_59,MAYANS_WORD_CULTURES_487,VIKINGS_WORD_CULTURES_487],[LIME_WORD_MINERALS_253,VIRGO_WORD_ZODIAC_59,EQUINE_WORD_FAMILIES_234],[STATUE_OF_LIBERTY_PIC_LANDMARK_56,CLARINET_WORD_VIOLIN_508,PRODUCE_WORD_INDUSTRY_921],[HOSPITAL_WORD_BUILD_384,NAP_TIME_WORD_TODDLER_231,PACIFIER_WORD_TODDLER_231],[GYPSUM_WORD_MINERALS_253,COFFIN_PIC_VAMPIRE_55,SOFT_BUN_WORD_HOT_DOG_201],[GRENACHE_WORD_GRAPE_177,METHANE_WORD_ALKANES_641,OVINE_WORD_FAMILIES_234],[MERLOT_WORD_GRAPE_177,PORCINE_WORD_FAMILIES_234,ETHANE_WORD_ALKANES_641],[MEGA_WORD_PREFIX_922,SCORPIO_WORD_ZODIAC_59,TAURUS_WORD_ZODIAC_59],[MALBEC_WORD_GRAPE_177,KETCHUP_WORD_HOT_DOG_201,FELINE_WORD_FAMILIES_234],[SHIRAZ_WORD_GRAPE_177,PISCES_WORD_ZODIAC_59,CANINE_WORD_FAMILIES_234],[AZURITE_WORD_MINERALS_253,BRASS_WORD_ALLOY_264,ALNICO_WORD_ALLOY_264],[DECA_WORD_PREFIX_922,NICHROME_WORD_ALLOY_264,BRONZE_WORD_ALLOY_264],[NANO_WORD_PREFIX_922,CHEDDAR_WORD_CHEESE_108,BRIE_WORD_CHEESE_108],[CALCITE_WORD_MINERALS_253,FANGS_PIC_VAMPIRE_55,BOVINE_WORD_FAMILIES_234],[RIESLING_WORD_GRAPE_177,CAPRINE_WORD_FAMILIES_234,ARIES_WORD_ZODIAC_59],[QUARTZ_WORD_MINERALS_253,PARMESAN_WORD_CHEESE_108,ENVELOPE_WORD_MAILMAN_63],[COLOSSEUM_PIC_LANDMARK_56,MAIL_WORD_MAILMAN_63,LETTER_WORD_MAILMAN_63],[LIBRA_WORD_ZODIAC_59,DIALOGUE_WORD_SPEAK_244,CURLY_WORD_HAIR_245],[GARLIC_PIC_VAMPIRE_55,COILY_WORD_HAIR_245,COUGH_WORD_FLU_251],[BATS_PIC_VAMPIRE_55,SAUSAGE_WORD_HOT_DOG_201,MURINE_WORD_FAMILIES_234]]</t>
-  </si>
-  <si>
-    <t>[WORD_MINERALS_253,WORD_PREFIX_922,WORD_GRAPE_177,PIC_VAMPIRE_55,PIC_LANDMARK_56,WORD_ZODIAC_59,WORD_FAMILIES_234,WORD_ALKANES_641,WORD_HOT_DOG_201]</t>
-  </si>
-  <si>
-    <t>SORT_GAME_LEVE_36_BOARD_1</t>
-  </si>
-  <si>
-    <t>[1,3,10]</t>
-  </si>
-  <si>
-    <t>[[ENOKI_WORD_MUSHROOM_178,PORCINI_WORD_MUSHROOM_178,VIKINGS_WORD_CULTURES_487],[OBOE_WORD_VIOLIN_508,NAP_TIME_WORD_TODDLER_231],[TRUFFLE_WORD_MUSHROOM_178,CACTI_PIC_DESERT_57],[KITE_PIC_TOYS_58,OASIS_PIC_DESERT_57],[HOTEL_WORD_BUILD_384,ROMANS_WORD_CULTURES_487],[DEBATE_WORD_SPEAK_244,NITINOL_WORD_ALLOY_264,BRASS_WORD_ALLOY_264],[CLARINET_WORD_VIOLIN_508,PARMESAN_WORD_CHEESE_108,STAMP_WORD_MAILMAN_63],[STADIUM_WORD_BUILD_384,ACTOR_WORD_JOBS_42,DOCTOR_WORD_JOBS_42],[SHIITAKE_WORD_MUSHROOM_178,WELDER_WORD_JOBS_42,PLUMBER_WORD_JOBS_42],[LIBRARY_WORD_BUILD_384,MAYANS_WORD_CULTURES_487,DUNES_PIC_DESERT_57],[AMANITA_WORD_MUSHROOM_178,GOODS_WORD_INDUSTRY_921],[CELLO_WORD_VIOLIN_508,PLAYPEN_WORD_TODDLER_231],[SCHOOL_BUILDING_WORD_BUILD_384,AZTECS_WORD_CULTURES_487],[MUSEUM_WORD_BUILD_384,CELTS_WORD_CULTURES_487],[TEDDY_BEAR_PIC_TOYS_58,CAMEL_PIC_DESERT_57],[FLUTE_WORD_VIOLIN_508,PILOT_WORD_JOBS_42],[ATHENS_WORD_CAPITALS_119,MAILMAN_WORD_JOBS_42],[ALNICO_WORD_ALLOY_264,ENGINEER_WORD_JOBS_42],[RUSSULA_WORD_MUSHROOM_178,ROME_WORD_CAPITALS_119],[MALL_WORD_BUILD_384,GREEKS_WORD_CULTURES_487],[LEGO_PIC_TOYS_58,CAIRO_WORD_CAPITALS_119],[PACIFIER_WORD_TODDLER_231,TUDOR_WORD_DYNASTY_991],[HOSPITAL_WORD_BUILD_384,LORD_WORD_MEDIEVAL_228],[UNEARTH_WORD_SHOVEL_261,PUPIL_WORD_EYE_260],[FACTORY_WORD_BUILD_384,STEEL_WORD_INDUSTRY_921,PRODUCE_WORD_INDUSTRY_921]]</t>
-  </si>
-  <si>
-    <t>[WORD_VIOLIN_508,PIC_TOYS_58,WORD_MUSHROOM_178,WORD_BUILD_384,WORD_TODDLER_231,WORD_CULTURES_487,WORD_INDUSTRY_921,PIC_DESERT_57]</t>
-  </si>
-  <si>
-    <t>SORT_GAME_LEVE_37_BOARD_1</t>
-  </si>
-  <si>
-    <t>[4,8,9]</t>
-  </si>
-  <si>
-    <t>[[ALNICO_WORD_ALLOY_264,ENGINEER_WORD_JOBS_42,MADRID_WORD_CAPITALS_119],[RICOTTA_WORD_CHEESE_108,PRAGUE_WORD_CAPITALS_119,KENNEDY_WORD_DYNASTY_991],[MAIL_WORD_MAILMAN_63,SEAL_WORD_MAILMAN_63,LAVENDER_PIC_PURPLE_59],[NICHROME_WORD_ALLOY_264,TUNGSTEN_WORD_ALLOY_264],[PLUMBER_WORD_JOBS_42,ROMANOV_WORD_DYNASTY_991,DIG_WORD_SHOVEL_261],[BRASS_WORD_ALLOY_264,NEPTUNE_WORD_PLANET_90,VENUS_WORD_PLANET_90],[NURSE_WORD_JOBS_42,JUPITER_WORD_PLANET_90,URANUS_WORD_PLANET_90],[LETTER_WORD_MAILMAN_63,STELLITE_WORD_ALLOY_264,VIOLET_PIC_PURPLE_59],[EDAM_WORD_CHEESE_108,NITINOL_WORD_ALLOY_264],[COUGH_WORD_FLU_251,MERCURY_WORD_PLANET_90,DIAMOND_WORD_GEMSTONE_186],[COILY_WORD_HAIR_245,TOPAZ_WORD_GEMSTONE_186],[CAT_WORD_PETS_2,MATRIX_WORD_AI_238],[PILLS_WORD_FLU_251,AMALGAM_WORD_ALLOY_264],[ENVELOPE_WORD_MAILMAN_63,BRONZE_WORD_ALLOY_264],[EXCAVATE_WORD_SHOVEL_261,DATASET_WORD_AI_238],[STAMP_WORD_MAILMAN_63,EGGPLANT_PIC_PURPLE_59],[CURLY_WORD_HAIR_245,CHEESE_PIC_YELLOW_60,CORN_PIC_YELLOW_60],[PARMESAN_WORD_CHEESE_108,FETA_WORD_CHEESE_108],[CHEDDAR_WORD_CHEESE_108,BRIE_WORD_CHEESE_108],[DORBLU_WORD_CHEESE_108,DEBATE_WORD_SPEAK_244,PLUM_PIC_PURPLE_59],[GOUDA_WORD_CHEESE_108,CHEESE_WORD_BURGER_8],[RUBY_WORD_GEMSTONE_186,BEEF_WORD_BURGER_8],[HEADACHE_WORD_FLU_251,ARGUMENT_WORD_SPEAK_244,BANANA_PIC_YELLOW_60],[INK_WORD_MAILMAN_63,DIALOGUE_WORD_SPEAK_244,GOLD_PIC_YELLOW_60],[WAVY_WORD_HAIR_245,SAUCE_WORD_BURGER_8]]</t>
-  </si>
-  <si>
-    <t>[WORD_MAILMAN_63,WORD_FLU_251,WORD_ALLOY_264,WORD_HAIR_245,WORD_CHEESE_108,PIC_PURPLE_59,WORD_SPEAK_244,PIC_YELLOW_60]</t>
-  </si>
-  <si>
-    <t>SORT_GAME_LEVE_38_BOARD_1</t>
-  </si>
-  <si>
-    <t>[3,5,6]</t>
-  </si>
-  <si>
-    <t>[[KETTLEBELL_PIC_GYM_62,PUDDLE_PIC_RAIN_61],[PLASMA_WORD_DISPLAY_486,SATURN_WORD_PLANET_90,SAPPHIRE_WORD_GEMSTONE_186],[EARTH_WORD_PLANET_90,TOPAZ_WORD_GEMSTONE_186,OPAL_WORD_GEMSTONE_186],[RETINA_WORD_EYE_260,CORTEX_WORD_AI_238,ALTAIR_WORD_STARS_236],[LIGHTNING_PIC_RAIN_61,PARROT_WORD_PETS_2,HAMSTER_WORD_PETS_2],[ROME_WORD_CAPITALS_119,UMBRELLA_PIC_RAIN_61,KINGDOM_WORD_MEDIEVAL_228],[DIAMOND_WORD_GEMSTONE_186,CHEESE_WORD_BURGER_8,SAUCE_WORD_BURGER_8],[CLOUD_PIC_RAIN_61,BEEF_WORD_BURGER_8,FELON_WORD_PRISONER_312],[UNEARTH_WORD_SHOVEL_261,DETAINEE_WORD_PRISONER_312,NEBULA_WORD_SPACE_314],[INMATE_WORD_PRISONER_312,YTTRIUM_WORD_METAL_272,LUTETIUM_WORD_METAL_272],[BARBELL_PIC_GYM_62,NURSE_WORD_JOBS_42,ENGINEER_WORD_JOBS_42],[OSLO_WORD_CAPITALS_119,ROMANOV_WORD_DYNASTY_991],[RAINCOAT_PIC_RAIN_61,LORD_WORD_MEDIEVAL_228,KENNEDY_WORD_DYNASTY_991],[MADRID_WORD_CAPITALS_119,CAIRO_WORD_CAPITALS_119,PILOT_WORD_JOBS_42],[TREADMILL_PIC_GYM_62,RIYADH_WORD_CAPITALS_119,KNIGHT_WORD_MEDIEVAL_228],[CASTLE_WORD_MEDIEVAL_228,ACTOR_WORD_JOBS_42],[AIR_BIKE_PIC_GYM_62,THULIUM_WORD_METAL_272,LED_WORD_DISPLAY_486],[JOURNEY_WORD_MAPS_1022,AMOLED_WORD_DISPLAY_486],[DUMBBELL_PIC_GYM_62,JUICE_WORD_DRINKS_16],[RAIN_BOOTS_PIC_RAIN_61,OVERTURE_WORD_SYMPHONY_210],[IRIS_WORD_EYE_260,PRAGUE_WORD_CAPITALS_119,WELDER_WORD_JOBS_42],[EXCAVATE_WORD_SHOVEL_261,TUDOR_WORD_DYNASTY_991],[PUPIL_WORD_EYE_260,OTTAWA_WORD_CAPITALS_119,BOURBON_WORD_DYNASTY_991],[ATHENS_WORD_CAPITALS_119,DOCTOR_WORD_JOBS_42],[DIG_WORD_SHOVEL_261,MAILMAN_WORD_JOBS_42,PLUMBER_WORD_JOBS_42]]</t>
-  </si>
-  <si>
-    <t>[WORD_SHOVEL_261,WORD_EYE_260,PIC_GYM_62,PIC_RAIN_61,WORD_CAPITALS_119,WORD_MEDIEVAL_228,WORD_DYNASTY_991,WORD_JOBS_42]</t>
-  </si>
-  <si>
-    <t>SORT_GAME_LEVE_39_BOARD_1</t>
-  </si>
-  <si>
-    <t>[3,4,5]</t>
-  </si>
-  <si>
-    <t>[[DATASET_WORD_AI_238,JOURNEY_WORD_MAPS_1022,LANDMARK_WORD_MAPS_1022],[METEOR_WORD_SPACE_314,ATLAS_WORD_MAPS_1022,ASTEROID_WORD_SPACE_314],[PUPIL_WORD_EYE_260,NEBULA_WORD_SPACE_314,ECLIPSE_WORD_SPACE_314],[DOCTOR_WORD_JOBS_42,LUTETIUM_WORD_METAL_272,THULIUM_WORD_METAL_272],[ACTOR_WORD_JOBS_42,PLASMA_WORD_DISPLAY_486,OLED_WORD_DISPLAY_486],[NOVA_WORD_SPACE_314,LCD_WORD_DISPLAY_486,TRUSTY_WORD_LOCK_321],[SODA_WORD_DRINKS_16,PILOT_WORD_JOBS_42,PLUMBER_WORD_JOBS_42],[CORTEX_WORD_AI_238,MADRID_WORD_CAPITALS_119,TUDOR_WORD_DYNASTY_991],[LED_WORD_DISPLAY_486,LORD_WORD_MEDIEVAL_228,IRIS_WORD_EYE_260],[STURDY_WORD_LOCK_321,DIG_WORD_SHOVEL_261],[INMATE_WORD_PRISONER_312,RIGEL_WORD_STARS_236,PARROT_WORD_PETS_2],[URANUS_WORD_PLANET_90,ALTAIR_WORD_STARS_236,CAT_WORD_PETS_2],[MERCURY_WORD_PLANET_90,SIRIUS_WORD_STARS_236],[ALKAID_WORD_STARS_236,CHATBOT_WORD_AI_238,CHEESE_WORD_BURGER_8],[POLARIS_WORD_STARS_236,HAMMOCK_PIC_CAMPING_64,DIAMOND_WORD_GEMSTONE_186],[SATURN_WORD_PLANET_90,MATRIX_WORD_AI_238,SAUCE_WORD_BURGER_8],[EARTH_WORD_PLANET_90,DOG_WORD_PETS_2,SKIS_PIC_PAIRS_63],[VENUS_WORD_PLANET_90,NEURAL_WORD_AI_238,BEEF_WORD_BURGER_8],[VEGA_WORD_STARS_236,BUN_WORD_BURGER_8],[FELON_WORD_PRISONER_312,TOPAZ_WORD_GEMSTONE_186,TENT_PIC_CAMPING_64],[DETAINEE_WORD_PRISONER_312,TWINS_PIC_PAIRS_63,ONYX_WORD_GEMSTONE_186],[JUPITER_WORD_PLANET_90,CAMPFIRE_PIC_CAMPING_64,AGATE_WORD_GEMSTONE_186],[AGENT_WORD_AI_238,GARNET_WORD_GEMSTONE_186,SAPPHIRE_WORD_GEMSTONE_186],[NEPTUNE_WORD_PLANET_90,HAMSTER_WORD_PETS_2,RUBY_WORD_GEMSTONE_186],[MARS_WORD_PLANET_90,SOCKS_PIC_PAIRS_63,OPAL_WORD_GEMSTONE_186]]</t>
-  </si>
-  <si>
-    <t>[WORD_PLANET_90,WORD_STARS_236,WORD_PRISONER_312,WORD_AI_238,WORD_PETS_2,PIC_CAMPING_64,PIC_PAIRS_63,WORD_BURGER_8,WORD_GEMSTONE_186]</t>
+    <t>[[HAMMOCK_PIC_CAMPING_64,LENS_WORD_CAMERA_73,FLASH_WORD_CAMERA_73],[DATASET_WORD_AI_238,ALTAIR_WORD_STARS_236,AGENT_WORD_AI_238],[TENT_PIC_CAMPING_64,ZOOM_WORD_CAMERA_73,FILTER_WORD_CAMERA_73],[CAT_WORD_PETS_2,MIST_WORD_FOG_76,SHUTTER_WORD_CAMERA_73],[SKIS_PIC_PAIRS_63,ALKAID_WORD_STARS_236],[CAMPFIRE_PIC_CAMPING_64,HAZE_WORD_FOG_76,RHODIUM_WORD_METAL_272],[USA_WORD_MAP_32,HAMSTER_WORD_PETS_2,BUN_WORD_BURGER_8],[JAPAN_WORD_MAP_32,HOLMIUM_WORD_METAL_272,YTTRIUM_WORD_METAL_272],[TWINS_PIC_PAIRS_63,RIGEL_WORD_STARS_236,AGATE_WORD_GEMSTONE_186],[INDIA_WORD_MAP_32,LCD_WORD_DISPLAY_486,OLED_WORD_DISPLAY_486],[SIRIUS_WORD_STARS_236,POLARIS_WORD_STARS_236,SAUCE_WORD_BURGER_8],[VEGA_WORD_STARS_236,CORTEX_WORD_AI_238,ONYX_WORD_GEMSTONE_186],[DOG_WORD_PETS_2,MATRIX_WORD_AI_238],[SOCKS_PIC_PAIRS_63,GARNET_WORD_GEMSTONE_186,RUBY_WORD_GEMSTONE_186],[CYPRUS_WORD_MAP_32,TOPAZ_WORD_GEMSTONE_186,CHEESE_WORD_BURGER_8],[AUSTRALIA_WORD_MAP_32,OVERTURE_WORD_SYMPHONY_210,WELDER_WORD_JOBS_42],[CHATBOT_WORD_AI_238,NEURAL_WORD_AI_238,SAPPHIRE_WORD_GEMSTONE_186],[LED_WORD_DISPLAY_486,NURSE_WORD_JOBS_42,DOCTOR_WORD_JOBS_42],[INMATE_WORD_PRISONER_312,SLEET_WORD_SNOW_77,FLAKE_WORD_SNOW_77],[DETAINEE_WORD_PRISONER_312,EXPOSURE_WORD_CAMERA_73,ROMANOV_WORD_DYNASTY_991],[FELON_WORD_PRISONER_312,BEEF_WORD_BURGER_8,DIAMOND_WORD_GEMSTONE_186],[UK_WORD_MAP_32,PARROT_WORD_PETS_2,OPAL_WORD_GEMSTONE_186],[ITALY_WORD_MAP_32,BOURBON_WORD_DYNASTY_991,LORD_WORD_MEDIEVAL_228],[MELODY_WORD_SYMPHONY_210,PUPIL_WORD_EYE_260,RETINA_WORD_EYE_260],[FRANCE_WORD_MAP_32,ICEBERG_WORD_SNOW_77]]</t>
+  </si>
+  <si>
+    <t>[WORD_MAP_32,WORD_STARS_236,WORD_PRISONER_312,WORD_AI_238,WORD_PETS_2,PIC_CAMPING_64,PIC_PAIRS_63,WORD_BURGER_8,WORD_GEMSTONE_186]</t>
   </si>
   <si>
     <t>SORT_GAME_LEVE_40_BOARD_1</t>
@@ -714,10 +714,10 @@
     <t>[1,9,12]</t>
   </si>
   <si>
-    <t>[[TERRAIN_WORD_MAPS_1022,AMOLED_WORD_DISPLAY_486,ECLIPSE_WORD_SPACE_314],[OLED_WORD_DISPLAY_486,PLASMA_WORD_DISPLAY_486,WORD_MAPS_1022,PULSAR_WORD_SPACE_314],[LED_WORD_DISPLAY_486,GLOBE_WORD_MAPS_1022,SANTA_PIC_XMAS_65],[STAMP_PIC_MAIL_66,CANDY_CANE_PIC_XMAS_65,YTTRIUM_WORD_METAL_272],[OVERTURE_WORD_SYMPHONY_210,ATLAS_WORD_MAPS_1022,ASTEROID_WORD_SPACE_314],[PIC_MAIL_66,LANDMARK_WORD_MAPS_1022],[STURDY_WORD_LOCK_321,DIAMOND_WORD_GEMSTONE_186],[DOCTOR_WORD_JOBS_42,CHATBOT_WORD_AI_238,POLARIS_WORD_STARS_236],[LUTETIUM_WORD_METAL_272,SECURE_WORD_LOCK_321,HOLMIUM_WORD_METAL_272],[HARMONY_WORD_SYMPHONY_210,VEGA_WORD_STARS_236],[LEMONADE_WORD_DRINKS_16,CAT_WORD_PETS_2,DOG_WORD_PETS_2],[BORDER_WORD_MAPS_1022,CHEESE_WORD_BURGER_8,DETAINEE_WORD_PRISONER_312],[ERBIUM_WORD_METAL_272,LETTER_PIC_MAIL_66,NOVA_WORD_SPACE_314],[JUICE_WORD_DRINKS_16,JOURNEY_WORD_MAPS_1022,QUASAR_WORD_SPACE_314],[SCALE_WORD_MAPS_1022],[ESPRESSO_WORD_DRINKS_16,ENGINEER_WORD_JOBS_42,RIYADH_WORD_CAPITALS_119],[CHRISTMAS_TREE_PIC_XMAS_65,CHRISTMAS_STOCKING_PIC_XMAS_65,NEBULA_WORD_SPACE_314],[SODA_WORD_DRINKS_16,ROME_WORD_CAPITALS_119],[LCD_WORD_DISPLAY_486,CONTOUR_WORD_MAPS_1022,METEOR_WORD_SPACE_314],[THULIUM_WORD_METAL_272,PRAGUE_WORD_CAPITALS_119,CAIRO_WORD_CAPITALS_119],[MELODY_WORD_SYMPHONY_210,EUROPIUM_WORD_METAL_272,AURORA_WORD_SPACE_314],[TRUSTY_WORD_LOCK_321,OSLO_WORD_CAPITALS_119,ATHENS_WORD_CAPITALS_119],[CRT_WORD_DISPLAY_486,BOURBON_WORD_DYNASTY_991],[PARCEL_PIC_MAIL_66,IRIDIUM_WORD_METAL_272,RHODIUM_WORD_METAL_272],[WELDER_WORD_JOBS_42,KNIGHT_WORD_MEDIEVAL_228,EXCAVATE_WORD_SHOVEL_261]]</t>
-  </si>
-  <si>
-    <t>[WORD_DRINKS_16,WORD_DISPLAY_486,WORD_SYMPHONY_210,PIC_XMAS_65,WORD_LOCK_321,WORD_METAL_272,WORD_SPACE_314]</t>
+    <t>[[TERRAIN_WORD_MAPS_1022,AMOLED_WORD_DISPLAY_486,ECLIPSE_WORD_SPACE_314],[OLED_WORD_DISPLAY_486,PLASMA_WORD_DISPLAY_486,PULSAR_WORD_SPACE_314],[LED_WORD_DISPLAY_486,GLOBE_WORD_MAPS_1022,SANTA_PIC_XMAS_65],[STAMP_PIC_MAIL_66,CANDY_CANE_PIC_XMAS_65,YTTRIUM_WORD_METAL_272],[OVERTURE_WORD_SYMPHONY_210,ATLAS_WORD_MAPS_1022,ASTEROID_WORD_SPACE_314],[LANDMARK_WORD_MAPS_1022,DEGREE_WORD_PHD_296,THESIS_WORD_PHD_296],[STURDY_WORD_LOCK_321,DIAMOND_WORD_GEMSTONE_186,AGENT_WORD_AI_238],[DOCTOR_WORD_JOBS_42,CHATBOT_WORD_AI_238,HI_WORD_HELLO_295],[LUTETIUM_WORD_METAL_272,SECURE_WORD_LOCK_321,HOLMIUM_WORD_METAL_272],[HARMONY_WORD_SYMPHONY_210,HOWDY_WORD_HELLO_295,HEY_WORD_HELLO_295],[LEMONADE_WORD_DRINKS_16,CAT_WORD_PETS_2,DOG_WORD_PETS_2],[BORDER_WORD_MAPS_1022,CHEESE_WORD_BURGER_8,DETAINEE_WORD_PRISONER_312],[ERBIUM_WORD_METAL_272,LETTER_PIC_MAIL_66,NOVA_WORD_SPACE_314],[JUICE_WORD_DRINKS_16,JOURNEY_WORD_MAPS_1022,QUASAR_WORD_SPACE_314],[SCALE_WORD_MAPS_1022,MAILMAN_WORD_JOBS_42,PILOT_WORD_JOBS_42],[ESPRESSO_WORD_DRINKS_16,ENGINEER_WORD_JOBS_42,RESEARCH_WORD_PHD_296],[CHRISTMAS_TREE_PIC_XMAS_65,CHRISTMAS_STOCKING_PIC_XMAS_65,NEBULA_WORD_SPACE_314],[SODA_WORD_DRINKS_16,YES_WORD_OK_SIGN_301,LAW_WORD_JUSTICE_310],[LCD_WORD_DISPLAY_486,CONTOUR_WORD_MAPS_1022,METEOR_WORD_SPACE_314],[THULIUM_WORD_METAL_272,HAY_WORD_FARMING_333,HARVEST_WORD_FARMING_333],[MELODY_WORD_SYMPHONY_210,EUROPIUM_WORD_METAL_272,AURORA_WORD_SPACE_314],[TRUSTY_WORD_LOCK_321,CONSENT_WORD_OK_SIGN_301,OKAY_WORD_OK_SIGN_301],[CRT_WORD_DISPLAY_486,BOURBON_WORD_DYNASTY_991,ROMANOV_WORD_DYNASTY_991],[PARCEL_PIC_MAIL_66,IRIDIUM_WORD_METAL_272,RHODIUM_WORD_METAL_272],[WELDER_WORD_JOBS_42,KNIGHT_WORD_MEDIEVAL_228,EXCAVATE_WORD_SHOVEL_261]]</t>
+  </si>
+  <si>
+    <t>[WORD_DRINKS_16,WORD_DISPLAY_486,WORD_SYMPHONY_210,PIC_XMAS_65,WORD_MAPS_1022,WORD_LOCK_321,WORD_METAL_272,PIC_MAIL_66,WORD_SPACE_314]</t>
   </si>
 </sst>
 </file>
@@ -1457,8 +1457,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2078,19 +2078,19 @@
         <v>2</v>
       </c>
       <c r="H6" s="6"/>
-      <c r="I6" s="7">
-        <v>1</v>
-      </c>
-      <c r="J6" s="7" t="s">
+      <c r="I6" s="8">
+        <v>1</v>
+      </c>
+      <c r="J6" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="K6" s="7">
-        <v>2</v>
-      </c>
-      <c r="L6" s="7" t="s">
+      <c r="K6" s="8">
+        <v>2</v>
+      </c>
+      <c r="L6" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="M6" s="7" t="s">
+      <c r="M6" s="8" t="s">
         <v>57</v>
       </c>
       <c r="N6" s="7" t="s">
@@ -2129,19 +2129,19 @@
         <v>3</v>
       </c>
       <c r="H7" s="6"/>
-      <c r="I7" s="7">
-        <v>1</v>
-      </c>
-      <c r="J7" s="7" t="s">
+      <c r="I7" s="8">
+        <v>1</v>
+      </c>
+      <c r="J7" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="K7" s="7">
-        <v>2</v>
-      </c>
-      <c r="L7" s="7" t="s">
+      <c r="K7" s="8">
+        <v>2</v>
+      </c>
+      <c r="L7" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="M7" s="7" t="s">
+      <c r="M7" s="8" t="s">
         <v>64</v>
       </c>
       <c r="N7" s="7" t="s">
@@ -2180,19 +2180,19 @@
         <v>4</v>
       </c>
       <c r="H8" s="6"/>
-      <c r="I8" s="7">
-        <v>1</v>
-      </c>
-      <c r="J8" s="7" t="s">
+      <c r="I8" s="8">
+        <v>1</v>
+      </c>
+      <c r="J8" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="K8" s="7">
-        <v>2</v>
-      </c>
-      <c r="L8" s="7" t="s">
+      <c r="K8" s="8">
+        <v>2</v>
+      </c>
+      <c r="L8" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="M8" s="7" t="s">
+      <c r="M8" s="8" t="s">
         <v>70</v>
       </c>
       <c r="N8" s="7" t="s">
@@ -2231,19 +2231,19 @@
         <v>5</v>
       </c>
       <c r="H9" s="6"/>
-      <c r="I9" s="7">
-        <v>2</v>
-      </c>
-      <c r="J9" s="7" t="s">
+      <c r="I9" s="8">
+        <v>2</v>
+      </c>
+      <c r="J9" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="K9" s="7">
-        <v>2</v>
-      </c>
-      <c r="L9" s="7" t="s">
+      <c r="K9" s="8">
+        <v>2</v>
+      </c>
+      <c r="L9" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="M9" s="7" t="s">
+      <c r="M9" s="8" t="s">
         <v>76</v>
       </c>
       <c r="N9" s="7" t="s">
@@ -2282,19 +2282,19 @@
         <v>6</v>
       </c>
       <c r="H10" s="6"/>
-      <c r="I10" s="7">
-        <v>2</v>
-      </c>
-      <c r="J10" s="7" t="s">
+      <c r="I10" s="8">
+        <v>2</v>
+      </c>
+      <c r="J10" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="K10" s="7">
-        <v>2</v>
-      </c>
-      <c r="L10" s="7" t="s">
+      <c r="K10" s="8">
+        <v>2</v>
+      </c>
+      <c r="L10" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="M10" s="7" t="s">
+      <c r="M10" s="8" t="s">
         <v>82</v>
       </c>
       <c r="N10" s="7" t="s">
@@ -2333,19 +2333,19 @@
         <v>7</v>
       </c>
       <c r="H11" s="6"/>
-      <c r="I11" s="7">
-        <v>1</v>
-      </c>
-      <c r="J11" s="7" t="s">
+      <c r="I11" s="8">
+        <v>1</v>
+      </c>
+      <c r="J11" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="K11" s="7">
-        <v>2</v>
-      </c>
-      <c r="L11" s="7" t="s">
+      <c r="K11" s="8">
+        <v>2</v>
+      </c>
+      <c r="L11" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="M11" s="7" t="s">
+      <c r="M11" s="8" t="s">
         <v>87</v>
       </c>
       <c r="N11" s="7" t="s">
@@ -2384,19 +2384,19 @@
         <v>8</v>
       </c>
       <c r="H12" s="6"/>
-      <c r="I12" s="7">
-        <v>1</v>
-      </c>
-      <c r="J12" s="7" t="s">
+      <c r="I12" s="8">
+        <v>1</v>
+      </c>
+      <c r="J12" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="K12" s="7">
-        <v>2</v>
-      </c>
-      <c r="L12" s="7" t="s">
+      <c r="K12" s="8">
+        <v>2</v>
+      </c>
+      <c r="L12" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="M12" s="7" t="s">
+      <c r="M12" s="8" t="s">
         <v>93</v>
       </c>
       <c r="N12" s="7" t="s">
@@ -2435,19 +2435,19 @@
         <v>9</v>
       </c>
       <c r="H13" s="6"/>
-      <c r="I13" s="7">
-        <v>2</v>
-      </c>
-      <c r="J13" s="7" t="s">
+      <c r="I13" s="8">
+        <v>2</v>
+      </c>
+      <c r="J13" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="K13" s="7">
-        <v>2</v>
-      </c>
-      <c r="L13" s="7" t="s">
+      <c r="K13" s="8">
+        <v>2</v>
+      </c>
+      <c r="L13" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="M13" s="7" t="s">
+      <c r="M13" s="8" t="s">
         <v>99</v>
       </c>
       <c r="N13" s="7" t="s">
@@ -2486,19 +2486,19 @@
         <v>10</v>
       </c>
       <c r="H14" s="6"/>
-      <c r="I14" s="7">
-        <v>2</v>
-      </c>
-      <c r="J14" s="7" t="s">
+      <c r="I14" s="8">
+        <v>2</v>
+      </c>
+      <c r="J14" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="K14" s="7">
-        <v>2</v>
-      </c>
-      <c r="L14" s="7" t="s">
+      <c r="K14" s="8">
+        <v>2</v>
+      </c>
+      <c r="L14" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="M14" s="7" t="s">
+      <c r="M14" s="8" t="s">
         <v>105</v>
       </c>
       <c r="N14" s="7" t="s">
@@ -2537,19 +2537,19 @@
         <v>11</v>
       </c>
       <c r="H15" s="6"/>
-      <c r="I15" s="7">
-        <v>2</v>
-      </c>
-      <c r="J15" s="7" t="s">
+      <c r="I15" s="8">
+        <v>2</v>
+      </c>
+      <c r="J15" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="K15" s="7">
-        <v>2</v>
-      </c>
-      <c r="L15" s="7" t="s">
+      <c r="K15" s="8">
+        <v>2</v>
+      </c>
+      <c r="L15" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="M15" s="7" t="s">
+      <c r="M15" s="8" t="s">
         <v>111</v>
       </c>
       <c r="N15" s="7" t="s">
@@ -2586,19 +2586,19 @@
         <v>12</v>
       </c>
       <c r="H16" s="6"/>
-      <c r="I16" s="7">
-        <v>1</v>
-      </c>
-      <c r="J16" s="7" t="s">
+      <c r="I16" s="8">
+        <v>1</v>
+      </c>
+      <c r="J16" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="K16" s="7">
-        <v>2</v>
-      </c>
-      <c r="L16" s="7" t="s">
+      <c r="K16" s="8">
+        <v>2</v>
+      </c>
+      <c r="L16" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="M16" s="7" t="s">
+      <c r="M16" s="8" t="s">
         <v>116</v>
       </c>
       <c r="N16" s="7" t="s">
@@ -2635,19 +2635,19 @@
         <v>13</v>
       </c>
       <c r="H17" s="6"/>
-      <c r="I17" s="7">
-        <v>2</v>
-      </c>
-      <c r="J17" s="7" t="s">
+      <c r="I17" s="8">
+        <v>2</v>
+      </c>
+      <c r="J17" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="K17" s="7">
-        <v>2</v>
-      </c>
-      <c r="L17" s="7" t="s">
+      <c r="K17" s="8">
+        <v>2</v>
+      </c>
+      <c r="L17" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="M17" s="7" t="s">
+      <c r="M17" s="8" t="s">
         <v>120</v>
       </c>
       <c r="N17" s="7" t="s">
@@ -2684,19 +2684,19 @@
         <v>14</v>
       </c>
       <c r="H18" s="6"/>
-      <c r="I18" s="7">
-        <v>2</v>
-      </c>
-      <c r="J18" s="7" t="s">
+      <c r="I18" s="8">
+        <v>2</v>
+      </c>
+      <c r="J18" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="K18" s="7">
-        <v>2</v>
-      </c>
-      <c r="L18" s="7" t="s">
+      <c r="K18" s="8">
+        <v>2</v>
+      </c>
+      <c r="L18" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="M18" s="7" t="s">
+      <c r="M18" s="8" t="s">
         <v>123</v>
       </c>
       <c r="N18" s="7" t="s">
@@ -2733,19 +2733,19 @@
         <v>15</v>
       </c>
       <c r="H19" s="6"/>
-      <c r="I19" s="7">
-        <v>2</v>
-      </c>
-      <c r="J19" s="7" t="s">
+      <c r="I19" s="8">
+        <v>2</v>
+      </c>
+      <c r="J19" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="K19" s="7">
-        <v>2</v>
-      </c>
-      <c r="L19" s="7" t="s">
+      <c r="K19" s="8">
+        <v>2</v>
+      </c>
+      <c r="L19" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="M19" s="7" t="s">
+      <c r="M19" s="8" t="s">
         <v>127</v>
       </c>
       <c r="N19" s="7" t="s">
@@ -2782,19 +2782,19 @@
         <v>16</v>
       </c>
       <c r="H20" s="6"/>
-      <c r="I20" s="7">
-        <v>2</v>
-      </c>
-      <c r="J20" s="7" t="s">
+      <c r="I20" s="8">
+        <v>2</v>
+      </c>
+      <c r="J20" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="K20" s="7">
-        <v>2</v>
-      </c>
-      <c r="L20" s="7" t="s">
+      <c r="K20" s="8">
+        <v>2</v>
+      </c>
+      <c r="L20" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="M20" s="7" t="s">
+      <c r="M20" s="8" t="s">
         <v>131</v>
       </c>
       <c r="N20" s="7" t="s">
@@ -2831,19 +2831,19 @@
         <v>17</v>
       </c>
       <c r="H21" s="6"/>
-      <c r="I21" s="7">
-        <v>1</v>
-      </c>
-      <c r="J21" s="7" t="s">
+      <c r="I21" s="8">
+        <v>1</v>
+      </c>
+      <c r="J21" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="K21" s="7">
-        <v>2</v>
-      </c>
-      <c r="L21" s="7" t="s">
+      <c r="K21" s="8">
+        <v>2</v>
+      </c>
+      <c r="L21" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="M21" s="7" t="s">
+      <c r="M21" s="8" t="s">
         <v>135</v>
       </c>
       <c r="N21" s="7" t="s">
@@ -2880,19 +2880,19 @@
         <v>18</v>
       </c>
       <c r="H22" s="6"/>
-      <c r="I22" s="7">
-        <v>2</v>
-      </c>
-      <c r="J22" s="7" t="s">
+      <c r="I22" s="8">
+        <v>2</v>
+      </c>
+      <c r="J22" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="K22" s="7">
-        <v>2</v>
-      </c>
-      <c r="L22" s="7" t="s">
+      <c r="K22" s="8">
+        <v>2</v>
+      </c>
+      <c r="L22" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="M22" s="7" t="s">
+      <c r="M22" s="8" t="s">
         <v>139</v>
       </c>
       <c r="N22" s="7" t="s">
@@ -2929,19 +2929,19 @@
         <v>19</v>
       </c>
       <c r="H23" s="6"/>
-      <c r="I23" s="7">
-        <v>2</v>
-      </c>
-      <c r="J23" s="7" t="s">
+      <c r="I23" s="8">
+        <v>2</v>
+      </c>
+      <c r="J23" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="K23" s="7">
-        <v>2</v>
-      </c>
-      <c r="L23" s="7" t="s">
+      <c r="K23" s="8">
+        <v>2</v>
+      </c>
+      <c r="L23" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="M23" s="7" t="s">
+      <c r="M23" s="8" t="s">
         <v>142</v>
       </c>
       <c r="N23" s="7" t="s">
@@ -2978,19 +2978,19 @@
         <v>20</v>
       </c>
       <c r="H24" s="6"/>
-      <c r="I24" s="7">
-        <v>2</v>
-      </c>
-      <c r="J24" s="7" t="s">
+      <c r="I24" s="8">
+        <v>2</v>
+      </c>
+      <c r="J24" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="K24" s="7">
-        <v>2</v>
-      </c>
-      <c r="L24" s="7" t="s">
+      <c r="K24" s="8">
+        <v>2</v>
+      </c>
+      <c r="L24" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="M24" s="7" t="s">
+      <c r="M24" s="8" t="s">
         <v>145</v>
       </c>
       <c r="N24" s="7" t="s">
@@ -3027,19 +3027,19 @@
         <v>21</v>
       </c>
       <c r="H25" s="6"/>
-      <c r="I25" s="7">
+      <c r="I25" s="8">
         <v>3</v>
       </c>
-      <c r="J25" s="7" t="s">
+      <c r="J25" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="K25" s="7">
-        <v>2</v>
-      </c>
-      <c r="L25" s="7" t="s">
+      <c r="K25" s="8">
+        <v>2</v>
+      </c>
+      <c r="L25" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="M25" s="7" t="s">
+      <c r="M25" s="8" t="s">
         <v>149</v>
       </c>
       <c r="N25" s="7" t="s">
@@ -3076,19 +3076,19 @@
         <v>22</v>
       </c>
       <c r="H26" s="6"/>
-      <c r="I26" s="7">
-        <v>2</v>
-      </c>
-      <c r="J26" s="7" t="s">
+      <c r="I26" s="8">
+        <v>2</v>
+      </c>
+      <c r="J26" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="K26" s="7">
-        <v>2</v>
-      </c>
-      <c r="L26" s="7" t="s">
+      <c r="K26" s="8">
+        <v>2</v>
+      </c>
+      <c r="L26" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="M26" s="7" t="s">
+      <c r="M26" s="8" t="s">
         <v>153</v>
       </c>
       <c r="N26" s="7" t="s">
@@ -3125,19 +3125,19 @@
         <v>23</v>
       </c>
       <c r="H27" s="6"/>
-      <c r="I27" s="7">
-        <v>2</v>
-      </c>
-      <c r="J27" s="7" t="s">
+      <c r="I27" s="8">
+        <v>2</v>
+      </c>
+      <c r="J27" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="K27" s="7">
-        <v>2</v>
-      </c>
-      <c r="L27" s="7" t="s">
+      <c r="K27" s="8">
+        <v>2</v>
+      </c>
+      <c r="L27" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="M27" s="7" t="s">
+      <c r="M27" s="8" t="s">
         <v>157</v>
       </c>
       <c r="N27" s="7" t="s">
@@ -3174,19 +3174,19 @@
         <v>24</v>
       </c>
       <c r="H28" s="6"/>
-      <c r="I28" s="7">
-        <v>2</v>
-      </c>
-      <c r="J28" s="7" t="s">
+      <c r="I28" s="8">
+        <v>2</v>
+      </c>
+      <c r="J28" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="K28" s="7">
-        <v>2</v>
-      </c>
-      <c r="L28" s="7" t="s">
+      <c r="K28" s="8">
+        <v>2</v>
+      </c>
+      <c r="L28" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="M28" s="7" t="s">
+      <c r="M28" s="8" t="s">
         <v>161</v>
       </c>
       <c r="N28" s="7" t="s">
@@ -3223,19 +3223,19 @@
         <v>25</v>
       </c>
       <c r="H29" s="6"/>
-      <c r="I29" s="7">
+      <c r="I29" s="8">
         <v>3</v>
       </c>
-      <c r="J29" s="7" t="s">
+      <c r="J29" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="K29" s="7">
-        <v>2</v>
-      </c>
-      <c r="L29" s="7" t="s">
+      <c r="K29" s="8">
+        <v>2</v>
+      </c>
+      <c r="L29" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="M29" s="7" t="s">
+      <c r="M29" s="8" t="s">
         <v>165</v>
       </c>
       <c r="N29" s="7" t="s">
@@ -3272,19 +3272,19 @@
         <v>26</v>
       </c>
       <c r="H30" s="6"/>
-      <c r="I30" s="7">
+      <c r="I30" s="8">
         <v>3</v>
       </c>
-      <c r="J30" s="7" t="s">
+      <c r="J30" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="K30" s="7">
-        <v>2</v>
-      </c>
-      <c r="L30" s="7" t="s">
+      <c r="K30" s="8">
+        <v>2</v>
+      </c>
+      <c r="L30" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="M30" s="7" t="s">
+      <c r="M30" s="8" t="s">
         <v>169</v>
       </c>
       <c r="N30" s="7" t="s">
@@ -3321,19 +3321,19 @@
         <v>27</v>
       </c>
       <c r="H31" s="6"/>
-      <c r="I31" s="7">
-        <v>2</v>
-      </c>
-      <c r="J31" s="7" t="s">
+      <c r="I31" s="8">
+        <v>2</v>
+      </c>
+      <c r="J31" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="K31" s="7">
-        <v>2</v>
-      </c>
-      <c r="L31" s="7" t="s">
+      <c r="K31" s="8">
+        <v>2</v>
+      </c>
+      <c r="L31" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="M31" s="7" t="s">
+      <c r="M31" s="8" t="s">
         <v>173</v>
       </c>
       <c r="N31" s="7" t="s">
@@ -3370,19 +3370,19 @@
         <v>28</v>
       </c>
       <c r="H32" s="6"/>
-      <c r="I32" s="7">
-        <v>2</v>
-      </c>
-      <c r="J32" s="7" t="s">
+      <c r="I32" s="8">
+        <v>2</v>
+      </c>
+      <c r="J32" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="K32" s="7">
-        <v>2</v>
-      </c>
-      <c r="L32" s="7" t="s">
+      <c r="K32" s="8">
+        <v>2</v>
+      </c>
+      <c r="L32" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="M32" s="7" t="s">
+      <c r="M32" s="8" t="s">
         <v>177</v>
       </c>
       <c r="N32" s="7" t="s">
@@ -3419,19 +3419,19 @@
         <v>29</v>
       </c>
       <c r="H33" s="6"/>
-      <c r="I33" s="7">
+      <c r="I33" s="8">
         <v>3</v>
       </c>
-      <c r="J33" s="7" t="s">
+      <c r="J33" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="K33" s="7">
-        <v>2</v>
-      </c>
-      <c r="L33" s="7" t="s">
+      <c r="K33" s="8">
+        <v>2</v>
+      </c>
+      <c r="L33" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="M33" s="7" t="s">
+      <c r="M33" s="8" t="s">
         <v>181</v>
       </c>
       <c r="N33" s="7" t="s">
@@ -3468,19 +3468,19 @@
         <v>30</v>
       </c>
       <c r="H34" s="6"/>
-      <c r="I34" s="7">
+      <c r="I34" s="8">
         <v>3</v>
       </c>
-      <c r="J34" s="7" t="s">
+      <c r="J34" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="K34" s="7">
+      <c r="K34" s="8">
         <v>3</v>
       </c>
-      <c r="L34" s="7" t="s">
+      <c r="L34" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="M34" s="7" t="s">
+      <c r="M34" s="8" t="s">
         <v>185</v>
       </c>
       <c r="N34" s="7" t="s">
@@ -3517,19 +3517,19 @@
         <v>31</v>
       </c>
       <c r="H35" s="6"/>
-      <c r="I35" s="7">
+      <c r="I35" s="8">
         <v>3</v>
       </c>
-      <c r="J35" s="7" t="s">
+      <c r="J35" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="K35" s="7">
+      <c r="K35" s="8">
         <v>3</v>
       </c>
-      <c r="L35" s="7" t="s">
+      <c r="L35" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="M35" s="7" t="s">
+      <c r="M35" s="8" t="s">
         <v>189</v>
       </c>
       <c r="N35" s="7" t="s">
@@ -3566,19 +3566,19 @@
         <v>32</v>
       </c>
       <c r="H36" s="6"/>
-      <c r="I36" s="7">
-        <v>2</v>
-      </c>
-      <c r="J36" s="7" t="s">
+      <c r="I36" s="8">
+        <v>2</v>
+      </c>
+      <c r="J36" s="8" t="s">
         <v>191</v>
       </c>
-      <c r="K36" s="7">
-        <v>2</v>
-      </c>
-      <c r="L36" s="7" t="s">
+      <c r="K36" s="8">
+        <v>2</v>
+      </c>
+      <c r="L36" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="M36" s="7" t="s">
+      <c r="M36" s="8" t="s">
         <v>193</v>
       </c>
       <c r="N36" s="7" t="s">
@@ -3615,19 +3615,19 @@
         <v>33</v>
       </c>
       <c r="H37" s="6"/>
-      <c r="I37" s="7">
+      <c r="I37" s="8">
         <v>3</v>
       </c>
-      <c r="J37" s="7" t="s">
+      <c r="J37" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="K37" s="7">
-        <v>2</v>
-      </c>
-      <c r="L37" s="7" t="s">
+      <c r="K37" s="8">
+        <v>2</v>
+      </c>
+      <c r="L37" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="M37" s="7" t="s">
+      <c r="M37" s="8" t="s">
         <v>197</v>
       </c>
       <c r="N37" s="7" t="s">
@@ -3664,19 +3664,19 @@
         <v>34</v>
       </c>
       <c r="H38" s="6"/>
-      <c r="I38" s="7">
+      <c r="I38" s="8">
         <v>3</v>
       </c>
-      <c r="J38" s="7" t="s">
+      <c r="J38" s="8" t="s">
         <v>199</v>
       </c>
-      <c r="K38" s="7">
-        <v>2</v>
-      </c>
-      <c r="L38" s="7" t="s">
+      <c r="K38" s="8">
+        <v>2</v>
+      </c>
+      <c r="L38" s="8" t="s">
         <v>200</v>
       </c>
-      <c r="M38" s="7" t="s">
+      <c r="M38" s="8" t="s">
         <v>201</v>
       </c>
       <c r="N38" s="7" t="s">
@@ -3713,19 +3713,19 @@
         <v>35</v>
       </c>
       <c r="H39" s="6"/>
-      <c r="I39" s="7">
+      <c r="I39" s="8">
         <v>3</v>
       </c>
-      <c r="J39" s="7" t="s">
+      <c r="J39" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="K39" s="7">
+      <c r="K39" s="8">
         <v>3</v>
       </c>
-      <c r="L39" s="7" t="s">
+      <c r="L39" s="8" t="s">
         <v>204</v>
       </c>
-      <c r="M39" s="7" t="s">
+      <c r="M39" s="8" t="s">
         <v>205</v>
       </c>
       <c r="N39" s="7" t="s">
@@ -3762,19 +3762,19 @@
         <v>36</v>
       </c>
       <c r="H40" s="6"/>
-      <c r="I40" s="7">
+      <c r="I40" s="8">
         <v>3</v>
       </c>
-      <c r="J40" s="7" t="s">
+      <c r="J40" s="8" t="s">
         <v>207</v>
       </c>
-      <c r="K40" s="7">
+      <c r="K40" s="8">
         <v>3</v>
       </c>
-      <c r="L40" s="7" t="s">
+      <c r="L40" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="M40" s="7" t="s">
+      <c r="M40" s="8" t="s">
         <v>209</v>
       </c>
       <c r="N40" s="7" t="s">
@@ -3811,19 +3811,19 @@
         <v>37</v>
       </c>
       <c r="H41" s="6"/>
-      <c r="I41" s="7">
+      <c r="I41" s="8">
         <v>3</v>
       </c>
-      <c r="J41" s="7" t="s">
+      <c r="J41" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="K41" s="7">
-        <v>2</v>
-      </c>
-      <c r="L41" s="7" t="s">
+      <c r="K41" s="8">
+        <v>2</v>
+      </c>
+      <c r="L41" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="M41" s="7" t="s">
+      <c r="M41" s="8" t="s">
         <v>213</v>
       </c>
       <c r="N41" s="7" t="s">
@@ -3860,19 +3860,19 @@
         <v>38</v>
       </c>
       <c r="H42" s="6"/>
-      <c r="I42" s="7">
+      <c r="I42" s="8">
         <v>3</v>
       </c>
-      <c r="J42" s="7" t="s">
+      <c r="J42" s="8" t="s">
         <v>215</v>
       </c>
-      <c r="K42" s="7">
-        <v>2</v>
-      </c>
-      <c r="L42" s="7" t="s">
+      <c r="K42" s="8">
+        <v>2</v>
+      </c>
+      <c r="L42" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="M42" s="7" t="s">
+      <c r="M42" s="8" t="s">
         <v>217</v>
       </c>
       <c r="N42" s="7" t="s">
@@ -3909,19 +3909,19 @@
         <v>39</v>
       </c>
       <c r="H43" s="6"/>
-      <c r="I43" s="7">
+      <c r="I43" s="8">
         <v>3</v>
       </c>
-      <c r="J43" s="7" t="s">
+      <c r="J43" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="K43" s="7">
-        <v>2</v>
-      </c>
-      <c r="L43" s="7" t="s">
+      <c r="K43" s="8">
+        <v>2</v>
+      </c>
+      <c r="L43" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="M43" s="7" t="s">
+      <c r="M43" s="8" t="s">
         <v>221</v>
       </c>
       <c r="N43" s="7" t="s">
@@ -3958,19 +3958,19 @@
         <v>40</v>
       </c>
       <c r="H44" s="6"/>
-      <c r="I44" s="7">
+      <c r="I44" s="8">
         <v>3</v>
       </c>
-      <c r="J44" s="7" t="s">
+      <c r="J44" s="8" t="s">
         <v>223</v>
       </c>
-      <c r="K44" s="7">
+      <c r="K44" s="8">
         <v>3</v>
       </c>
-      <c r="L44" s="7" t="s">
+      <c r="L44" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="M44" s="7" t="s">
+      <c r="M44" s="8" t="s">
         <v>225</v>
       </c>
       <c r="N44" s="7" t="s">
@@ -4007,13 +4007,13 @@
         <v>-1</v>
       </c>
       <c r="H45" s="6"/>
-      <c r="I45" s="7">
+      <c r="I45" s="8">
         <v>3</v>
       </c>
-      <c r="J45" s="7" t="s">
+      <c r="J45" s="8" t="s">
         <v>227</v>
       </c>
-      <c r="K45" s="7">
+      <c r="K45" s="8">
         <v>3</v>
       </c>
       <c r="L45" s="8" t="s">

--- a/config/level_config.xlsx
+++ b/config/level_config.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="276">
   <si>
     <t>id</t>
   </si>
@@ -192,7 +192,7 @@
     <t>string_config</t>
   </si>
   <si>
-    <t>SORT_GAME_LEVE_1_BOARD_1</t>
+    <t>SORT_GAME_LEVEL_1_BOARD_1</t>
   </si>
   <si>
     <t>[7]</t>
@@ -204,7 +204,7 @@
     <t>[WORD_LANDMASS_10,PIC_GARMENTS_7]</t>
   </si>
   <si>
-    <t>CONSTRUCTION_1_STORE_REWARD_6_1</t>
+    <t>SORT_GAME_LEVEL_REWARD_1</t>
   </si>
   <si>
     <t>DECK_CLEAN_1</t>
@@ -213,7 +213,7 @@
     <t>TID_SORT_GAME_LEVEL_1_DESC</t>
   </si>
   <si>
-    <t>SORT_GAME_LEVE_2_BOARD_1</t>
+    <t>SORT_GAME_LEVEL_2_BOARD_1</t>
   </si>
   <si>
     <t>[12]</t>
@@ -225,13 +225,16 @@
     <t>[WORD_HOLIDAY_163,WORD_HELP_183,PIC_FRUITS_9]</t>
   </si>
   <si>
+    <t>SORT_GAME_LEVEL_REWARD_2</t>
+  </si>
+  <si>
     <t>DECK_CLEAN_2</t>
   </si>
   <si>
     <t>TID_SORT_GAME_LEVEL_2_DESC</t>
   </si>
   <si>
-    <t>SORT_GAME_LEVE_3_BOARD_1</t>
+    <t>SORT_GAME_LEVEL_3_BOARD_1</t>
   </si>
   <si>
     <t>[10]</t>
@@ -243,13 +246,16 @@
     <t>[WORD_HELLO_295,WORD_HEART_344,WORD_OK_SIGN_301,PIC_CHESS_1]</t>
   </si>
   <si>
+    <t>SORT_GAME_LEVEL_REWARD_3</t>
+  </si>
+  <si>
     <t>DECK_CLEAN_3</t>
   </si>
   <si>
     <t>TID_SORT_GAME_LEVEL_3_DESC</t>
   </si>
   <si>
-    <t>SORT_GAME_LEVE_4_BOARD_1</t>
+    <t>SORT_GAME_LEVEL_4_BOARD_1</t>
   </si>
   <si>
     <t>[3,6]</t>
@@ -261,13 +267,16 @@
     <t>[WORD_FOOD_3,WORD_POINTING_379,WORD_SKIN_380,PIC_FURNITURE_3,WORD_STRENGTH_401]</t>
   </si>
   <si>
+    <t>SORT_GAME_LEVEL_REWARD_4</t>
+  </si>
+  <si>
     <t>BIG_SCREEN</t>
   </si>
   <si>
     <t>TID_BUILD_LIST_FIX_BIG_SCREEN</t>
   </si>
   <si>
-    <t>SORT_GAME_LEVE_5_BOARD_1</t>
+    <t>SORT_GAME_LEVEL_5_BOARD_1</t>
   </si>
   <si>
     <t>[5,8]</t>
@@ -279,13 +288,16 @@
     <t>[PIC_SPORTS_2,WORD_PRESENT_470,WORD_MEALS_444,WORD_MESSAGE_407,WORD_SECRET_471]</t>
   </si>
   <si>
+    <t>SORT_GAME_LEVEL_REWARD_5</t>
+  </si>
+  <si>
     <t>DECK_CLEAN_4</t>
   </si>
   <si>
     <t>TID_SORT_GAME_LEVEL_5_DESC</t>
   </si>
   <si>
-    <t>SORT_GAME_LEVE_6_BOARD_1</t>
+    <t>SORT_GAME_LEVEL_6_BOARD_1</t>
   </si>
   <si>
     <t>[[SURF_WORD_COAST_969,BEACH_WORD_COAST_969],[OPINION_WORD_ARTICLES_147],[ROAD_WORD_DRIVING_49,KNEE_WORD_LEGS_322],[SUCCESS_WORD_WREATH_544],[VIOLIN_PIC_PLAY_12],[ORGAN_PIC_PLAY_12],[ICEBERG_WORD_SNOW_77],[FLAKE_WORD_SNOW_77],[SIGN_WORD_DRIVING_49],[CLIFF_WORD_COAST_969],[BOBBER_WORD_FISHING_20],[TRAFFIC_WORD_DRIVING_49],[SUMMER_WORD_SEASONS_18],[PIANO_PIC_PLAY_12],[VICTORY_WORD_WREATH_544],[UKULELE_PIC_PLAY_12],[FLUTE_PIC_PLAY_12],[ESSAY_WORD_ARTICLES_147],[SLEET_WORD_SNOW_77],[TRIUMPH_WORD_WREATH_544,SPRING_WORD_SEASONS_18],[CAR_WORD_DRIVING_49,AUTUMN_WORD_SEASONS_18],[CELLO_PIC_PLAY_12],[GUITAR_PIC_PLAY_12],[REVIEW_WORD_ARTICLES_147,LEMON_WORD_CITRUS_173],[DRUM_PIC_PLAY_12]]</t>
@@ -294,13 +306,16 @@
     <t>[WORD_WREATH_544,WORD_ARTICLES_147,WORD_DRIVING_49,PIC_PLAY_12,WORD_SNOW_77]</t>
   </si>
   <si>
+    <t>SORT_GAME_LEVEL_REWARD_6</t>
+  </si>
+  <si>
     <t>DECK_CLEAN_5</t>
   </si>
   <si>
     <t>TID_SORT_GAME_LEVEL_6_DESC</t>
   </si>
   <si>
-    <t>SORT_GAME_LEVE_7_BOARD_1</t>
+    <t>SORT_GAME_LEVEL_7_BOARD_1</t>
   </si>
   <si>
     <t>[6]</t>
@@ -312,13 +327,16 @@
     <t>[WORD_SEASONS_18,WORD_FISHING_20,WORD_CITRUS_173,WORD_LEGS_322,PIC_HATS_11]</t>
   </si>
   <si>
+    <t>SORT_GAME_LEVEL_REWARD_7</t>
+  </si>
+  <si>
     <t>DECK_CLEAN_6</t>
   </si>
   <si>
     <t>TID_SORT_GAME_LEVEL_7_DESC</t>
   </si>
   <si>
-    <t>SORT_GAME_LEVE_8_BOARD_1</t>
+    <t>SORT_GAME_LEVEL_8_BOARD_1</t>
   </si>
   <si>
     <t>[4,11]</t>
@@ -330,13 +348,19 @@
     <t>[WORD_RAINY_100,WORD_MATERIAL_27,WORD_DATE_87,WORD_DEVICE_38,PIC_CHAIR_10,WORD_COAST_969]</t>
   </si>
   <si>
+    <t>SORT_GAME_LEVEL_REWARD_8</t>
+  </si>
+  <si>
     <t>DECK_CLEAN_7</t>
   </si>
   <si>
     <t>TID_SORT_GAME_LEVEL_8_DESC</t>
   </si>
   <si>
-    <t>SORT_GAME_LEVE_9_BOARD_1</t>
+    <t>SORT_GAME_LEVEL_9_BOARD_1</t>
+  </si>
+  <si>
+    <t>TASK_FIX_FLOOR_SCREEN</t>
   </si>
   <si>
     <t>[8,12]</t>
@@ -348,13 +372,16 @@
     <t>[WORD_CAMPING_221,WORD_FAME_161,PIC_CLEANING_13,WORD_CROWN_194,WORD_DEFENSE_277,WORD_RACING_182]</t>
   </si>
   <si>
+    <t>SORT_GAME_LEVEL_REWARD_9</t>
+  </si>
+  <si>
     <t>DECK_CLEAN_8</t>
   </si>
   <si>
     <t>TID_SORT_GAME_LEVEL_9_DESC</t>
   </si>
   <si>
-    <t>SORT_GAME_LEVE_10_BOARD_1</t>
+    <t>SORT_GAME_LEVEL_10_BOARD_1</t>
   </si>
   <si>
     <t>[2,3]</t>
@@ -366,13 +393,16 @@
     <t>[WORD_GYM_164,WORD_COZY_58,WORD_COMBAT_121,WORD_LUXURY_133,PIC_DECK_4,WORD_SLIDING_339,WORD_JUSTICE_310]</t>
   </si>
   <si>
+    <t>SORT_GAME_LEVEL_REWARD_10</t>
+  </si>
+  <si>
     <t>DECK_CLEAN_COMMON</t>
   </si>
   <si>
     <t>TID_SORT_GAME_LEVEL_DEFAULT_DESC</t>
   </si>
   <si>
-    <t>SORT_GAME_LEVE_11_BOARD_1</t>
+    <t>SORT_GAME_LEVEL_11_BOARD_1</t>
   </si>
   <si>
     <t>[[COAL_WORD_FUELS_190],[GEMINI_PIC_ZODIAC_5,MYTH_WORD_LEGENDS_291],[TALE_WORD_LEGENDS_291,FALSIFY_WORD_LIE_492],[BIKE_WORD_STREET_768,COMPASS_WORD_NAVIGATE_230],[TAURUS_PIC_ZODIAC_5,SEXTANT_WORD_NAVIGATE_230],[YOGURT_WORD_DAIRY_30],[YOGA_WORD_FITNESS_110,PILATES_WORD_FITNESS_110],[GASOLINE_WORD_FUELS_190,SPIDER_WORD_NO_BONES_289],[FABLE_WORD_LEGENDS_291],[ARIES_PIC_ZODIAC_5],[CREAM_WORD_DAIRY_30],[WALRUS_WORD_ARCTIC_180],[SIGNPOST_WORD_NAVIGATE_230],[BUTTER_WORD_DAIRY_30],[PROPANE_WORD_FUELS_190],[POLAR_BEAR_WORD_ARCTIC_180,SNOWY_OWL_WORD_ARCTIC_180],[REINDEER_WORD_ARCTIC_180],[DIESEL_WORD_FUELS_190],[GYM_WORD_FITNESS_110],[LEAGUE_WORD_UNITE_126],[KEROSENE_WORD_FUELS_190],[BRICK_WORD_STREET_768],[WOUND_WORD_INJURIES_249],[CORNER_WORD_STREET_768],[DRIVER_WORD_STREET_768]]</t>
@@ -381,7 +411,10 @@
     <t>[WORD_DAIRY_30,WORD_STREET_768,WORD_FUELS_190,PIC_ZODIAC_5,WORD_ARCTIC_180]</t>
   </si>
   <si>
-    <t>SORT_GAME_LEVE_12_BOARD_1</t>
+    <t>SORT_GAME_LEVEL_REWARD_11</t>
+  </si>
+  <si>
+    <t>SORT_GAME_LEVEL_12_BOARD_1</t>
   </si>
   <si>
     <t>[3,4]</t>
@@ -393,7 +426,13 @@
     <t>[WORD_NAVIGATE_230,WORD_LIE_492,PIC_TOOLBOX_6,WORD_LEGENDS_291,PIC_VEGGIE_8,WORD_UNITE_126]</t>
   </si>
   <si>
-    <t>SORT_GAME_LEVE_13_BOARD_1</t>
+    <t>SORT_GAME_LEVEL_REWARD_12</t>
+  </si>
+  <si>
+    <t>SORT_GAME_LEVEL_13_BOARD_1</t>
+  </si>
+  <si>
+    <t>TASK_FIX_COSTUME_SHOP</t>
   </si>
   <si>
     <t>[[GYM_WORD_FITNESS_110,WESTERN_WORD_CINEMA_6],[BARBERRY_WORD_BERRY_116,VICTORIA_WORD_WATER_152],[JOGGING_WORD_FITNESS_110],[OXFORDS_PIC_SHOES_14,PEONY_WORD_FLOWERS_4],[INDIA_PIC_MAP_15,PURSUIT_WORD_QUEST_680],[HEBREW_WORD_LANGUAGE_70,ITALIAN_WORD_LANGUAGE_70],[FRACTURE_WORD_INJURIES_249,QUEENS_WORD_NEW_YORK_287],[BARNACLE_WORD_NO_BONES_289],[SONGKRAN_WORD_FESTIVAL_270,DURIAN_WORD_SPIKY_78],[AUSTRALIA_PIC_MAP_15],[PREACHER_WORD_PRIEST_1019],[HOLI_WORD_FESTIVAL_270],[BRUISE_WORD_INJURIES_249,HEELS_PIC_SHOES_14],[WORM_WORD_NO_BONES_289],[YOGA_WORD_FITNESS_110],[DIWALI_WORD_FESTIVAL_270],[WORKOUT_WORD_FITNESS_110,DRAMA_WORD_CINEMA_6],[CARDIO_WORD_FITNESS_110,FLATS_PIC_SHOES_14],[SPIDER_WORD_NO_BONES_289],[PILATES_WORD_FITNESS_110],[ITALY_PIC_MAP_15],[SQUID_WORD_NO_BONES_289],[SPRAIN_WORD_INJURIES_249],[WOUND_WORD_INJURIES_249],[STARFISH_WORD_NO_BONES_289,BOOTS_PIC_SHOES_14]]</t>
@@ -402,7 +441,10 @@
     <t>[WORD_FITNESS_110,PIC_MAP_15,WORD_NO_BONES_289,WORD_INJURIES_249,WORD_FESTIVAL_270,PIC_SHOES_14]</t>
   </si>
   <si>
-    <t>SORT_GAME_LEVE_14_BOARD_1</t>
+    <t>SORT_GAME_LEVEL_REWARD_13</t>
+  </si>
+  <si>
+    <t>SORT_GAME_LEVEL_14_BOARD_1</t>
   </si>
   <si>
     <t>[6,9]</t>
@@ -414,7 +456,10 @@
     <t>[WORD_FLOWERS_4,WORD_CINEMA_6,WORD_QUEST_680,WORD_PATTERN_188,WORD_WATER_152,PIC_SEAFOOD_17,PIC_BIRD_16]</t>
   </si>
   <si>
-    <t>SORT_GAME_LEVE_15_BOARD_1</t>
+    <t>SORT_GAME_LEVEL_REWARD_14</t>
+  </si>
+  <si>
+    <t>SORT_GAME_LEVEL_15_BOARD_1</t>
   </si>
   <si>
     <t>[4,8]</t>
@@ -426,7 +471,10 @@
     <t>[WORD_NEW_YORK_287,WORD_LANGUAGE_70,WORD_DIVISION_242,WORD_PRIEST_1019,PIC_DOGS_18,WORD_SPIKY_78,WORD_BERRY_116]</t>
   </si>
   <si>
-    <t>SORT_GAME_LEVE_16_BOARD_1</t>
+    <t>SORT_GAME_LEVEL_REWARD_15</t>
+  </si>
+  <si>
+    <t>SORT_GAME_LEVEL_16_BOARD_1</t>
   </si>
   <si>
     <t>[11]</t>
@@ -438,7 +486,13 @@
     <t>[WORD_MEDITATE_160,WORD_AUCTION_215,WORD_AIRPORT_29,WORD_MUSCLES_112,WORD_SHIP_62,PIC_EATS_19,WORD_HIPPIE_349]</t>
   </si>
   <si>
-    <t>SORT_GAME_LEVE_17_BOARD_1</t>
+    <t>SORT_GAME_LEVEL_REWARD_16</t>
+  </si>
+  <si>
+    <t>SORT_GAME_LEVEL_17_BOARD_1</t>
+  </si>
+  <si>
+    <t>TASK_BUILD_SERVICE_CENTER</t>
   </si>
   <si>
     <t>[4,6]</t>
@@ -450,7 +504,10 @@
     <t>[WORD_PILLS_99,WORD_EXPLORER_51,PIC_FOLKLORE_21,PIC_BUILD_20,WORD_CHESS_17,WORD_LANDMARK_948,WORD_FOOTWEAR_46]</t>
   </si>
   <si>
-    <t>SORT_GAME_LEVE_18_BOARD_1</t>
+    <t>SORT_GAME_LEVEL_REWARD_17</t>
+  </si>
+  <si>
+    <t>SORT_GAME_LEVEL_18_BOARD_1</t>
   </si>
   <si>
     <t>[[JAMAICA_WORD_ISLANDS_21,PIER_WORD_HARBOR_764],[SICILY_WORD_ISLANDS_21,ADAMS_WORD_LEADER_196],[IBIZA_WORD_ISLANDS_21,BLUSH_WORD_MAKEUP_120],[ICELAND_WORD_ISLANDS_21,MARINA_WORD_HARBOR_764],[BAY_WORD_HARBOR_764,PEEL_WORD_MAKEUP_120],[BARBADOS_WORD_ISLANDS_21,VESSEL_WORD_HARBOR_764],[STEER_WORD_WHEEL_890,POWDER_WORD_MAKEUP_120],[BARRE_WORD_BALLET_125,SAMURAI_WORD_WARRIORS_491],[POINTE_WORD_BALLET_125,FORTUNE_WORD_WHEEL_890],[TSUNAMI_WORD_DISASTER_148,BUST_WORD_SCULPT_64],[COAST_WORD_HARBOR_764,PEACH_PIC_DRUPES_22],[HUBCAP_WORD_WHEEL_890,RESEARCH_WORD_PHD_296],[WHARF_WORD_HARBOR_764,PERCH_WORD_FISH_31],[BALI_WORD_ISLANDS_21,CHERRY_PIC_DRUPES_22],[TUTU_WORD_BALLET_125,MARLIN_WORD_FISH_31],[HAWAII_WORD_ISLANDS_21,SANDWICH_PIC_PICNIC_23],[APRICOT_PIC_DRUPES_22,TUNA_WORD_FISH_31],[PLUM_PIC_DRUPES_22,GOLDFISH_WORD_FISH_31],[CRETE_WORD_ISLANDS_21,BASKET_PIC_PICNIC_23],[VAPOR_WORD_FOG_76,GROUPER_WORD_FISH_31],[FLOOD_WORD_DISASTER_148,BLANKET_PIC_PICNIC_23],[AXLE_WORD_WHEEL_890,SMOG_WORD_FOG_76],[TIRE_WORD_WHEEL_890,HAZE_WORD_FOG_76],[TORNADO_WORD_DISASTER_148,ANTS_PIC_PICNIC_23],[MONUMENT_WORD_SCULPT_64,JUMP_WORD_MOVEMENT_52]]</t>
@@ -459,7 +516,10 @@
     <t>[WORD_DISASTER_148,WORD_HARBOR_764,WORD_ISLANDS_21,WORD_BALLET_125,WORD_WHEEL_890,PIC_DRUPES_22,PIC_PICNIC_23]</t>
   </si>
   <si>
-    <t>SORT_GAME_LEVE_19_BOARD_1</t>
+    <t>SORT_GAME_LEVEL_REWARD_18</t>
+  </si>
+  <si>
+    <t>SORT_GAME_LEVEL_19_BOARD_1</t>
   </si>
   <si>
     <t>[[BUSH_WORD_LEADER_196,REAGAN_WORD_LEADER_196],[LINCOLN_WORD_LEADER_196,MARLIN_WORD_FISH_31],[STATUE_WORD_SCULPT_64,GOLDFISH_WORD_FISH_31],[PAELLA_WORD_RICE_342,CAPYBARA_WORD_RODENTS_141],[BLUSH_WORD_MAKEUP_120,MIST_WORD_FOG_76],[THESIS_WORD_PHD_296,LOBE_WORD_BRAIN_106],[PALETTE_WORD_MAKEUP_120,KENNEDY_WORD_LEADER_196],[FIGURINE_WORD_SCULPT_64,CORTEX_WORD_BRAIN_106],[MONUMENT_WORD_SCULPT_64,GYRUS_WORD_BRAIN_106],[RESEARCH_WORD_PHD_296,HAY_WORD_FARMING_333],[CONGEE_WORD_RICE_342,COMPOST_WORD_FARMING_333],[TUBA_PIC_WIND_25,PADDOCK_WORD_FARMING_333],[SPONGE_WORD_MAKEUP_120,ADAMS_WORD_LEADER_196],[SUSHI_WORD_RICE_342,ASSASSIN_WORD_WARRIORS_491],[CAKE_PIC_PASTRY_24,RONIN_WORD_WARRIORS_491],[BUST_WORD_SCULPT_64,OBAMA_WORD_LEADER_196],[POWDER_WORD_MAKEUP_120,CLINTON_WORD_LEADER_196],[RISOTTO_WORD_RICE_342,BIDEN_WORD_LEADER_196],[DEGREE_WORD_PHD_296,NINJA_WORD_WARRIORS_491],[SERUM_WORD_MAKEUP_120,SHINOBI_WORD_WARRIORS_491],[PIE_PIC_PASTRY_24,TEMPERA_WORD_PAINTING_340],[PROFITEROLE_PIC_PASTRY_24,OIL_WORD_PAINTING_340],[BUGLE_PIC_WIND_25,VOTER_WORD_ELECT_193],[FLUTE_PIC_WIND_25,PAPYRUS_WORD_EGYPT_114],[PEEL_WORD_MAKEUP_120,SAMURAI_WORD_WARRIORS_491]]</t>
@@ -468,7 +528,10 @@
     <t>[WORD_SCULPT_64,WORD_RICE_342,WORD_PHD_296,WORD_LEADER_196,WORD_MAKEUP_120,PIC_PASTRY_24,PIC_WIND_25,WORD_WARRIORS_491]</t>
   </si>
   <si>
-    <t>SORT_GAME_LEVE_20_BOARD_1</t>
+    <t>SORT_GAME_LEVEL_REWARD_19</t>
+  </si>
+  <si>
+    <t>SORT_GAME_LEVEL_20_BOARD_1</t>
   </si>
   <si>
     <t>[3,7,8]</t>
@@ -480,7 +543,13 @@
     <t>[WORD_FOG_76,WORD_MOVEMENT_52,WORD_FISH_31,WORD_LEATHER_480,PIC_STRINGS_27,WORD_BRAIN_106,WORD_RODENTS_141,PIC_MALL_26]</t>
   </si>
   <si>
-    <t>SORT_GAME_LEVE_21_BOARD_1</t>
+    <t>SORT_GAME_LEVEL_REWARD_20</t>
+  </si>
+  <si>
+    <t>SORT_GAME_LEVEL_21_BOARD_1</t>
+  </si>
+  <si>
+    <t>TASK_BUILD_FLOOR</t>
   </si>
   <si>
     <t>[2,10]</t>
@@ -492,7 +561,10 @@
     <t>[WORD_MEMES_620,PIC_JEWELRY_28,WORD_AIRCRAFT_174,WORD_ELECT_193,WORD_EGYPT_114,WORD_FARMING_333,WORD_PAINTING_340]</t>
   </si>
   <si>
-    <t>SORT_GAME_LEVE_22_BOARD_1</t>
+    <t>SORT_GAME_LEVEL_REWARD_21</t>
+  </si>
+  <si>
+    <t>SORT_GAME_LEVEL_22_BOARD_1</t>
   </si>
   <si>
     <t>[10,11]</t>
@@ -504,7 +576,10 @@
     <t>[WORD_GREECE_359,PIC_REPTILES_30,WORD_PLANET_90,WORD_ROBOT_354,WORD_ITALY_376,PIC_FLOWERS_29,WORD_GAMER_36,WORD_VOICES_439]</t>
   </si>
   <si>
-    <t>SORT_GAME_LEVE_23_BOARD_1</t>
+    <t>SORT_GAME_LEVEL_REWARD_22</t>
+  </si>
+  <si>
+    <t>SORT_GAME_LEVEL_23_BOARD_1</t>
   </si>
   <si>
     <t>[3,5]</t>
@@ -516,7 +591,10 @@
     <t>[WORD_HOCKEY_86,WORD_DANCES_24,WORD_RIVERS_959,PIC_INSECTS_32,WORD_LAKES_365,PIC_GEMSTONE_31,WORD_COASTAL_882,WORD_GUITAR_122]</t>
   </si>
   <si>
-    <t>SORT_GAME_LEVE_24_BOARD_1</t>
+    <t>SORT_GAME_LEVEL_REWARD_23</t>
+  </si>
+  <si>
+    <t>SORT_GAME_LEVEL_24_BOARD_1</t>
   </si>
   <si>
     <t>[5,7,12]</t>
@@ -528,7 +606,10 @@
     <t>[WORD_BIOMES_135,WORD_ARMY_156,WORD_ACTOR_89,WORD_VIEWS_410,PIC_TAROT_48,WORD_CAMERA_73,WORD_LINGUIST_162,PIC_WESTERN_34]</t>
   </si>
   <si>
-    <t>SORT_GAME_LEVE_25_BOARD_1</t>
+    <t>SORT_GAME_LEVEL_REWARD_24</t>
+  </si>
+  <si>
+    <t>SORT_GAME_LEVEL_25_BOARD_1</t>
   </si>
   <si>
     <t>[2,7,12]</t>
@@ -540,7 +621,13 @@
     <t>[WORD_POETRY_440,WORD_EQUIDAE_475,WORD_PARTICLE_281,WORD_CHIMERA_795,WORD_RAP_151,PIC_BEACH_36,PIC_ICONS_79,WORD_BEANS_219]</t>
   </si>
   <si>
-    <t>SORT_GAME_LEVE_26_BOARD_1</t>
+    <t>SORT_GAME_LEVEL_REWARD_25</t>
+  </si>
+  <si>
+    <t>SORT_GAME_LEVEL_26_BOARD_1</t>
+  </si>
+  <si>
+    <t>TASK_BUILD_CHAIR_SOFA</t>
   </si>
   <si>
     <t>[2,5]</t>
@@ -552,7 +639,10 @@
     <t>[WORD_CUSTOMS_592,WORD_LEAVES_1055,WORD_PLAY_223,PIC_SUPPLIES_70,WORD_EVALUATE_651,PIC_SPACE_38,WORD_PHASE_57,WORD_SHAFT_331]</t>
   </si>
   <si>
-    <t>SORT_GAME_LEVE_27_BOARD_1</t>
+    <t>SORT_GAME_LEVEL_REWARD_26</t>
+  </si>
+  <si>
+    <t>SORT_GAME_LEVEL_27_BOARD_1</t>
   </si>
   <si>
     <t>[7,12]</t>
@@ -564,7 +654,10 @@
     <t>[WORD_ZEN_549,PIC_BIRTHDAY_40,WORD_BEARDS_681,WORD_OPERA_760,WORD_ENERGY_145,WORD_OPTICS_229,PIC_SEA_FISH_39,WORD_PLANE_139]</t>
   </si>
   <si>
-    <t>SORT_GAME_LEVE_28_BOARD_1</t>
+    <t>SORT_GAME_LEVEL_REWARD_27</t>
+  </si>
+  <si>
+    <t>SORT_GAME_LEVEL_28_BOARD_1</t>
   </si>
   <si>
     <t>[7,10,12]</t>
@@ -576,7 +669,10 @@
     <t>[PIC_AQUATICS_78,WORD_BREEDS_940,WORD_ALARM_1031,WORD_CIPHER_208,PIC_CHARGER_41,WORD_WILLIAM_165,WORD_SCREEN_1030,WORD_KNIGHT_34]</t>
   </si>
   <si>
-    <t>SORT_GAME_LEVE_29_BOARD_1</t>
+    <t>SORT_GAME_LEVEL_REWARD_28</t>
+  </si>
+  <si>
+    <t>SORT_GAME_LEVEL_29_BOARD_1</t>
   </si>
   <si>
     <t>[1,4,9]</t>
@@ -588,7 +684,10 @@
     <t>[WORD_DISHWARE_829,WORD_EARTH_831,WORD_POND_830,WORD_YINYANG_721,WORD_ELEMENTS_107,PIC_BURGER_44,PIC_WHISKERS_43,WORD_HORMONES_259,WORD_FOODIE_726]</t>
   </si>
   <si>
-    <t>SORT_GAME_LEVE_30_BOARD_1</t>
+    <t>SORT_GAME_LEVEL_REWARD_29</t>
+  </si>
+  <si>
+    <t>SORT_GAME_LEVEL_30_BOARD_1</t>
   </si>
   <si>
     <t>[1,2,11]</t>
@@ -600,7 +699,13 @@
     <t>[WORD_SINGING_1054,PIC_SHAPES_46,WORD_DRUM_518,WORD_BIRDS_80,PIC_DRINKS_45,WORD_HOUSE_40,WORD_GENETICS_1060,WORD_SKINCARE_984,WORD_ARTIFACT_276]</t>
   </si>
   <si>
-    <t>SORT_GAME_LEVE_31_BOARD_1</t>
+    <t>SORT_GAME_LEVEL_REWARD_30</t>
+  </si>
+  <si>
+    <t>SORT_GAME_LEVEL_31_BOARD_1</t>
+  </si>
+  <si>
+    <t>TASK_BUILD_PLANT</t>
   </si>
   <si>
     <t>[8,9]</t>
@@ -612,7 +717,10 @@
     <t>[WORD_CARRIAGE_800,WORD_PYRAMIDS_330,WORD_EARTH_831,WORD_GAITS_810,PIC_RODENTS_33,WORD_ORGANS_412,PIC_LUXURY_47,WORD_LESSONS_94]</t>
   </si>
   <si>
-    <t>SORT_GAME_LEVE_32_BOARD_1</t>
+    <t>SORT_GAME_LEVEL_REWARD_31</t>
+  </si>
+  <si>
+    <t>SORT_GAME_LEVEL_32_BOARD_1</t>
   </si>
   <si>
     <t>[3,4,7]</t>
@@ -624,7 +732,10 @@
     <t>[WORD_SAW_88,WORD_VIOLINS_845,WORD_CONCRETE_601,WORD_NUCLEAR_366,WORD_CASTLE_485,PIC_BABIES_49,PIC_SAILOR_50,WORD_CANINES_168]</t>
   </si>
   <si>
-    <t>SORT_GAME_LEVE_33_BOARD_1</t>
+    <t>SORT_GAME_LEVEL_REWARD_32</t>
+  </si>
+  <si>
+    <t>SORT_GAME_LEVEL_33_BOARD_1</t>
   </si>
   <si>
     <t>[3,4,9]</t>
@@ -636,7 +747,10 @@
     <t>[PIC_CANDY_51,WORD_PRIMATES_149,PIC_KEYS_52,WORD_FINANCE_227,WORD_GRAMMAR_861,WORD_MINDS_82,WORD_NETWORK_588,WORD_CODING_150]</t>
   </si>
   <si>
-    <t>SORT_GAME_LEVE_34_BOARD_1</t>
+    <t>SORT_GAME_LEVEL_REWARD_33</t>
+  </si>
+  <si>
+    <t>SORT_GAME_LEVEL_34_BOARD_1</t>
   </si>
   <si>
     <t>[2,7,9]</t>
@@ -648,7 +762,10 @@
     <t>[WORD_TOYS_154,PIC_LAWN_53,WORD_BREADS_102,PIC_3D_54,WORD_TAROT_417,WORD_WESTERN_317,WORD_SPICY_136,WORD_PAGANISM_469,WORD_STUDIES_169]</t>
   </si>
   <si>
-    <t>SORT_GAME_LEVE_35_BOARD_1</t>
+    <t>SORT_GAME_LEVEL_REWARD_34</t>
+  </si>
+  <si>
+    <t>SORT_GAME_LEVEL_35_BOARD_1</t>
   </si>
   <si>
     <t>[3,10,11]</t>
@@ -660,7 +777,13 @@
     <t>[WORD_MINERALS_253,WORD_PREFIX_922,WORD_GRAPE_177,PIC_VAMPIRE_55,PIC_LANDMARK_56,WORD_ZODIAC_59,WORD_FAMILIES_234,WORD_ALKANES_641,WORD_HOT_DOG_201]</t>
   </si>
   <si>
-    <t>SORT_GAME_LEVE_36_BOARD_1</t>
+    <t>SORT_GAME_LEVEL_REWARD_35</t>
+  </si>
+  <si>
+    <t>SORT_GAME_LEVEL_36_BOARD_1</t>
+  </si>
+  <si>
+    <t>TASK_BUILD_ARCH</t>
   </si>
   <si>
     <t>[1,2,3]</t>
@@ -672,7 +795,10 @@
     <t>[WORD_VIOLIN_508,PIC_EGYPT_37,WORD_MUSHROOM_178,WORD_BUILD_384,WORD_TODDLER_231,WORD_CULTURES_487,WORD_INDUSTRY_921,PIC_DESERT_57]</t>
   </si>
   <si>
-    <t>SORT_GAME_LEVE_37_BOARD_1</t>
+    <t>SORT_GAME_LEVEL_REWARD_36</t>
+  </si>
+  <si>
+    <t>SORT_GAME_LEVEL_37_BOARD_1</t>
   </si>
   <si>
     <t>[5,9,11]</t>
@@ -684,7 +810,10 @@
     <t>[WORD_MAILMAN_63,WORD_FLU_251,WORD_ALLOY_264,WORD_HAIR_245,WORD_CHEESE_108,PIC_PURPLE_59,WORD_SPEAK_244,PIC_DECOR_77]</t>
   </si>
   <si>
-    <t>SORT_GAME_LEVE_38_BOARD_1</t>
+    <t>SORT_GAME_LEVEL_REWARD_37</t>
+  </si>
+  <si>
+    <t>SORT_GAME_LEVEL_38_BOARD_1</t>
   </si>
   <si>
     <t>[3,5,6]</t>
@@ -696,7 +825,10 @@
     <t>[WORD_SHOVEL_261,WORD_EYE_260,PIC_GYM_62,PIC_RAIN_61,WORD_CAPITALS_119,WORD_MEDIEVAL_228,WORD_DYNASTY_991,WORD_JOBS_42]</t>
   </si>
   <si>
-    <t>SORT_GAME_LEVE_39_BOARD_1</t>
+    <t>SORT_GAME_LEVEL_REWARD_38</t>
+  </si>
+  <si>
+    <t>SORT_GAME_LEVEL_39_BOARD_1</t>
   </si>
   <si>
     <t>[3,7,12]</t>
@@ -708,7 +840,10 @@
     <t>[WORD_MAP_32,WORD_STARS_236,WORD_PRISONER_312,WORD_AI_238,WORD_PETS_2,PIC_CAMPING_64,PIC_PAIRS_63,WORD_BURGER_8,WORD_GEMSTONE_186]</t>
   </si>
   <si>
-    <t>SORT_GAME_LEVE_40_BOARD_1</t>
+    <t>SORT_GAME_LEVEL_REWARD_39</t>
+  </si>
+  <si>
+    <t>SORT_GAME_LEVEL_40_BOARD_1</t>
   </si>
   <si>
     <t>[1,9,12]</t>
@@ -718,6 +853,9 @@
   </si>
   <si>
     <t>[WORD_DRINKS_16,WORD_DISPLAY_486,WORD_SYMPHONY_210,PIC_XMAS_65,WORD_MAPS_1022,WORD_LOCK_321,WORD_METAL_272,PIC_MAIL_66,WORD_SPACE_314]</t>
+  </si>
+  <si>
+    <t>SORT_GAME_LEVEL_REWARD_40</t>
   </si>
 </sst>
 </file>
@@ -1427,7 +1565,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1442,6 +1580,12 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment/>
@@ -1450,15 +1594,6 @@
           <etc:displayText val="2"/>
         </ext>
       </extLst>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1955,7 +2090,7 @@
       <c r="M3" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="N3" s="9" t="s">
+      <c r="N3" s="8" t="s">
         <v>37</v>
       </c>
       <c r="O3" s="4" t="s">
@@ -2068,47 +2203,47 @@
       <c r="B6" s="6"/>
       <c r="C6" s="6"/>
       <c r="D6" s="6"/>
-      <c r="E6" s="7">
-        <v>1</v>
-      </c>
-      <c r="F6" s="7">
-        <v>1</v>
-      </c>
-      <c r="G6" s="7">
+      <c r="E6" s="5">
+        <v>1</v>
+      </c>
+      <c r="F6" s="5">
+        <v>1</v>
+      </c>
+      <c r="G6" s="5">
         <v>2</v>
       </c>
       <c r="H6" s="6"/>
-      <c r="I6" s="8">
-        <v>1</v>
-      </c>
-      <c r="J6" s="8" t="s">
+      <c r="I6" s="5">
+        <v>1</v>
+      </c>
+      <c r="J6" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="K6" s="8">
-        <v>2</v>
-      </c>
-      <c r="L6" s="8" t="s">
+      <c r="K6" s="5">
+        <v>2</v>
+      </c>
+      <c r="L6" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="M6" s="8" t="s">
+      <c r="M6" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="N6" s="7" t="s">
+      <c r="N6" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="O6" s="10" t="s">
+      <c r="O6" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="P6" s="11" t="s">
+      <c r="P6" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="Q6" s="7" t="s">
+      <c r="Q6" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="R6" s="13">
+      <c r="R6" s="12">
         <v>105</v>
       </c>
-      <c r="S6" s="13">
+      <c r="S6" s="12">
         <v>2</v>
       </c>
     </row>
@@ -2119,1923 +2254,1937 @@
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
-      <c r="E7" s="7">
-        <v>2</v>
-      </c>
-      <c r="F7" s="7">
-        <v>1</v>
-      </c>
-      <c r="G7" s="7">
+      <c r="E7" s="5">
+        <v>2</v>
+      </c>
+      <c r="F7" s="5">
+        <v>1</v>
+      </c>
+      <c r="G7" s="5">
         <v>3</v>
       </c>
       <c r="H7" s="6"/>
-      <c r="I7" s="8">
-        <v>1</v>
-      </c>
-      <c r="J7" s="8" t="s">
+      <c r="I7" s="5">
+        <v>1</v>
+      </c>
+      <c r="J7" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="K7" s="8">
-        <v>2</v>
-      </c>
-      <c r="L7" s="8" t="s">
+      <c r="K7" s="5">
+        <v>2</v>
+      </c>
+      <c r="L7" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="M7" s="8" t="s">
+      <c r="M7" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="N7" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="O7" s="10" t="s">
+      <c r="N7" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="P7" s="12" t="s">
+      <c r="O7" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="Q7" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="R7" s="13">
+      <c r="P7" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q7" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="R7" s="12">
         <v>125</v>
       </c>
-      <c r="S7" s="13">
+      <c r="S7" s="12">
         <v>2</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="50" customHeight="1" spans="1:19">
       <c r="A8" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B8" s="6"/>
       <c r="C8" s="6"/>
       <c r="D8" s="6"/>
-      <c r="E8" s="7">
+      <c r="E8" s="5">
         <v>3</v>
       </c>
-      <c r="F8" s="7">
-        <v>1</v>
-      </c>
-      <c r="G8" s="7">
+      <c r="F8" s="5">
+        <v>1</v>
+      </c>
+      <c r="G8" s="5">
         <v>4</v>
       </c>
       <c r="H8" s="6"/>
-      <c r="I8" s="8">
-        <v>1</v>
-      </c>
-      <c r="J8" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="K8" s="8">
-        <v>2</v>
-      </c>
-      <c r="L8" s="8" t="s">
+      <c r="I8" s="5">
+        <v>1</v>
+      </c>
+      <c r="J8" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="M8" s="8" t="s">
+      <c r="K8" s="5">
+        <v>2</v>
+      </c>
+      <c r="L8" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="N8" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="O8" s="10" t="s">
+      <c r="M8" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="P8" s="12" t="s">
+      <c r="N8" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="Q8" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="R8" s="13">
+      <c r="O8" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="P8" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q8" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="R8" s="12">
         <v>130</v>
       </c>
-      <c r="S8" s="13">
+      <c r="S8" s="12">
         <v>2</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="50" customHeight="1" spans="1:19">
       <c r="A9" s="5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
       <c r="D9" s="6"/>
-      <c r="E9" s="7">
+      <c r="E9" s="5">
         <v>4</v>
       </c>
-      <c r="F9" s="7">
-        <v>1</v>
-      </c>
-      <c r="G9" s="7">
+      <c r="F9" s="5">
+        <v>1</v>
+      </c>
+      <c r="G9" s="5">
         <v>5</v>
       </c>
       <c r="H9" s="6"/>
-      <c r="I9" s="8">
-        <v>2</v>
-      </c>
-      <c r="J9" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="K9" s="8">
-        <v>2</v>
-      </c>
-      <c r="L9" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="M9" s="8" t="s">
+      <c r="I9" s="5">
+        <v>2</v>
+      </c>
+      <c r="J9" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="N9" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="O9" s="10" t="s">
+      <c r="K9" s="5">
+        <v>2</v>
+      </c>
+      <c r="L9" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="P9" s="12" t="s">
+      <c r="M9" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="Q9" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="R9" s="13">
+      <c r="N9" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="O9" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="P9" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q9" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="R9" s="12">
         <v>130</v>
       </c>
-      <c r="S9" s="13">
+      <c r="S9" s="12">
         <v>2</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="50" customHeight="1" spans="1:19">
       <c r="A10" s="5" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B10" s="6"/>
       <c r="C10" s="6"/>
       <c r="D10" s="6"/>
-      <c r="E10" s="7">
+      <c r="E10" s="5">
         <v>5</v>
       </c>
-      <c r="F10" s="7">
-        <v>1</v>
-      </c>
-      <c r="G10" s="7">
+      <c r="F10" s="5">
+        <v>1</v>
+      </c>
+      <c r="G10" s="5">
         <v>6</v>
       </c>
       <c r="H10" s="6"/>
-      <c r="I10" s="8">
-        <v>2</v>
-      </c>
-      <c r="J10" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="K10" s="8">
-        <v>2</v>
-      </c>
-      <c r="L10" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="M10" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="N10" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="O10" s="10" t="s">
+      <c r="I10" s="5">
+        <v>2</v>
+      </c>
+      <c r="J10" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="P10" s="12" t="s">
+      <c r="K10" s="5">
+        <v>2</v>
+      </c>
+      <c r="L10" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="Q10" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="R10" s="13">
+      <c r="M10" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="N10" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="O10" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="P10" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q10" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="R10" s="12">
         <v>145</v>
       </c>
-      <c r="S10" s="13">
+      <c r="S10" s="12">
         <v>3</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="50" customHeight="1" spans="1:19">
       <c r="A11" s="5" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
       <c r="D11" s="6"/>
-      <c r="E11" s="7">
+      <c r="E11" s="5">
         <v>6</v>
       </c>
-      <c r="F11" s="7">
-        <v>1</v>
-      </c>
-      <c r="G11" s="7">
+      <c r="F11" s="5">
+        <v>1</v>
+      </c>
+      <c r="G11" s="5">
         <v>7</v>
       </c>
       <c r="H11" s="6"/>
-      <c r="I11" s="8">
-        <v>1</v>
-      </c>
-      <c r="J11" s="8" t="s">
+      <c r="I11" s="5">
+        <v>1</v>
+      </c>
+      <c r="J11" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="K11" s="8">
-        <v>2</v>
-      </c>
-      <c r="L11" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="M11" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="N11" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="O11" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="P11" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="Q11" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="R11" s="13">
+      <c r="K11" s="5">
+        <v>2</v>
+      </c>
+      <c r="L11" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="M11" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="N11" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="O11" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="P11" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q11" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="R11" s="12">
         <v>135</v>
       </c>
-      <c r="S11" s="13">
+      <c r="S11" s="12">
         <v>3</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="50" customHeight="1" spans="1:19">
       <c r="A12" s="5" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
       <c r="D12" s="6"/>
-      <c r="E12" s="7">
+      <c r="E12" s="5">
         <v>7</v>
       </c>
-      <c r="F12" s="7">
-        <v>1</v>
-      </c>
-      <c r="G12" s="7">
+      <c r="F12" s="5">
+        <v>1</v>
+      </c>
+      <c r="G12" s="5">
         <v>8</v>
       </c>
       <c r="H12" s="6"/>
-      <c r="I12" s="8">
-        <v>1</v>
-      </c>
-      <c r="J12" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="K12" s="8">
-        <v>2</v>
-      </c>
-      <c r="L12" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="M12" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="N12" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="O12" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="P12" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="Q12" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="R12" s="13">
+      <c r="I12" s="5">
+        <v>1</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="K12" s="5">
+        <v>2</v>
+      </c>
+      <c r="L12" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="M12" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="N12" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="O12" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="P12" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q12" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="R12" s="12">
         <v>125</v>
       </c>
-      <c r="S12" s="13">
+      <c r="S12" s="12">
         <v>3</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="50" customHeight="1" spans="1:19">
       <c r="A13" s="5" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
-      <c r="E13" s="7">
+      <c r="E13" s="5">
         <v>8</v>
       </c>
-      <c r="F13" s="7">
-        <v>1</v>
-      </c>
-      <c r="G13" s="7">
+      <c r="F13" s="5">
+        <v>1</v>
+      </c>
+      <c r="G13" s="5">
         <v>9</v>
       </c>
       <c r="H13" s="6"/>
-      <c r="I13" s="8">
-        <v>2</v>
-      </c>
-      <c r="J13" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="K13" s="8">
-        <v>2</v>
-      </c>
-      <c r="L13" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="M13" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="N13" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="O13" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="P13" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="Q13" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="R13" s="13">
+      <c r="I13" s="5">
+        <v>2</v>
+      </c>
+      <c r="J13" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="K13" s="5">
+        <v>2</v>
+      </c>
+      <c r="L13" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="M13" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="N13" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="O13" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="P13" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q13" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="R13" s="12">
         <v>140</v>
       </c>
-      <c r="S13" s="13">
+      <c r="S13" s="12">
         <v>3</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="50" customHeight="1" spans="1:19">
       <c r="A14" s="5" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
       <c r="D14" s="6"/>
-      <c r="E14" s="7">
+      <c r="E14" s="5">
         <v>9</v>
       </c>
-      <c r="F14" s="7">
-        <v>1</v>
-      </c>
-      <c r="G14" s="7">
+      <c r="F14" s="5">
+        <v>1</v>
+      </c>
+      <c r="G14" s="5">
         <v>10</v>
       </c>
-      <c r="H14" s="6"/>
-      <c r="I14" s="8">
-        <v>2</v>
-      </c>
-      <c r="J14" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="K14" s="8">
-        <v>2</v>
-      </c>
-      <c r="L14" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="M14" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="N14" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="O14" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="P14" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="Q14" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="R14" s="13">
+      <c r="H14" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="I14" s="5">
+        <v>2</v>
+      </c>
+      <c r="J14" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="K14" s="5">
+        <v>2</v>
+      </c>
+      <c r="L14" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="M14" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="N14" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="O14" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="P14" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q14" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="R14" s="12">
         <v>125</v>
       </c>
-      <c r="S14" s="13">
+      <c r="S14" s="12">
         <v>3</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" ht="50" customHeight="1" spans="1:19">
-      <c r="A15" s="5" t="s">
-        <v>108</v>
+      <c r="A15" s="7" t="s">
+        <v>117</v>
       </c>
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
-      <c r="E15" s="7">
+      <c r="E15" s="5">
         <v>10</v>
       </c>
-      <c r="F15" s="7">
-        <v>1</v>
-      </c>
-      <c r="G15" s="7">
+      <c r="F15" s="5">
+        <v>1</v>
+      </c>
+      <c r="G15" s="5">
         <v>11</v>
       </c>
       <c r="H15" s="6"/>
-      <c r="I15" s="8">
-        <v>2</v>
-      </c>
-      <c r="J15" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="K15" s="8">
-        <v>2</v>
-      </c>
-      <c r="L15" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="M15" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="N15" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="O15" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="P15" s="5" t="s">
-        <v>113</v>
+      <c r="I15" s="5">
+        <v>2</v>
+      </c>
+      <c r="J15" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="K15" s="5">
+        <v>2</v>
+      </c>
+      <c r="L15" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="M15" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="N15" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="O15" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="P15" s="7" t="s">
+        <v>123</v>
       </c>
       <c r="Q15" s="6"/>
-      <c r="R15" s="13">
+      <c r="R15" s="12">
         <v>135</v>
       </c>
-      <c r="S15" s="13">
+      <c r="S15" s="12">
         <v>3</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" ht="50" customHeight="1" spans="1:19">
-      <c r="A16" s="5" t="s">
-        <v>114</v>
+      <c r="A16" s="7" t="s">
+        <v>124</v>
       </c>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
       <c r="D16" s="6"/>
-      <c r="E16" s="7">
+      <c r="E16" s="5">
         <v>11</v>
       </c>
-      <c r="F16" s="7">
-        <v>1</v>
-      </c>
-      <c r="G16" s="7">
+      <c r="F16" s="5">
+        <v>1</v>
+      </c>
+      <c r="G16" s="5">
         <v>12</v>
       </c>
       <c r="H16" s="6"/>
-      <c r="I16" s="8">
-        <v>1</v>
-      </c>
-      <c r="J16" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="K16" s="8">
-        <v>2</v>
-      </c>
-      <c r="L16" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="M16" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="N16" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="O16" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="P16" s="5" t="s">
-        <v>113</v>
+      <c r="I16" s="5">
+        <v>1</v>
+      </c>
+      <c r="J16" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="K16" s="5">
+        <v>2</v>
+      </c>
+      <c r="L16" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="M16" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="N16" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="O16" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="P16" s="7" t="s">
+        <v>123</v>
       </c>
       <c r="Q16" s="6"/>
-      <c r="R16" s="13">
+      <c r="R16" s="12">
         <v>90</v>
       </c>
-      <c r="S16" s="13">
+      <c r="S16" s="12">
         <v>3</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" ht="50" customHeight="1" spans="1:19">
-      <c r="A17" s="5" t="s">
-        <v>117</v>
+      <c r="A17" s="7" t="s">
+        <v>128</v>
       </c>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
-      <c r="E17" s="7">
+      <c r="E17" s="5">
         <v>12</v>
       </c>
-      <c r="F17" s="7">
-        <v>1</v>
-      </c>
-      <c r="G17" s="7">
+      <c r="F17" s="5">
+        <v>1</v>
+      </c>
+      <c r="G17" s="5">
         <v>13</v>
       </c>
       <c r="H17" s="6"/>
-      <c r="I17" s="8">
-        <v>2</v>
-      </c>
-      <c r="J17" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="K17" s="8">
-        <v>2</v>
-      </c>
-      <c r="L17" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="M17" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="N17" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="O17" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="P17" s="5" t="s">
-        <v>113</v>
+      <c r="I17" s="5">
+        <v>2</v>
+      </c>
+      <c r="J17" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="K17" s="5">
+        <v>2</v>
+      </c>
+      <c r="L17" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="M17" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="N17" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="O17" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="P17" s="7" t="s">
+        <v>123</v>
       </c>
       <c r="Q17" s="6"/>
-      <c r="R17" s="13">
+      <c r="R17" s="12">
         <v>100</v>
       </c>
-      <c r="S17" s="13">
+      <c r="S17" s="12">
         <v>3</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" ht="50" customHeight="1" spans="1:19">
-      <c r="A18" s="5" t="s">
-        <v>121</v>
+      <c r="A18" s="7" t="s">
+        <v>133</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
       <c r="D18" s="6"/>
-      <c r="E18" s="7">
+      <c r="E18" s="5">
         <v>13</v>
       </c>
-      <c r="F18" s="7">
-        <v>1</v>
-      </c>
-      <c r="G18" s="7">
+      <c r="F18" s="5">
+        <v>1</v>
+      </c>
+      <c r="G18" s="5">
         <v>14</v>
       </c>
-      <c r="H18" s="6"/>
-      <c r="I18" s="8">
-        <v>2</v>
-      </c>
-      <c r="J18" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="K18" s="8">
-        <v>2</v>
-      </c>
-      <c r="L18" s="8" t="s">
+      <c r="H18" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="I18" s="5">
+        <v>2</v>
+      </c>
+      <c r="J18" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="K18" s="5">
+        <v>2</v>
+      </c>
+      <c r="L18" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="M18" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="N18" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="O18" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="M18" s="8" t="s">
+      <c r="P18" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="N18" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="O18" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="P18" s="5" t="s">
-        <v>113</v>
-      </c>
       <c r="Q18" s="6"/>
-      <c r="R18" s="13">
+      <c r="R18" s="12">
         <v>115</v>
       </c>
-      <c r="S18" s="13">
+      <c r="S18" s="12">
         <v>3</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" ht="50" customHeight="1" spans="1:19">
-      <c r="A19" s="5" t="s">
-        <v>124</v>
+      <c r="A19" s="7" t="s">
+        <v>138</v>
       </c>
       <c r="B19" s="6"/>
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
-      <c r="E19" s="7">
+      <c r="E19" s="5">
         <v>14</v>
       </c>
-      <c r="F19" s="7">
-        <v>1</v>
-      </c>
-      <c r="G19" s="7">
+      <c r="F19" s="5">
+        <v>1</v>
+      </c>
+      <c r="G19" s="5">
         <v>15</v>
       </c>
       <c r="H19" s="6"/>
-      <c r="I19" s="8">
-        <v>2</v>
-      </c>
-      <c r="J19" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="K19" s="8">
-        <v>2</v>
-      </c>
-      <c r="L19" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="M19" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="N19" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="O19" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="P19" s="5" t="s">
-        <v>113</v>
+      <c r="I19" s="5">
+        <v>2</v>
+      </c>
+      <c r="J19" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="K19" s="5">
+        <v>2</v>
+      </c>
+      <c r="L19" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="M19" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="N19" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="O19" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="P19" s="7" t="s">
+        <v>123</v>
       </c>
       <c r="Q19" s="6"/>
-      <c r="R19" s="13">
+      <c r="R19" s="12">
         <v>130</v>
       </c>
-      <c r="S19" s="13">
+      <c r="S19" s="12">
         <v>3</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" ht="50" customHeight="1" spans="1:19">
-      <c r="A20" s="5" t="s">
-        <v>128</v>
+      <c r="A20" s="7" t="s">
+        <v>143</v>
       </c>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
       <c r="D20" s="6"/>
-      <c r="E20" s="7">
+      <c r="E20" s="5">
         <v>15</v>
       </c>
-      <c r="F20" s="7">
-        <v>1</v>
-      </c>
-      <c r="G20" s="7">
+      <c r="F20" s="5">
+        <v>1</v>
+      </c>
+      <c r="G20" s="5">
         <v>16</v>
       </c>
       <c r="H20" s="6"/>
-      <c r="I20" s="8">
-        <v>2</v>
-      </c>
-      <c r="J20" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="K20" s="8">
-        <v>2</v>
-      </c>
-      <c r="L20" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="M20" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="N20" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="O20" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="P20" s="5" t="s">
-        <v>113</v>
+      <c r="I20" s="5">
+        <v>2</v>
+      </c>
+      <c r="J20" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="K20" s="5">
+        <v>2</v>
+      </c>
+      <c r="L20" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="M20" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="N20" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="O20" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="P20" s="7" t="s">
+        <v>123</v>
       </c>
       <c r="Q20" s="6"/>
-      <c r="R20" s="13">
+      <c r="R20" s="12">
         <v>150</v>
       </c>
-      <c r="S20" s="13">
+      <c r="S20" s="12">
         <v>3</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" ht="50" customHeight="1" spans="1:19">
-      <c r="A21" s="5" t="s">
-        <v>132</v>
+      <c r="A21" s="7" t="s">
+        <v>148</v>
       </c>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
       <c r="D21" s="6"/>
-      <c r="E21" s="7">
+      <c r="E21" s="5">
         <v>16</v>
       </c>
-      <c r="F21" s="7">
-        <v>1</v>
-      </c>
-      <c r="G21" s="7">
+      <c r="F21" s="5">
+        <v>1</v>
+      </c>
+      <c r="G21" s="5">
         <v>17</v>
       </c>
       <c r="H21" s="6"/>
-      <c r="I21" s="8">
-        <v>1</v>
-      </c>
-      <c r="J21" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="K21" s="8">
-        <v>2</v>
-      </c>
-      <c r="L21" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="M21" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="N21" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="O21" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="P21" s="5" t="s">
-        <v>113</v>
+      <c r="I21" s="5">
+        <v>1</v>
+      </c>
+      <c r="J21" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="K21" s="5">
+        <v>2</v>
+      </c>
+      <c r="L21" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="M21" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="N21" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="O21" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="P21" s="7" t="s">
+        <v>123</v>
       </c>
       <c r="Q21" s="6"/>
-      <c r="R21" s="13">
+      <c r="R21" s="12">
         <v>130</v>
       </c>
-      <c r="S21" s="13">
+      <c r="S21" s="12">
         <v>3</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" ht="50" customHeight="1" spans="1:19">
-      <c r="A22" s="5" t="s">
-        <v>136</v>
+      <c r="A22" s="7" t="s">
+        <v>153</v>
       </c>
       <c r="B22" s="6"/>
       <c r="C22" s="6"/>
       <c r="D22" s="6"/>
-      <c r="E22" s="7">
+      <c r="E22" s="5">
         <v>17</v>
       </c>
-      <c r="F22" s="7">
-        <v>1</v>
-      </c>
-      <c r="G22" s="7">
+      <c r="F22" s="5">
+        <v>1</v>
+      </c>
+      <c r="G22" s="5">
         <v>18</v>
       </c>
-      <c r="H22" s="6"/>
-      <c r="I22" s="8">
-        <v>2</v>
-      </c>
-      <c r="J22" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="K22" s="8">
-        <v>2</v>
-      </c>
-      <c r="L22" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="M22" s="8" t="s">
-        <v>139</v>
-      </c>
-      <c r="N22" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="O22" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="P22" s="5" t="s">
-        <v>113</v>
+      <c r="H22" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="I22" s="5">
+        <v>2</v>
+      </c>
+      <c r="J22" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="K22" s="5">
+        <v>2</v>
+      </c>
+      <c r="L22" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="M22" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="N22" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="O22" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="P22" s="7" t="s">
+        <v>123</v>
       </c>
       <c r="Q22" s="6"/>
-      <c r="R22" s="13">
+      <c r="R22" s="12">
         <v>130</v>
       </c>
-      <c r="S22" s="13">
+      <c r="S22" s="12">
         <v>3</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" ht="50" customHeight="1" spans="1:19">
-      <c r="A23" s="5" t="s">
-        <v>140</v>
+      <c r="A23" s="7" t="s">
+        <v>159</v>
       </c>
       <c r="B23" s="6"/>
       <c r="C23" s="6"/>
       <c r="D23" s="6"/>
-      <c r="E23" s="7">
+      <c r="E23" s="5">
         <v>18</v>
       </c>
-      <c r="F23" s="7">
-        <v>1</v>
-      </c>
-      <c r="G23" s="7">
+      <c r="F23" s="5">
+        <v>1</v>
+      </c>
+      <c r="G23" s="5">
         <v>19</v>
       </c>
       <c r="H23" s="6"/>
-      <c r="I23" s="8">
-        <v>2</v>
-      </c>
-      <c r="J23" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="K23" s="8">
-        <v>2</v>
-      </c>
-      <c r="L23" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="M23" s="8" t="s">
-        <v>142</v>
-      </c>
-      <c r="N23" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="O23" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="P23" s="5" t="s">
-        <v>113</v>
+      <c r="I23" s="5">
+        <v>2</v>
+      </c>
+      <c r="J23" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="K23" s="5">
+        <v>2</v>
+      </c>
+      <c r="L23" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="M23" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="N23" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="O23" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="P23" s="7" t="s">
+        <v>123</v>
       </c>
       <c r="Q23" s="6"/>
-      <c r="R23" s="13">
+      <c r="R23" s="12">
         <v>140</v>
       </c>
-      <c r="S23" s="13">
+      <c r="S23" s="12">
         <v>3</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" ht="50" customHeight="1" spans="1:19">
-      <c r="A24" s="5" t="s">
-        <v>143</v>
+      <c r="A24" s="7" t="s">
+        <v>163</v>
       </c>
       <c r="B24" s="6"/>
       <c r="C24" s="6"/>
       <c r="D24" s="6"/>
-      <c r="E24" s="7">
+      <c r="E24" s="5">
         <v>19</v>
       </c>
-      <c r="F24" s="7">
-        <v>1</v>
-      </c>
-      <c r="G24" s="7">
+      <c r="F24" s="5">
+        <v>1</v>
+      </c>
+      <c r="G24" s="5">
         <v>20</v>
       </c>
       <c r="H24" s="6"/>
-      <c r="I24" s="8">
-        <v>2</v>
-      </c>
-      <c r="J24" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="K24" s="8">
-        <v>2</v>
-      </c>
-      <c r="L24" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="M24" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="N24" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="O24" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="P24" s="5" t="s">
-        <v>113</v>
+      <c r="I24" s="5">
+        <v>2</v>
+      </c>
+      <c r="J24" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="K24" s="5">
+        <v>2</v>
+      </c>
+      <c r="L24" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="M24" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="N24" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="O24" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="P24" s="7" t="s">
+        <v>123</v>
       </c>
       <c r="Q24" s="6"/>
-      <c r="R24" s="13">
+      <c r="R24" s="12">
         <v>155</v>
       </c>
-      <c r="S24" s="13">
+      <c r="S24" s="12">
         <v>3</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" ht="50" customHeight="1" spans="1:19">
-      <c r="A25" s="5" t="s">
-        <v>146</v>
+      <c r="A25" s="7" t="s">
+        <v>167</v>
       </c>
       <c r="B25" s="6"/>
       <c r="C25" s="6"/>
       <c r="D25" s="6"/>
-      <c r="E25" s="7">
+      <c r="E25" s="5">
         <v>20</v>
       </c>
-      <c r="F25" s="7">
-        <v>1</v>
-      </c>
-      <c r="G25" s="7">
+      <c r="F25" s="5">
+        <v>1</v>
+      </c>
+      <c r="G25" s="5">
         <v>21</v>
       </c>
       <c r="H25" s="6"/>
-      <c r="I25" s="8">
+      <c r="I25" s="5">
         <v>3</v>
       </c>
-      <c r="J25" s="8" t="s">
-        <v>147</v>
-      </c>
-      <c r="K25" s="8">
-        <v>2</v>
-      </c>
-      <c r="L25" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="M25" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="N25" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="O25" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="P25" s="5" t="s">
-        <v>113</v>
+      <c r="J25" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="K25" s="5">
+        <v>2</v>
+      </c>
+      <c r="L25" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="M25" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="N25" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="O25" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="P25" s="7" t="s">
+        <v>123</v>
       </c>
       <c r="Q25" s="6"/>
-      <c r="R25" s="13">
+      <c r="R25" s="12">
         <v>165</v>
       </c>
-      <c r="S25" s="13">
+      <c r="S25" s="12">
         <v>3</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" ht="50" customHeight="1" spans="1:19">
-      <c r="A26" s="5" t="s">
-        <v>150</v>
+      <c r="A26" s="7" t="s">
+        <v>172</v>
       </c>
       <c r="B26" s="6"/>
       <c r="C26" s="6"/>
       <c r="D26" s="6"/>
-      <c r="E26" s="7">
+      <c r="E26" s="5">
         <v>21</v>
       </c>
-      <c r="F26" s="7">
-        <v>1</v>
-      </c>
-      <c r="G26" s="7">
+      <c r="F26" s="5">
+        <v>1</v>
+      </c>
+      <c r="G26" s="5">
         <v>22</v>
       </c>
-      <c r="H26" s="6"/>
-      <c r="I26" s="8">
-        <v>2</v>
-      </c>
-      <c r="J26" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="K26" s="8">
-        <v>2</v>
-      </c>
-      <c r="L26" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="M26" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="N26" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="O26" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="P26" s="5" t="s">
-        <v>113</v>
+      <c r="H26" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="I26" s="5">
+        <v>2</v>
+      </c>
+      <c r="J26" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="K26" s="5">
+        <v>2</v>
+      </c>
+      <c r="L26" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="M26" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="N26" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="O26" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="P26" s="7" t="s">
+        <v>123</v>
       </c>
       <c r="Q26" s="6"/>
-      <c r="R26" s="13">
+      <c r="R26" s="12">
         <v>140</v>
       </c>
-      <c r="S26" s="13">
+      <c r="S26" s="12">
         <v>3</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" ht="50" customHeight="1" spans="1:19">
-      <c r="A27" s="5" t="s">
-        <v>154</v>
+      <c r="A27" s="7" t="s">
+        <v>178</v>
       </c>
       <c r="B27" s="6"/>
       <c r="C27" s="6"/>
       <c r="D27" s="6"/>
-      <c r="E27" s="7">
+      <c r="E27" s="5">
         <v>22</v>
       </c>
-      <c r="F27" s="7">
-        <v>1</v>
-      </c>
-      <c r="G27" s="7">
+      <c r="F27" s="5">
+        <v>1</v>
+      </c>
+      <c r="G27" s="5">
         <v>23</v>
       </c>
       <c r="H27" s="6"/>
-      <c r="I27" s="8">
-        <v>2</v>
-      </c>
-      <c r="J27" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="K27" s="8">
-        <v>2</v>
-      </c>
-      <c r="L27" s="8" t="s">
-        <v>156</v>
-      </c>
-      <c r="M27" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="N27" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="O27" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="P27" s="5" t="s">
-        <v>113</v>
+      <c r="I27" s="5">
+        <v>2</v>
+      </c>
+      <c r="J27" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="K27" s="5">
+        <v>2</v>
+      </c>
+      <c r="L27" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="M27" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="N27" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="O27" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="P27" s="7" t="s">
+        <v>123</v>
       </c>
       <c r="Q27" s="6"/>
-      <c r="R27" s="13">
+      <c r="R27" s="12">
         <v>145</v>
       </c>
-      <c r="S27" s="13">
+      <c r="S27" s="12">
         <v>4</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" ht="50" customHeight="1" spans="1:19">
-      <c r="A28" s="5" t="s">
-        <v>158</v>
+      <c r="A28" s="7" t="s">
+        <v>183</v>
       </c>
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
       <c r="D28" s="6"/>
-      <c r="E28" s="7">
+      <c r="E28" s="5">
         <v>23</v>
       </c>
-      <c r="F28" s="7">
-        <v>1</v>
-      </c>
-      <c r="G28" s="7">
+      <c r="F28" s="5">
+        <v>1</v>
+      </c>
+      <c r="G28" s="5">
         <v>24</v>
       </c>
       <c r="H28" s="6"/>
-      <c r="I28" s="8">
-        <v>2</v>
-      </c>
-      <c r="J28" s="8" t="s">
-        <v>159</v>
-      </c>
-      <c r="K28" s="8">
-        <v>2</v>
-      </c>
-      <c r="L28" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="M28" s="8" t="s">
-        <v>161</v>
-      </c>
-      <c r="N28" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="O28" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="P28" s="5" t="s">
-        <v>113</v>
+      <c r="I28" s="5">
+        <v>2</v>
+      </c>
+      <c r="J28" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="K28" s="5">
+        <v>2</v>
+      </c>
+      <c r="L28" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="M28" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="N28" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="O28" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="P28" s="7" t="s">
+        <v>123</v>
       </c>
       <c r="Q28" s="6"/>
-      <c r="R28" s="13">
+      <c r="R28" s="12">
         <v>150</v>
       </c>
-      <c r="S28" s="13">
+      <c r="S28" s="12">
         <v>4</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" ht="50" customHeight="1" spans="1:19">
-      <c r="A29" s="5" t="s">
-        <v>162</v>
+      <c r="A29" s="7" t="s">
+        <v>188</v>
       </c>
       <c r="B29" s="6"/>
       <c r="C29" s="6"/>
       <c r="D29" s="6"/>
-      <c r="E29" s="7">
+      <c r="E29" s="5">
         <v>24</v>
       </c>
-      <c r="F29" s="7">
-        <v>1</v>
-      </c>
-      <c r="G29" s="7">
+      <c r="F29" s="5">
+        <v>1</v>
+      </c>
+      <c r="G29" s="5">
         <v>25</v>
       </c>
       <c r="H29" s="6"/>
-      <c r="I29" s="8">
+      <c r="I29" s="5">
         <v>3</v>
       </c>
-      <c r="J29" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="K29" s="8">
-        <v>2</v>
-      </c>
-      <c r="L29" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="M29" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="N29" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="O29" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="P29" s="5" t="s">
-        <v>113</v>
+      <c r="J29" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="K29" s="5">
+        <v>2</v>
+      </c>
+      <c r="L29" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="M29" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="N29" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="O29" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="P29" s="7" t="s">
+        <v>123</v>
       </c>
       <c r="Q29" s="6"/>
-      <c r="R29" s="13">
+      <c r="R29" s="12">
         <v>155</v>
       </c>
-      <c r="S29" s="13">
+      <c r="S29" s="12">
         <v>4</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" ht="50" customHeight="1" spans="1:19">
-      <c r="A30" s="5" t="s">
-        <v>166</v>
+      <c r="A30" s="7" t="s">
+        <v>193</v>
       </c>
       <c r="B30" s="6"/>
       <c r="C30" s="6"/>
       <c r="D30" s="6"/>
-      <c r="E30" s="7">
+      <c r="E30" s="5">
         <v>25</v>
       </c>
-      <c r="F30" s="7">
-        <v>1</v>
-      </c>
-      <c r="G30" s="7">
+      <c r="F30" s="5">
+        <v>1</v>
+      </c>
+      <c r="G30" s="5">
         <v>26</v>
       </c>
       <c r="H30" s="6"/>
-      <c r="I30" s="8">
+      <c r="I30" s="5">
         <v>3</v>
       </c>
-      <c r="J30" s="8" t="s">
-        <v>167</v>
-      </c>
-      <c r="K30" s="8">
-        <v>2</v>
-      </c>
-      <c r="L30" s="8" t="s">
-        <v>168</v>
-      </c>
-      <c r="M30" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="N30" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="O30" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="P30" s="5" t="s">
-        <v>113</v>
+      <c r="J30" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="K30" s="5">
+        <v>2</v>
+      </c>
+      <c r="L30" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="M30" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="N30" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="O30" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="P30" s="7" t="s">
+        <v>123</v>
       </c>
       <c r="Q30" s="6"/>
-      <c r="R30" s="13">
+      <c r="R30" s="12">
         <v>165</v>
       </c>
-      <c r="S30" s="13">
+      <c r="S30" s="12">
         <v>4</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" ht="50" customHeight="1" spans="1:19">
-      <c r="A31" s="5" t="s">
-        <v>170</v>
+      <c r="A31" s="7" t="s">
+        <v>198</v>
       </c>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
       <c r="D31" s="6"/>
-      <c r="E31" s="7">
+      <c r="E31" s="5">
         <v>26</v>
       </c>
-      <c r="F31" s="7">
-        <v>1</v>
-      </c>
-      <c r="G31" s="7">
+      <c r="F31" s="5">
+        <v>1</v>
+      </c>
+      <c r="G31" s="5">
         <v>27</v>
       </c>
-      <c r="H31" s="6"/>
-      <c r="I31" s="8">
-        <v>2</v>
-      </c>
-      <c r="J31" s="8" t="s">
-        <v>171</v>
-      </c>
-      <c r="K31" s="8">
-        <v>2</v>
-      </c>
-      <c r="L31" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="M31" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="N31" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="O31" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="P31" s="5" t="s">
-        <v>113</v>
+      <c r="H31" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="I31" s="5">
+        <v>2</v>
+      </c>
+      <c r="J31" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="K31" s="5">
+        <v>2</v>
+      </c>
+      <c r="L31" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="M31" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="N31" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="O31" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="P31" s="7" t="s">
+        <v>123</v>
       </c>
       <c r="Q31" s="6"/>
-      <c r="R31" s="13">
+      <c r="R31" s="12">
         <v>150</v>
       </c>
-      <c r="S31" s="13">
+      <c r="S31" s="12">
         <v>4</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" ht="50" customHeight="1" spans="1:19">
-      <c r="A32" s="5" t="s">
-        <v>174</v>
+      <c r="A32" s="7" t="s">
+        <v>204</v>
       </c>
       <c r="B32" s="6"/>
       <c r="C32" s="6"/>
       <c r="D32" s="6"/>
-      <c r="E32" s="7">
+      <c r="E32" s="5">
         <v>27</v>
       </c>
-      <c r="F32" s="7">
-        <v>1</v>
-      </c>
-      <c r="G32" s="7">
+      <c r="F32" s="5">
+        <v>1</v>
+      </c>
+      <c r="G32" s="5">
         <v>28</v>
       </c>
       <c r="H32" s="6"/>
-      <c r="I32" s="8">
-        <v>2</v>
-      </c>
-      <c r="J32" s="8" t="s">
-        <v>175</v>
-      </c>
-      <c r="K32" s="8">
-        <v>2</v>
-      </c>
-      <c r="L32" s="8" t="s">
-        <v>176</v>
-      </c>
-      <c r="M32" s="8" t="s">
-        <v>177</v>
-      </c>
-      <c r="N32" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="O32" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="P32" s="5" t="s">
-        <v>113</v>
+      <c r="I32" s="5">
+        <v>2</v>
+      </c>
+      <c r="J32" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="K32" s="5">
+        <v>2</v>
+      </c>
+      <c r="L32" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="M32" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="N32" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="O32" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="P32" s="7" t="s">
+        <v>123</v>
       </c>
       <c r="Q32" s="6"/>
-      <c r="R32" s="13">
+      <c r="R32" s="12">
         <v>135</v>
       </c>
-      <c r="S32" s="13">
+      <c r="S32" s="12">
         <v>4</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" ht="50" customHeight="1" spans="1:19">
-      <c r="A33" s="5" t="s">
-        <v>178</v>
+      <c r="A33" s="7" t="s">
+        <v>209</v>
       </c>
       <c r="B33" s="6"/>
       <c r="C33" s="6"/>
       <c r="D33" s="6"/>
-      <c r="E33" s="7">
+      <c r="E33" s="5">
         <v>28</v>
       </c>
-      <c r="F33" s="7">
-        <v>1</v>
-      </c>
-      <c r="G33" s="7">
+      <c r="F33" s="5">
+        <v>1</v>
+      </c>
+      <c r="G33" s="5">
         <v>29</v>
       </c>
       <c r="H33" s="6"/>
-      <c r="I33" s="8">
+      <c r="I33" s="5">
         <v>3</v>
       </c>
-      <c r="J33" s="8" t="s">
-        <v>179</v>
-      </c>
-      <c r="K33" s="8">
-        <v>2</v>
-      </c>
-      <c r="L33" s="8" t="s">
-        <v>180</v>
-      </c>
-      <c r="M33" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="N33" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="O33" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="P33" s="5" t="s">
-        <v>113</v>
+      <c r="J33" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="K33" s="5">
+        <v>2</v>
+      </c>
+      <c r="L33" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="M33" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="N33" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="O33" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="P33" s="7" t="s">
+        <v>123</v>
       </c>
       <c r="Q33" s="6"/>
-      <c r="R33" s="13">
+      <c r="R33" s="12">
         <v>145</v>
       </c>
-      <c r="S33" s="13">
+      <c r="S33" s="12">
         <v>4</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" ht="50" customHeight="1" spans="1:19">
-      <c r="A34" s="5" t="s">
-        <v>182</v>
+      <c r="A34" s="7" t="s">
+        <v>214</v>
       </c>
       <c r="B34" s="6"/>
       <c r="C34" s="6"/>
       <c r="D34" s="6"/>
-      <c r="E34" s="7">
+      <c r="E34" s="5">
         <v>29</v>
       </c>
-      <c r="F34" s="7">
-        <v>1</v>
-      </c>
-      <c r="G34" s="7">
+      <c r="F34" s="5">
+        <v>1</v>
+      </c>
+      <c r="G34" s="5">
         <v>30</v>
       </c>
       <c r="H34" s="6"/>
-      <c r="I34" s="8">
+      <c r="I34" s="5">
         <v>3</v>
       </c>
-      <c r="J34" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="K34" s="8">
+      <c r="J34" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="K34" s="5">
         <v>3</v>
       </c>
-      <c r="L34" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="M34" s="8" t="s">
-        <v>185</v>
-      </c>
-      <c r="N34" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="O34" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="P34" s="5" t="s">
-        <v>113</v>
+      <c r="L34" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="M34" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="N34" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="O34" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="P34" s="7" t="s">
+        <v>123</v>
       </c>
       <c r="Q34" s="6"/>
-      <c r="R34" s="13">
+      <c r="R34" s="12">
         <v>160</v>
       </c>
-      <c r="S34" s="13">
+      <c r="S34" s="12">
         <v>4</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" ht="50" customHeight="1" spans="1:19">
-      <c r="A35" s="5" t="s">
-        <v>186</v>
+      <c r="A35" s="7" t="s">
+        <v>219</v>
       </c>
       <c r="B35" s="6"/>
       <c r="C35" s="6"/>
       <c r="D35" s="6"/>
-      <c r="E35" s="7">
+      <c r="E35" s="5">
         <v>30</v>
       </c>
-      <c r="F35" s="7">
-        <v>1</v>
-      </c>
-      <c r="G35" s="7">
+      <c r="F35" s="5">
+        <v>1</v>
+      </c>
+      <c r="G35" s="5">
         <v>31</v>
       </c>
       <c r="H35" s="6"/>
-      <c r="I35" s="8">
+      <c r="I35" s="5">
         <v>3</v>
       </c>
-      <c r="J35" s="8" t="s">
-        <v>187</v>
-      </c>
-      <c r="K35" s="8">
+      <c r="J35" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="K35" s="5">
         <v>3</v>
       </c>
-      <c r="L35" s="8" t="s">
-        <v>188</v>
-      </c>
-      <c r="M35" s="8" t="s">
-        <v>189</v>
-      </c>
-      <c r="N35" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="O35" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="P35" s="5" t="s">
-        <v>113</v>
+      <c r="L35" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="M35" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="N35" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="O35" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="P35" s="7" t="s">
+        <v>123</v>
       </c>
       <c r="Q35" s="6"/>
-      <c r="R35" s="13">
+      <c r="R35" s="12">
         <v>165</v>
       </c>
-      <c r="S35" s="13">
+      <c r="S35" s="12">
         <v>4</v>
       </c>
     </row>
     <row r="36" s="1" customFormat="1" ht="50" customHeight="1" spans="1:19">
-      <c r="A36" s="5" t="s">
-        <v>190</v>
+      <c r="A36" s="7" t="s">
+        <v>224</v>
       </c>
       <c r="B36" s="6"/>
       <c r="C36" s="6"/>
       <c r="D36" s="6"/>
-      <c r="E36" s="7">
+      <c r="E36" s="5">
         <v>31</v>
       </c>
-      <c r="F36" s="7">
-        <v>1</v>
-      </c>
-      <c r="G36" s="7">
+      <c r="F36" s="5">
+        <v>1</v>
+      </c>
+      <c r="G36" s="5">
         <v>32</v>
       </c>
-      <c r="H36" s="6"/>
-      <c r="I36" s="8">
-        <v>2</v>
-      </c>
-      <c r="J36" s="8" t="s">
-        <v>191</v>
-      </c>
-      <c r="K36" s="8">
-        <v>2</v>
-      </c>
-      <c r="L36" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="M36" s="8" t="s">
-        <v>193</v>
-      </c>
-      <c r="N36" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="O36" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="P36" s="5" t="s">
-        <v>113</v>
+      <c r="H36" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="I36" s="5">
+        <v>2</v>
+      </c>
+      <c r="J36" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="K36" s="5">
+        <v>2</v>
+      </c>
+      <c r="L36" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="M36" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="N36" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="O36" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="P36" s="7" t="s">
+        <v>123</v>
       </c>
       <c r="Q36" s="6"/>
-      <c r="R36" s="13">
+      <c r="R36" s="12">
         <v>130</v>
       </c>
-      <c r="S36" s="13">
+      <c r="S36" s="12">
         <v>5</v>
       </c>
     </row>
     <row r="37" s="1" customFormat="1" ht="50" customHeight="1" spans="1:19">
-      <c r="A37" s="5" t="s">
-        <v>194</v>
+      <c r="A37" s="7" t="s">
+        <v>230</v>
       </c>
       <c r="B37" s="6"/>
       <c r="C37" s="6"/>
       <c r="D37" s="6"/>
-      <c r="E37" s="7">
+      <c r="E37" s="5">
         <v>32</v>
       </c>
-      <c r="F37" s="7">
-        <v>1</v>
-      </c>
-      <c r="G37" s="7">
+      <c r="F37" s="5">
+        <v>1</v>
+      </c>
+      <c r="G37" s="5">
         <v>33</v>
       </c>
       <c r="H37" s="6"/>
-      <c r="I37" s="8">
+      <c r="I37" s="5">
         <v>3</v>
       </c>
-      <c r="J37" s="8" t="s">
-        <v>195</v>
-      </c>
-      <c r="K37" s="8">
-        <v>2</v>
-      </c>
-      <c r="L37" s="8" t="s">
-        <v>196</v>
-      </c>
-      <c r="M37" s="8" t="s">
-        <v>197</v>
-      </c>
-      <c r="N37" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="O37" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="P37" s="5" t="s">
-        <v>113</v>
+      <c r="J37" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="K37" s="5">
+        <v>2</v>
+      </c>
+      <c r="L37" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="M37" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="N37" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="O37" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="P37" s="7" t="s">
+        <v>123</v>
       </c>
       <c r="Q37" s="6"/>
-      <c r="R37" s="13">
+      <c r="R37" s="12">
         <v>135</v>
       </c>
-      <c r="S37" s="13">
+      <c r="S37" s="12">
         <v>5</v>
       </c>
     </row>
     <row r="38" s="1" customFormat="1" ht="50" customHeight="1" spans="1:19">
-      <c r="A38" s="5" t="s">
-        <v>198</v>
+      <c r="A38" s="7" t="s">
+        <v>235</v>
       </c>
       <c r="B38" s="6"/>
       <c r="C38" s="6"/>
       <c r="D38" s="6"/>
-      <c r="E38" s="7">
+      <c r="E38" s="5">
         <v>33</v>
       </c>
-      <c r="F38" s="7">
-        <v>1</v>
-      </c>
-      <c r="G38" s="7">
+      <c r="F38" s="5">
+        <v>1</v>
+      </c>
+      <c r="G38" s="5">
         <v>34</v>
       </c>
       <c r="H38" s="6"/>
-      <c r="I38" s="8">
+      <c r="I38" s="5">
         <v>3</v>
       </c>
-      <c r="J38" s="8" t="s">
-        <v>199</v>
-      </c>
-      <c r="K38" s="8">
-        <v>2</v>
-      </c>
-      <c r="L38" s="8" t="s">
-        <v>200</v>
-      </c>
-      <c r="M38" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="N38" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="O38" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="P38" s="5" t="s">
-        <v>113</v>
+      <c r="J38" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="K38" s="5">
+        <v>2</v>
+      </c>
+      <c r="L38" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="M38" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="N38" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="O38" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="P38" s="7" t="s">
+        <v>123</v>
       </c>
       <c r="Q38" s="6"/>
-      <c r="R38" s="13">
+      <c r="R38" s="12">
         <v>145</v>
       </c>
-      <c r="S38" s="13">
+      <c r="S38" s="12">
         <v>5</v>
       </c>
     </row>
     <row r="39" s="1" customFormat="1" ht="50" customHeight="1" spans="1:19">
-      <c r="A39" s="5" t="s">
-        <v>202</v>
+      <c r="A39" s="7" t="s">
+        <v>240</v>
       </c>
       <c r="B39" s="6"/>
       <c r="C39" s="6"/>
       <c r="D39" s="6"/>
-      <c r="E39" s="7">
+      <c r="E39" s="5">
         <v>34</v>
       </c>
-      <c r="F39" s="7">
-        <v>1</v>
-      </c>
-      <c r="G39" s="7">
+      <c r="F39" s="5">
+        <v>1</v>
+      </c>
+      <c r="G39" s="5">
         <v>35</v>
       </c>
       <c r="H39" s="6"/>
-      <c r="I39" s="8">
+      <c r="I39" s="5">
         <v>3</v>
       </c>
-      <c r="J39" s="8" t="s">
-        <v>203</v>
-      </c>
-      <c r="K39" s="8">
+      <c r="J39" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="K39" s="5">
         <v>3</v>
       </c>
-      <c r="L39" s="8" t="s">
-        <v>204</v>
-      </c>
-      <c r="M39" s="8" t="s">
-        <v>205</v>
-      </c>
-      <c r="N39" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="O39" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="P39" s="5" t="s">
-        <v>113</v>
+      <c r="L39" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="M39" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="N39" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="O39" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="P39" s="7" t="s">
+        <v>123</v>
       </c>
       <c r="Q39" s="6"/>
-      <c r="R39" s="13">
+      <c r="R39" s="12">
         <v>135</v>
       </c>
-      <c r="S39" s="13">
+      <c r="S39" s="12">
         <v>5</v>
       </c>
     </row>
     <row r="40" s="1" customFormat="1" ht="50" customHeight="1" spans="1:19">
-      <c r="A40" s="5" t="s">
-        <v>206</v>
+      <c r="A40" s="7" t="s">
+        <v>245</v>
       </c>
       <c r="B40" s="6"/>
       <c r="C40" s="6"/>
       <c r="D40" s="6"/>
-      <c r="E40" s="7">
+      <c r="E40" s="5">
         <v>35</v>
       </c>
-      <c r="F40" s="7">
-        <v>1</v>
-      </c>
-      <c r="G40" s="7">
+      <c r="F40" s="5">
+        <v>1</v>
+      </c>
+      <c r="G40" s="5">
         <v>36</v>
       </c>
       <c r="H40" s="6"/>
-      <c r="I40" s="8">
+      <c r="I40" s="5">
         <v>3</v>
       </c>
-      <c r="J40" s="8" t="s">
-        <v>207</v>
-      </c>
-      <c r="K40" s="8">
+      <c r="J40" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="K40" s="5">
         <v>3</v>
       </c>
-      <c r="L40" s="8" t="s">
-        <v>208</v>
-      </c>
-      <c r="M40" s="8" t="s">
-        <v>209</v>
-      </c>
-      <c r="N40" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="O40" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="P40" s="5" t="s">
-        <v>113</v>
+      <c r="L40" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="M40" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="N40" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="O40" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="P40" s="7" t="s">
+        <v>123</v>
       </c>
       <c r="Q40" s="6"/>
-      <c r="R40" s="13">
+      <c r="R40" s="12">
         <v>140</v>
       </c>
-      <c r="S40" s="13">
+      <c r="S40" s="12">
         <v>5</v>
       </c>
     </row>
     <row r="41" s="1" customFormat="1" ht="50" customHeight="1" spans="1:19">
-      <c r="A41" s="5" t="s">
-        <v>210</v>
+      <c r="A41" s="7" t="s">
+        <v>250</v>
       </c>
       <c r="B41" s="6"/>
       <c r="C41" s="6"/>
       <c r="D41" s="6"/>
-      <c r="E41" s="7">
+      <c r="E41" s="5">
         <v>36</v>
       </c>
-      <c r="F41" s="7">
-        <v>1</v>
-      </c>
-      <c r="G41" s="7">
+      <c r="F41" s="5">
+        <v>1</v>
+      </c>
+      <c r="G41" s="5">
         <v>37</v>
       </c>
-      <c r="H41" s="6"/>
-      <c r="I41" s="8">
+      <c r="H41" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="I41" s="5">
         <v>3</v>
       </c>
-      <c r="J41" s="8" t="s">
-        <v>211</v>
-      </c>
-      <c r="K41" s="8">
-        <v>2</v>
-      </c>
-      <c r="L41" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="M41" s="8" t="s">
-        <v>213</v>
-      </c>
-      <c r="N41" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="O41" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="P41" s="5" t="s">
-        <v>113</v>
+      <c r="J41" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="K41" s="5">
+        <v>2</v>
+      </c>
+      <c r="L41" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="M41" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="N41" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="O41" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="P41" s="7" t="s">
+        <v>123</v>
       </c>
       <c r="Q41" s="6"/>
-      <c r="R41" s="13">
+      <c r="R41" s="12">
         <v>110</v>
       </c>
-      <c r="S41" s="13">
+      <c r="S41" s="12">
         <v>5</v>
       </c>
     </row>
     <row r="42" s="1" customFormat="1" ht="50" customHeight="1" spans="1:19">
-      <c r="A42" s="5" t="s">
-        <v>214</v>
+      <c r="A42" s="7" t="s">
+        <v>256</v>
       </c>
       <c r="B42" s="6"/>
       <c r="C42" s="6"/>
       <c r="D42" s="6"/>
-      <c r="E42" s="7">
+      <c r="E42" s="5">
         <v>37</v>
       </c>
-      <c r="F42" s="7">
-        <v>1</v>
-      </c>
-      <c r="G42" s="7">
+      <c r="F42" s="5">
+        <v>1</v>
+      </c>
+      <c r="G42" s="5">
         <v>38</v>
       </c>
       <c r="H42" s="6"/>
-      <c r="I42" s="8">
+      <c r="I42" s="5">
         <v>3</v>
       </c>
-      <c r="J42" s="8" t="s">
-        <v>215</v>
-      </c>
-      <c r="K42" s="8">
-        <v>2</v>
-      </c>
-      <c r="L42" s="8" t="s">
-        <v>216</v>
-      </c>
-      <c r="M42" s="8" t="s">
-        <v>217</v>
-      </c>
-      <c r="N42" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="O42" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="P42" s="5" t="s">
-        <v>113</v>
+      <c r="J42" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="K42" s="5">
+        <v>2</v>
+      </c>
+      <c r="L42" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="M42" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="N42" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="O42" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="P42" s="7" t="s">
+        <v>123</v>
       </c>
       <c r="Q42" s="6"/>
-      <c r="R42" s="13">
+      <c r="R42" s="12">
         <v>115</v>
       </c>
-      <c r="S42" s="13">
+      <c r="S42" s="12">
         <v>5</v>
       </c>
     </row>
     <row r="43" s="1" customFormat="1" ht="50" customHeight="1" spans="1:19">
-      <c r="A43" s="5" t="s">
-        <v>218</v>
+      <c r="A43" s="7" t="s">
+        <v>261</v>
       </c>
       <c r="B43" s="6"/>
       <c r="C43" s="6"/>
       <c r="D43" s="6"/>
-      <c r="E43" s="7">
+      <c r="E43" s="5">
         <v>38</v>
       </c>
-      <c r="F43" s="7">
-        <v>1</v>
-      </c>
-      <c r="G43" s="7">
+      <c r="F43" s="5">
+        <v>1</v>
+      </c>
+      <c r="G43" s="5">
         <v>39</v>
       </c>
       <c r="H43" s="6"/>
-      <c r="I43" s="8">
+      <c r="I43" s="5">
         <v>3</v>
       </c>
-      <c r="J43" s="8" t="s">
-        <v>219</v>
-      </c>
-      <c r="K43" s="8">
-        <v>2</v>
-      </c>
-      <c r="L43" s="8" t="s">
-        <v>220</v>
-      </c>
-      <c r="M43" s="8" t="s">
-        <v>221</v>
-      </c>
-      <c r="N43" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="O43" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="P43" s="5" t="s">
-        <v>113</v>
+      <c r="J43" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="K43" s="5">
+        <v>2</v>
+      </c>
+      <c r="L43" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="M43" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="N43" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="O43" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="P43" s="7" t="s">
+        <v>123</v>
       </c>
       <c r="Q43" s="6"/>
-      <c r="R43" s="13">
+      <c r="R43" s="12">
         <v>125</v>
       </c>
-      <c r="S43" s="13">
+      <c r="S43" s="12">
         <v>5</v>
       </c>
     </row>
     <row r="44" s="1" customFormat="1" ht="50" customHeight="1" spans="1:19">
-      <c r="A44" s="5" t="s">
-        <v>222</v>
+      <c r="A44" s="7" t="s">
+        <v>266</v>
       </c>
       <c r="B44" s="6"/>
       <c r="C44" s="6"/>
       <c r="D44" s="6"/>
-      <c r="E44" s="7">
+      <c r="E44" s="5">
         <v>39</v>
       </c>
-      <c r="F44" s="7">
-        <v>1</v>
-      </c>
-      <c r="G44" s="7">
+      <c r="F44" s="5">
+        <v>1</v>
+      </c>
+      <c r="G44" s="5">
         <v>40</v>
       </c>
       <c r="H44" s="6"/>
-      <c r="I44" s="8">
+      <c r="I44" s="5">
         <v>3</v>
       </c>
-      <c r="J44" s="8" t="s">
-        <v>223</v>
-      </c>
-      <c r="K44" s="8">
+      <c r="J44" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="K44" s="5">
         <v>3</v>
       </c>
-      <c r="L44" s="8" t="s">
-        <v>224</v>
-      </c>
-      <c r="M44" s="8" t="s">
-        <v>225</v>
-      </c>
-      <c r="N44" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="O44" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="P44" s="5" t="s">
-        <v>113</v>
+      <c r="L44" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="M44" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="N44" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="O44" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="P44" s="7" t="s">
+        <v>123</v>
       </c>
       <c r="Q44" s="6"/>
-      <c r="R44" s="13">
+      <c r="R44" s="12">
         <v>135</v>
       </c>
-      <c r="S44" s="13">
+      <c r="S44" s="12">
         <v>5</v>
       </c>
     </row>
     <row r="45" s="1" customFormat="1" ht="50" customHeight="1" spans="1:19">
-      <c r="A45" s="5" t="s">
-        <v>226</v>
+      <c r="A45" s="7" t="s">
+        <v>271</v>
       </c>
       <c r="B45" s="6"/>
       <c r="C45" s="6"/>
       <c r="D45" s="6"/>
-      <c r="E45" s="7">
+      <c r="E45" s="5">
         <v>40</v>
       </c>
-      <c r="F45" s="7">
-        <v>1</v>
-      </c>
-      <c r="G45" s="7">
+      <c r="F45" s="5">
+        <v>1</v>
+      </c>
+      <c r="G45" s="5">
         <v>-1</v>
       </c>
       <c r="H45" s="6"/>
-      <c r="I45" s="8">
+      <c r="I45" s="5">
         <v>3</v>
       </c>
-      <c r="J45" s="8" t="s">
-        <v>227</v>
-      </c>
-      <c r="K45" s="8">
+      <c r="J45" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="K45" s="5">
         <v>3</v>
       </c>
-      <c r="L45" s="8" t="s">
-        <v>228</v>
-      </c>
-      <c r="M45" s="8" t="s">
-        <v>229</v>
-      </c>
-      <c r="N45" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="O45" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="P45" s="5" t="s">
-        <v>113</v>
+      <c r="L45" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="M45" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="N45" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="O45" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="P45" s="7" t="s">
+        <v>123</v>
       </c>
       <c r="Q45" s="6"/>
-      <c r="R45" s="13">
+      <c r="R45" s="12">
         <v>140</v>
       </c>
-      <c r="S45" s="13">
+      <c r="S45" s="12">
         <v>5</v>
       </c>
     </row>

--- a/config/level_config.xlsx
+++ b/config/level_config.xlsx
@@ -771,10 +771,10 @@
     <t>[3,10,11]</t>
   </si>
   <si>
-    <t>[[BIG_BEN_PIC_LANDMARK_56,MARBLE_WORD_MINERALS_253,BUTANE_WORD_ALKANES_641],[MICA_WORD_MINERALS_253,FACTORY_WORD_BUILD_384,LIBRARY_WORD_BUILD_384],[PORCINI_WORD_MUSHROOM_178,STADIUM_WORD_BUILD_384,RUSSULA_WORD_MUSHROOM_178],[MUSCAT_WORD_GRAPE_177,ROMANS_WORD_CULTURES_487,CELTS_WORD_CULTURES_487],[BERYL_WORD_MINERALS_253,GEMINI_WORD_ZODIAC_59,PROPANE_WORD_ALKANES_641],[LEO_WORD_ZODIAC_59,MAYANS_WORD_CULTURES_487,VIKINGS_WORD_CULTURES_487],[LIME_WORD_MINERALS_253,VIRGO_WORD_ZODIAC_59,EQUINE_WORD_FAMILIES_234],[STATUE_OF_LIBERTY_PIC_LANDMARK_56,CLARINET_WORD_VIOLIN_508,PRODUCE_WORD_INDUSTRY_921],[HOSPITAL_WORD_BUILD_384,NAP_TIME_WORD_TODDLER_231,PACIFIER_WORD_TODDLER_231],[GYPSUM_WORD_MINERALS_253,COFFIN_PIC_VAMPIRE_55,SOFT_BUN_WORD_HOT_DOG_201],[GRENACHE_WORD_GRAPE_177,METHANE_WORD_ALKANES_641,OVINE_WORD_FAMILIES_234],[MERLOT_WORD_GRAPE_177,PORCINE_WORD_FAMILIES_234,ETHANE_WORD_ALKANES_641],[MEGA_WORD_PREFIX_922,SCORPIO_WORD_ZODIAC_59,TAURUS_WORD_ZODIAC_59],[MALBEC_WORD_GRAPE_177,KETCHUP_WORD_HOT_DOG_201,FELINE_WORD_FAMILIES_234],[SHIRAZ_WORD_GRAPE_177,PISCES_WORD_ZODIAC_59,CANINE_WORD_FAMILIES_234],[AZURITE_WORD_MINERALS_253,BRASS_WORD_ALLOY_264,ALNICO_WORD_ALLOY_264],[DECA_WORD_PREFIX_922,NICHROME_WORD_ALLOY_264,BRONZE_WORD_ALLOY_264],[NANO_WORD_PREFIX_922,CHEDDAR_WORD_CHEESE_108,BRIE_WORD_CHEESE_108],[CALCITE_WORD_MINERALS_253,FANGS_PIC_VAMPIRE_55,BOVINE_WORD_FAMILIES_234],[RIESLING_WORD_GRAPE_177,CAPRINE_WORD_FAMILIES_234,ARIES_WORD_ZODIAC_59],[QUARTZ_WORD_MINERALS_253,PARMESAN_WORD_CHEESE_108,ENVELOPE_WORD_MAILMAN_63],[COLOSSEUM_PIC_LANDMARK_56,MAIL_WORD_MAILMAN_63,LETTER_WORD_MAILMAN_63],[LIBRA_WORD_ZODIAC_59,DIALOGUE_WORD_SPEAK_244,CURLY_WORD_HAIR_245],[GARLIC_PIC_VAMPIRE_55,COILY_WORD_HAIR_245,COUGH_WORD_FLU_251],[BATS_PIC_VAMPIRE_55,SAUSAGE_WORD_HOT_DOG_201,MURINE_WORD_FAMILIES_234]]</t>
-  </si>
-  <si>
-    <t>[WORD_MINERALS_253,WORD_PREFIX_922,WORD_GRAPE_177,PIC_VAMPIRE_55,PIC_LANDMARK_56,WORD_ZODIAC_59,WORD_FAMILIES_234,WORD_ALKANES_641,WORD_HOT_DOG_201]</t>
+    <t>[[BIG_BEN_PIC_LANDMARK_56,MARBLE_WORD_MINERALS_253,BUTANE_WORD_ALKANES_641],[MICA_WORD_MINERALS_253,FACTORY_WORD_BUILD_384,LIBRARY_WORD_BUILD_384],[PORCINI_WORD_MUSHROOM_178,STADIUM_WORD_BUILD_384,RUSSULA_WORD_MUSHROOM_178],[MUSCAT_WORD_GRAPE_177,ROMANS_WORD_CULTURES_487,CELTS_WORD_CULTURES_487],[BERYL_WORD_MINERALS_253,GEMINI_WORD_ZODIAC_59,PROPANE_WORD_ALKANES_641],[LEO_WORD_ZODIAC_59,MAYANS_WORD_CULTURES_487,VIKINGS_WORD_CULTURES_487],[LIME_WORD_MINERALS_253,VIRGO_WORD_ZODIAC_59,EQUINE_WORD_FAMILIES_234],[STATUE_OF_LIBERTY_PIC_LANDMARK_56,CLARINET_WORD_VIOLIN_508,PRODUCE_WORD_INDUSTRY_921],[HOSPITAL_WORD_BUILD_384,NAP_TIME_WORD_TODDLER_231,PACIFIER_WORD_TODDLER_231],[GYPSUM_WORD_MINERALS_253,COFFIN_PIC_VAMPIRE_55,SOFT_BUN_WORD_HOT_DOG_201],[GRENACHE_WORD_GRAPE_177,METHANE_WORD_ALKANES_641,OVINE_WORD_FAMILIES_234],[MERLOT_WORD_GRAPE_177,PORCINE_WORD_FAMILIES_234,ETHANE_WORD_ALKANES_641],[DRAWING_WORD_ARTWORKS_211,SCORPIO_WORD_ZODIAC_59,TAURUS_WORD_ZODIAC_59],[MALBEC_WORD_GRAPE_177,KETCHUP_WORD_HOT_DOG_201,FELINE_WORD_FAMILIES_234],[SHIRAZ_WORD_GRAPE_177,PISCES_WORD_ZODIAC_59,CANINE_WORD_FAMILIES_234],[AZURITE_WORD_MINERALS_253,BRASS_WORD_ALLOY_264,ALNICO_WORD_ALLOY_264],[PHOTO_WORD_ARTWORKS_211,NICHROME_WORD_ALLOY_264,BRONZE_WORD_ALLOY_264],[PAINTING_WORD_ARTWORKS_211,CHEDDAR_WORD_CHEESE_108,BRIE_WORD_CHEESE_108],[CALCITE_WORD_MINERALS_253,FANGS_PIC_VAMPIRE_55,BOVINE_WORD_FAMILIES_234],[RIESLING_WORD_GRAPE_177,CAPRINE_WORD_FAMILIES_234,ARIES_WORD_ZODIAC_59],[QUARTZ_WORD_MINERALS_253,PARMESAN_WORD_CHEESE_108,ENVELOPE_WORD_MAILMAN_63],[COLOSSEUM_PIC_LANDMARK_56,MAIL_WORD_MAILMAN_63,LETTER_WORD_MAILMAN_63],[LIBRA_WORD_ZODIAC_59,DIALOGUE_WORD_SPEAK_244,CURLY_WORD_HAIR_245],[GARLIC_PIC_VAMPIRE_55,COILY_WORD_HAIR_245,COUGH_WORD_FLU_251],[BATS_PIC_VAMPIRE_55,SAUSAGE_WORD_HOT_DOG_201,MURINE_WORD_FAMILIES_234]]</t>
+  </si>
+  <si>
+    <t>[WORD_MINERALS_253,WORD_ARTWORKS_211,WORD_GRAPE_177,PIC_VAMPIRE_55,PIC_LANDMARK_56,WORD_ZODIAC_59,WORD_FAMILIES_234,WORD_ALKANES_641,WORD_HOT_DOG_201]</t>
   </si>
   <si>
     <t>SORT_GAME_LEVEL_REWARD_35</t>
@@ -1565,7 +1565,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1594,6 +1594,9 @@
           <etc:displayText val="2"/>
         </ext>
       </extLst>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2090,7 +2093,7 @@
       <c r="M3" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="N3" s="8" t="s">
+      <c r="N3" s="9" t="s">
         <v>37</v>
       </c>
       <c r="O3" s="4" t="s">
@@ -2231,19 +2234,19 @@
       <c r="N6" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="O6" s="9" t="s">
+      <c r="O6" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="P6" s="10" t="s">
+      <c r="P6" s="11" t="s">
         <v>60</v>
       </c>
       <c r="Q6" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="R6" s="12">
+      <c r="R6" s="13">
         <v>105</v>
       </c>
-      <c r="S6" s="12">
+      <c r="S6" s="13">
         <v>2</v>
       </c>
     </row>
@@ -2282,19 +2285,19 @@
       <c r="N7" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="O7" s="9" t="s">
+      <c r="O7" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="P7" s="11" t="s">
+      <c r="P7" s="12" t="s">
         <v>67</v>
       </c>
       <c r="Q7" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="R7" s="12">
+      <c r="R7" s="13">
         <v>125</v>
       </c>
-      <c r="S7" s="12">
+      <c r="S7" s="13">
         <v>2</v>
       </c>
     </row>
@@ -2333,19 +2336,19 @@
       <c r="N8" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="O8" s="9" t="s">
+      <c r="O8" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="P8" s="11" t="s">
+      <c r="P8" s="12" t="s">
         <v>74</v>
       </c>
       <c r="Q8" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="R8" s="12">
+      <c r="R8" s="13">
         <v>130</v>
       </c>
-      <c r="S8" s="12">
+      <c r="S8" s="13">
         <v>2</v>
       </c>
     </row>
@@ -2384,19 +2387,19 @@
       <c r="N9" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="O9" s="9" t="s">
+      <c r="O9" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="P9" s="11" t="s">
+      <c r="P9" s="12" t="s">
         <v>81</v>
       </c>
       <c r="Q9" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="R9" s="12">
+      <c r="R9" s="13">
         <v>130</v>
       </c>
-      <c r="S9" s="12">
+      <c r="S9" s="13">
         <v>2</v>
       </c>
     </row>
@@ -2435,19 +2438,19 @@
       <c r="N10" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="O10" s="9" t="s">
+      <c r="O10" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="P10" s="11" t="s">
+      <c r="P10" s="12" t="s">
         <v>88</v>
       </c>
       <c r="Q10" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="R10" s="12">
+      <c r="R10" s="13">
         <v>145</v>
       </c>
-      <c r="S10" s="12">
+      <c r="S10" s="13">
         <v>3</v>
       </c>
     </row>
@@ -2486,19 +2489,19 @@
       <c r="N11" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="O11" s="9" t="s">
+      <c r="O11" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="P11" s="11" t="s">
+      <c r="P11" s="12" t="s">
         <v>94</v>
       </c>
       <c r="Q11" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="R11" s="12">
+      <c r="R11" s="13">
         <v>135</v>
       </c>
-      <c r="S11" s="12">
+      <c r="S11" s="13">
         <v>3</v>
       </c>
     </row>
@@ -2537,19 +2540,19 @@
       <c r="N12" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="O12" s="9" t="s">
+      <c r="O12" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="P12" s="11" t="s">
+      <c r="P12" s="12" t="s">
         <v>101</v>
       </c>
       <c r="Q12" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="R12" s="12">
+      <c r="R12" s="13">
         <v>125</v>
       </c>
-      <c r="S12" s="12">
+      <c r="S12" s="13">
         <v>3</v>
       </c>
     </row>
@@ -2588,19 +2591,19 @@
       <c r="N13" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="O13" s="9" t="s">
+      <c r="O13" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="P13" s="11" t="s">
+      <c r="P13" s="12" t="s">
         <v>108</v>
       </c>
       <c r="Q13" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="R13" s="12">
+      <c r="R13" s="13">
         <v>140</v>
       </c>
-      <c r="S13" s="12">
+      <c r="S13" s="13">
         <v>3</v>
       </c>
     </row>
@@ -2641,19 +2644,19 @@
       <c r="N14" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="O14" s="9" t="s">
+      <c r="O14" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="P14" s="11" t="s">
+      <c r="P14" s="12" t="s">
         <v>116</v>
       </c>
       <c r="Q14" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="R14" s="12">
+      <c r="R14" s="13">
         <v>125</v>
       </c>
-      <c r="S14" s="12">
+      <c r="S14" s="13">
         <v>3</v>
       </c>
     </row>
@@ -2699,10 +2702,10 @@
         <v>123</v>
       </c>
       <c r="Q15" s="6"/>
-      <c r="R15" s="12">
+      <c r="R15" s="13">
         <v>135</v>
       </c>
-      <c r="S15" s="12">
+      <c r="S15" s="13">
         <v>3</v>
       </c>
     </row>
@@ -2748,10 +2751,10 @@
         <v>123</v>
       </c>
       <c r="Q16" s="6"/>
-      <c r="R16" s="12">
+      <c r="R16" s="13">
         <v>90</v>
       </c>
-      <c r="S16" s="12">
+      <c r="S16" s="13">
         <v>3</v>
       </c>
     </row>
@@ -2797,10 +2800,10 @@
         <v>123</v>
       </c>
       <c r="Q17" s="6"/>
-      <c r="R17" s="12">
+      <c r="R17" s="13">
         <v>100</v>
       </c>
-      <c r="S17" s="12">
+      <c r="S17" s="13">
         <v>3</v>
       </c>
     </row>
@@ -2848,10 +2851,10 @@
         <v>123</v>
       </c>
       <c r="Q18" s="6"/>
-      <c r="R18" s="12">
+      <c r="R18" s="13">
         <v>115</v>
       </c>
-      <c r="S18" s="12">
+      <c r="S18" s="13">
         <v>3</v>
       </c>
     </row>
@@ -2897,10 +2900,10 @@
         <v>123</v>
       </c>
       <c r="Q19" s="6"/>
-      <c r="R19" s="12">
+      <c r="R19" s="13">
         <v>130</v>
       </c>
-      <c r="S19" s="12">
+      <c r="S19" s="13">
         <v>3</v>
       </c>
     </row>
@@ -2946,10 +2949,10 @@
         <v>123</v>
       </c>
       <c r="Q20" s="6"/>
-      <c r="R20" s="12">
+      <c r="R20" s="13">
         <v>150</v>
       </c>
-      <c r="S20" s="12">
+      <c r="S20" s="13">
         <v>3</v>
       </c>
     </row>
@@ -2995,10 +2998,10 @@
         <v>123</v>
       </c>
       <c r="Q21" s="6"/>
-      <c r="R21" s="12">
+      <c r="R21" s="13">
         <v>130</v>
       </c>
-      <c r="S21" s="12">
+      <c r="S21" s="13">
         <v>3</v>
       </c>
     </row>
@@ -3046,10 +3049,10 @@
         <v>123</v>
       </c>
       <c r="Q22" s="6"/>
-      <c r="R22" s="12">
+      <c r="R22" s="13">
         <v>130</v>
       </c>
-      <c r="S22" s="12">
+      <c r="S22" s="13">
         <v>3</v>
       </c>
     </row>
@@ -3095,10 +3098,10 @@
         <v>123</v>
       </c>
       <c r="Q23" s="6"/>
-      <c r="R23" s="12">
+      <c r="R23" s="13">
         <v>140</v>
       </c>
-      <c r="S23" s="12">
+      <c r="S23" s="13">
         <v>3</v>
       </c>
     </row>
@@ -3144,10 +3147,10 @@
         <v>123</v>
       </c>
       <c r="Q24" s="6"/>
-      <c r="R24" s="12">
+      <c r="R24" s="13">
         <v>155</v>
       </c>
-      <c r="S24" s="12">
+      <c r="S24" s="13">
         <v>3</v>
       </c>
     </row>
@@ -3193,10 +3196,10 @@
         <v>123</v>
       </c>
       <c r="Q25" s="6"/>
-      <c r="R25" s="12">
+      <c r="R25" s="13">
         <v>165</v>
       </c>
-      <c r="S25" s="12">
+      <c r="S25" s="13">
         <v>3</v>
       </c>
     </row>
@@ -3244,10 +3247,10 @@
         <v>123</v>
       </c>
       <c r="Q26" s="6"/>
-      <c r="R26" s="12">
+      <c r="R26" s="13">
         <v>140</v>
       </c>
-      <c r="S26" s="12">
+      <c r="S26" s="13">
         <v>3</v>
       </c>
     </row>
@@ -3293,10 +3296,10 @@
         <v>123</v>
       </c>
       <c r="Q27" s="6"/>
-      <c r="R27" s="12">
+      <c r="R27" s="13">
         <v>145</v>
       </c>
-      <c r="S27" s="12">
+      <c r="S27" s="13">
         <v>4</v>
       </c>
     </row>
@@ -3342,10 +3345,10 @@
         <v>123</v>
       </c>
       <c r="Q28" s="6"/>
-      <c r="R28" s="12">
+      <c r="R28" s="13">
         <v>150</v>
       </c>
-      <c r="S28" s="12">
+      <c r="S28" s="13">
         <v>4</v>
       </c>
     </row>
@@ -3391,10 +3394,10 @@
         <v>123</v>
       </c>
       <c r="Q29" s="6"/>
-      <c r="R29" s="12">
+      <c r="R29" s="13">
         <v>155</v>
       </c>
-      <c r="S29" s="12">
+      <c r="S29" s="13">
         <v>4</v>
       </c>
     </row>
@@ -3440,10 +3443,10 @@
         <v>123</v>
       </c>
       <c r="Q30" s="6"/>
-      <c r="R30" s="12">
+      <c r="R30" s="13">
         <v>165</v>
       </c>
-      <c r="S30" s="12">
+      <c r="S30" s="13">
         <v>4</v>
       </c>
     </row>
@@ -3491,10 +3494,10 @@
         <v>123</v>
       </c>
       <c r="Q31" s="6"/>
-      <c r="R31" s="12">
+      <c r="R31" s="13">
         <v>150</v>
       </c>
-      <c r="S31" s="12">
+      <c r="S31" s="13">
         <v>4</v>
       </c>
     </row>
@@ -3540,10 +3543,10 @@
         <v>123</v>
       </c>
       <c r="Q32" s="6"/>
-      <c r="R32" s="12">
+      <c r="R32" s="13">
         <v>135</v>
       </c>
-      <c r="S32" s="12">
+      <c r="S32" s="13">
         <v>4</v>
       </c>
     </row>
@@ -3589,10 +3592,10 @@
         <v>123</v>
       </c>
       <c r="Q33" s="6"/>
-      <c r="R33" s="12">
+      <c r="R33" s="13">
         <v>145</v>
       </c>
-      <c r="S33" s="12">
+      <c r="S33" s="13">
         <v>4</v>
       </c>
     </row>
@@ -3638,10 +3641,10 @@
         <v>123</v>
       </c>
       <c r="Q34" s="6"/>
-      <c r="R34" s="12">
+      <c r="R34" s="13">
         <v>160</v>
       </c>
-      <c r="S34" s="12">
+      <c r="S34" s="13">
         <v>4</v>
       </c>
     </row>
@@ -3687,10 +3690,10 @@
         <v>123</v>
       </c>
       <c r="Q35" s="6"/>
-      <c r="R35" s="12">
+      <c r="R35" s="13">
         <v>165</v>
       </c>
-      <c r="S35" s="12">
+      <c r="S35" s="13">
         <v>4</v>
       </c>
     </row>
@@ -3738,10 +3741,10 @@
         <v>123</v>
       </c>
       <c r="Q36" s="6"/>
-      <c r="R36" s="12">
+      <c r="R36" s="13">
         <v>130</v>
       </c>
-      <c r="S36" s="12">
+      <c r="S36" s="13">
         <v>5</v>
       </c>
     </row>
@@ -3787,10 +3790,10 @@
         <v>123</v>
       </c>
       <c r="Q37" s="6"/>
-      <c r="R37" s="12">
+      <c r="R37" s="13">
         <v>135</v>
       </c>
-      <c r="S37" s="12">
+      <c r="S37" s="13">
         <v>5</v>
       </c>
     </row>
@@ -3836,10 +3839,10 @@
         <v>123</v>
       </c>
       <c r="Q38" s="6"/>
-      <c r="R38" s="12">
+      <c r="R38" s="13">
         <v>145</v>
       </c>
-      <c r="S38" s="12">
+      <c r="S38" s="13">
         <v>5</v>
       </c>
     </row>
@@ -3885,10 +3888,10 @@
         <v>123</v>
       </c>
       <c r="Q39" s="6"/>
-      <c r="R39" s="12">
+      <c r="R39" s="13">
         <v>135</v>
       </c>
-      <c r="S39" s="12">
+      <c r="S39" s="13">
         <v>5</v>
       </c>
     </row>
@@ -3918,10 +3921,10 @@
       <c r="K40" s="5">
         <v>3</v>
       </c>
-      <c r="L40" s="5" t="s">
+      <c r="L40" s="8" t="s">
         <v>247</v>
       </c>
-      <c r="M40" s="5" t="s">
+      <c r="M40" s="8" t="s">
         <v>248</v>
       </c>
       <c r="N40" s="5" t="s">
@@ -3934,10 +3937,10 @@
         <v>123</v>
       </c>
       <c r="Q40" s="6"/>
-      <c r="R40" s="12">
+      <c r="R40" s="13">
         <v>140</v>
       </c>
-      <c r="S40" s="12">
+      <c r="S40" s="13">
         <v>5</v>
       </c>
     </row>
@@ -3985,10 +3988,10 @@
         <v>123</v>
       </c>
       <c r="Q41" s="6"/>
-      <c r="R41" s="12">
+      <c r="R41" s="13">
         <v>110</v>
       </c>
-      <c r="S41" s="12">
+      <c r="S41" s="13">
         <v>5</v>
       </c>
     </row>
@@ -4034,10 +4037,10 @@
         <v>123</v>
       </c>
       <c r="Q42" s="6"/>
-      <c r="R42" s="12">
+      <c r="R42" s="13">
         <v>115</v>
       </c>
-      <c r="S42" s="12">
+      <c r="S42" s="13">
         <v>5</v>
       </c>
     </row>
@@ -4083,10 +4086,10 @@
         <v>123</v>
       </c>
       <c r="Q43" s="6"/>
-      <c r="R43" s="12">
+      <c r="R43" s="13">
         <v>125</v>
       </c>
-      <c r="S43" s="12">
+      <c r="S43" s="13">
         <v>5</v>
       </c>
     </row>
@@ -4132,10 +4135,10 @@
         <v>123</v>
       </c>
       <c r="Q44" s="6"/>
-      <c r="R44" s="12">
+      <c r="R44" s="13">
         <v>135</v>
       </c>
-      <c r="S44" s="12">
+      <c r="S44" s="13">
         <v>5</v>
       </c>
     </row>
@@ -4181,10 +4184,10 @@
         <v>123</v>
       </c>
       <c r="Q45" s="6"/>
-      <c r="R45" s="12">
+      <c r="R45" s="13">
         <v>140</v>
       </c>
-      <c r="S45" s="12">
+      <c r="S45" s="13">
         <v>5</v>
       </c>
     </row>

--- a/config/level_config.xlsx
+++ b/config/level_config.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="23960"/>
+    <workbookView windowWidth="29400" windowHeight="12880"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -198,10 +198,10 @@
     <t>[7]</t>
   </si>
   <si>
-    <t>[[PROPANE_WORD_FUELS_190],[ASIA_WORD_LANDMASS_10,PANTS_PIC_GARMENTS_7],[HOWDY_WORD_HELLO_295],[BIKE_WORD_STREET_768],[WALRUS_WORD_ARCTIC_180],[HEY_WORD_HELLO_295],[AFRICA_WORD_LANDMASS_10,GLOVES_PIC_GARMENTS_7],[SNOWY_OWL_WORD_ARCTIC_180],[COUPLE_WORD_HEART_344],[DIESEL_WORD_FUELS_190],[GASOLINE_WORD_FUELS_190],[SHIRT_PIC_GARMENTS_7],[CORNER_WORD_STREET_768],[HI_WORD_HELLO_295],[OKAY_WORD_OK_SIGN_301],[BUTTER_WORD_DAIRY_30],[DRESS_PIC_GARMENTS_7],[DRIVER_WORD_STREET_768],[YOGURT_WORD_DAIRY_30],[KEROSENE_WORD_FUELS_190],[COAL_WORD_FUELS_190],[EUROPE_WORD_LANDMASS_10],[POLAR_BEAR_WORD_ARCTIC_180],[ROMANCE_WORD_HEART_344],[CREAM_WORD_DAIRY_30]]</t>
-  </si>
-  <si>
-    <t>[WORD_LANDMASS_10,PIC_GARMENTS_7]</t>
+    <t>[[PROPANE_WORD_FUELS_190],[PANTS_PIC_GARMENTS_7],[HOWDY_WORD_HELLO_295],[BIKE_WORD_STREET_768],[WALRUS_WORD_ARCTIC_180],[HEY_WORD_HELLO_295],[GLOVES_PIC_GARMENTS_7],[SNOWY_OWL_WORD_ARCTIC_180],[COUPLE_WORD_HEART_344],[DIESEL_WORD_FUELS_190],[GASOLINE_WORD_FUELS_190],[SHIRT_PIC_GARMENTS_7],[CORNER_WORD_STREET_768],[HI_WORD_HELLO_295],[OKAY_WORD_OK_SIGN_301],[BUTTER_WORD_DAIRY_30],[DRESS_PIC_GARMENTS_7],[DRIVER_WORD_STREET_768],[YOGURT_WORD_DAIRY_30],[KEROSENE_WORD_FUELS_190],[COAL_WORD_FUELS_190],[COAT_PIC_GARMENTS_7],[POLAR_BEAR_WORD_ARCTIC_180],[ROMANCE_WORD_HEART_344],[CREAM_WORD_DAIRY_30]]</t>
+  </si>
+  <si>
+    <t>[PIC_GARMENTS_7]</t>
   </si>
   <si>
     <t>SORT_GAME_LEVEL_REWARD_1</t>
@@ -219,10 +219,10 @@
     <t>[12]</t>
   </si>
   <si>
-    <t>[[THOSE_WORD_POINTING_379,FABLE_WORD_LEGENDS_291],[MYTH_WORD_LEGENDS_291,KINGDOM_WORD_MEDIEVAL_228],[OILY_WORD_SKIN_380],[NORMAL_WORD_SKIN_380],[SUPPORT_WORD_HELP_183],[BURGER_WORD_FOOD_3],[BANANA_PIC_FRUITS_9],[NEW_YEAR_WORD_HOLIDAY_163],[FLAG_DAY_WORD_HOLIDAY_163],[LORD_WORD_MEDIEVAL_228],[FORCE_WORD_STRENGTH_401],[DONATE_WORD_HELP_183],[ASSIST_WORD_HELP_183],[ORANGE_PIC_FRUITS_9],[FALSIFY_WORD_LIE_492],[THAT_WORD_POINTING_379],[APPLE_PIC_FRUITS_9],[EASTER_WORD_HOLIDAY_163],[HOT_DOG_WORD_FOOD_3],[LEAGUE_WORD_UNITE_126],[KIWI_PIC_FRUITS_9],[PIZZA_WORD_FOOD_3],[THIS_WORD_POINTING_379],[TALE_WORD_LEGENDS_291],[FRIES_WORD_FOOD_3]]</t>
-  </si>
-  <si>
-    <t>[WORD_HOLIDAY_163,WORD_HELP_183,PIC_FRUITS_9]</t>
+    <t>[[ORANGE_PIC_FRUITS_9],[KINGDOM_WORD_MEDIEVAL_228],[OILY_WORD_SKIN_380],[NORMAL_WORD_SKIN_380],[PEACH_PIC_FRUITS_9],[BURGER_WORD_FOOD_3],[ASSIST_WORD_HELP_183],[NEW_YEAR_WORD_HOLIDAY_163],[POMEGRANATE_PIC_FRUITS_9],[LORD_WORD_MEDIEVAL_228],[PINEAPPLE_PIC_FRUITS_9],[DONATE_WORD_HELP_183],[APPLE_PIC_FRUITS_9],[SUPPORT_WORD_HELP_183],[FALSIFY_WORD_LIE_492],[THAT_WORD_POINTING_379],[BANANA_PIC_FRUITS_9],[EASTER_WORD_HOLIDAY_163],[HOT_DOG_WORD_FOOD_3],[WATERMELON_PIC_FRUITS_9],[KIWI_PIC_FRUITS_9],[PIZZA_WORD_FOOD_3],[THIS_WORD_POINTING_379],[TALE_WORD_LEGENDS_291],[FRIES_WORD_FOOD_3]]</t>
+  </si>
+  <si>
+    <t>[PIC_FRUITS_9]</t>
   </si>
   <si>
     <t>SORT_GAME_LEVEL_REWARD_2</t>
@@ -240,10 +240,10 @@
     <t>[10]</t>
   </si>
   <si>
-    <t>[[NOW_WORD_PRESENT_470,BURGER_WORD_FOOD_3],[DRY_WORD_SKIN_380],[PAWN_PIC_CHESS_1],[NORMAL_WORD_SKIN_380],[ROOK_PIC_CHESS_1],[KNIGHT_PIC_CHESS_1],[CONSENT_WORD_OK_SIGN_301],[COUPLE_WORD_HEART_344],[CODE_WORD_SECRET_471],[ROMANCE_WORD_HEART_344],[HOWDY_WORD_HELLO_295],[THIS_WORD_POINTING_379],[BISHOP_PIC_CHESS_1],[LUNCH_WORD_MEALS_444],[HEY_WORD_HELLO_295],[MIGHT_WORD_STRENGTH_401],[LETTER_WORD_MESSAGE_407],[WORD_WORD_SECRET_471],[FRIES_WORD_FOOD_3],[PASSION_WORD_HEART_344],[THOSE_WORD_POINTING_379],[HI_WORD_HELLO_295],[YES_WORD_OK_SIGN_301],[TEXT_WORD_MESSAGE_407],[OKAY_WORD_OK_SIGN_301]]</t>
-  </si>
-  <si>
-    <t>[WORD_HELLO_295,WORD_HEART_344,WORD_OK_SIGN_301,PIC_CHESS_1]</t>
+    <t>[[BURGER_WORD_FOOD_3],[DRY_WORD_SKIN_380],[NOW_WORD_PRESENT_470],[NORMAL_WORD_SKIN_380],[ROOK_PIC_CHESS_1],[KNIGHT_PIC_CHESS_1],[CONSENT_WORD_OK_SIGN_301],[COUPLE_WORD_HEART_344],[CODE_WORD_SECRET_471],[PAWN_PIC_CHESS_1],[HOWDY_WORD_HELLO_295],[THIS_WORD_POINTING_379],[BISHOP_PIC_CHESS_1],[LUNCH_WORD_MEALS_444],[HEY_WORD_HELLO_295],[MIGHT_WORD_STRENGTH_401],[LETTER_WORD_MESSAGE_407],[WORD_WORD_SECRET_471],[FRIES_WORD_FOOD_3],[YES_WORD_OK_SIGN_301],[THOSE_WORD_POINTING_379],[HI_WORD_HELLO_295],[ROMANCE_WORD_HEART_344],[TEXT_WORD_MESSAGE_407],[OKAY_WORD_OK_SIGN_301]]</t>
+  </si>
+  <si>
+    <t>[WORD_HELLO_295,WORD_OK_SIGN_301,PIC_CHESS_1]</t>
   </si>
   <si>
     <t>SORT_GAME_LEVEL_REWARD_3</t>
@@ -261,10 +261,10 @@
     <t>[3,6]</t>
   </si>
   <si>
-    <t>[[OILY_WORD_SKIN_380],[POWER_WORD_STRENGTH_401,EMAIL_WORD_MESSAGE_407],[DINNER_WORD_MEALS_444],[FRIES_WORD_FOOD_3],[ESSAY_WORD_ARTICLES_147],[THOSE_WORD_POINTING_379],[FORCE_WORD_STRENGTH_401],[CAR_WORD_DRIVING_49],[CODE_WORD_SECRET_471],[CHAIR_PIC_FURNITURE_3],[BURGER_WORD_FOOD_3],[NORMAL_WORD_SKIN_380],[MIGHT_WORD_STRENGTH_401],[SOFA_PIC_FURNITURE_3],[PIZZA_WORD_FOOD_3],[THAT_WORD_POINTING_379],[SIGN_WORD_DRIVING_49],[SUCCESS_WORD_WREATH_544],[TABLE_PIC_FURNITURE_3],[DESK_PIC_FURNITURE_3],[DRY_WORD_SKIN_380],[THIS_WORD_POINTING_379],[OPINION_WORD_ARTICLES_147],[HOT_DOG_WORD_FOOD_3],[ROAD_WORD_DRIVING_49]]</t>
-  </si>
-  <si>
-    <t>[WORD_FOOD_3,WORD_POINTING_379,WORD_SKIN_380,PIC_FURNITURE_3,WORD_STRENGTH_401]</t>
+    <t>[[OILY_WORD_SKIN_380],[EMAIL_WORD_MESSAGE_407],[DINNER_WORD_MEALS_444],[FRIES_WORD_FOOD_3],[ESSAY_WORD_ARTICLES_147],[POWER_WORD_STRENGTH_401],[FORCE_WORD_STRENGTH_401],[CAR_WORD_DRIVING_49],[CODE_WORD_SECRET_471],[CHAIR_PIC_FURNITURE_3],[BURGER_WORD_FOOD_3],[NORMAL_WORD_SKIN_380],[MIGHT_WORD_STRENGTH_401],[SOFA_PIC_FURNITURE_3],[PIZZA_WORD_FOOD_3],[TABLE_PIC_FURNITURE_3],[SIGN_WORD_DRIVING_49],[SUCCESS_WORD_WREATH_544],[THAT_WORD_POINTING_379],[DESK_PIC_FURNITURE_3],[DRY_WORD_SKIN_380],[THIS_WORD_POINTING_379],[OPINION_WORD_ARTICLES_147],[HOT_DOG_WORD_FOOD_3],[ROAD_WORD_DRIVING_49]]</t>
+  </si>
+  <si>
+    <t>[WORD_FOOD_3,WORD_SKIN_380,WORD_STRENGTH_401,PIC_FURNITURE_3]</t>
   </si>
   <si>
     <t>SORT_GAME_LEVEL_REWARD_4</t>
@@ -300,10 +300,10 @@
     <t>SORT_GAME_LEVEL_6_BOARD_1</t>
   </si>
   <si>
-    <t>[[SURF_WORD_COAST_969,BEACH_WORD_COAST_969],[OPINION_WORD_ARTICLES_147],[ROAD_WORD_DRIVING_49,KNEE_WORD_LEGS_322],[SUCCESS_WORD_WREATH_544],[VIOLIN_PIC_PLAY_12],[ORGAN_PIC_PLAY_12],[ICEBERG_WORD_SNOW_77],[FLAKE_WORD_SNOW_77],[SIGN_WORD_DRIVING_49],[CLIFF_WORD_COAST_969],[BOBBER_WORD_FISHING_20],[TRAFFIC_WORD_DRIVING_49],[SUMMER_WORD_SEASONS_18],[PIANO_PIC_PLAY_12],[VICTORY_WORD_WREATH_544],[UKULELE_PIC_PLAY_12],[FLUTE_PIC_PLAY_12],[ESSAY_WORD_ARTICLES_147],[SLEET_WORD_SNOW_77],[TRIUMPH_WORD_WREATH_544,SPRING_WORD_SEASONS_18],[CAR_WORD_DRIVING_49,AUTUMN_WORD_SEASONS_18],[CELLO_PIC_PLAY_12],[GUITAR_PIC_PLAY_12],[REVIEW_WORD_ARTICLES_147,LEMON_WORD_CITRUS_173],[DRUM_PIC_PLAY_12]]</t>
-  </si>
-  <si>
-    <t>[WORD_WREATH_544,WORD_ARTICLES_147,WORD_DRIVING_49,PIC_PLAY_12,WORD_SNOW_77]</t>
+    <t>[[SOLID_WORD_PHASE_57,BEACH_WORD_COAST_969],[OPINION_WORD_ARTICLES_147],[ROAD_WORD_DRIVING_49,KNEE_WORD_LEGS_322],[SUCCESS_WORD_WREATH_544],[VIOLIN_PIC_PLAY_12],[ORGAN_PIC_PLAY_12],[ASIA_WORD_LANDMASS_10],[AFRICA_WORD_LANDMASS_10],[SIGN_WORD_DRIVING_49],[LIQUID_WORD_PHASE_57],[BOBBER_WORD_FISHING_20],[TRAFFIC_WORD_DRIVING_49],[SUMMER_WORD_SEASONS_18],[PIANO_PIC_PLAY_12],[VICTORY_WORD_WREATH_544],[UKULELE_PIC_PLAY_12],[FLUTE_PIC_PLAY_12],[ESSAY_WORD_ARTICLES_147],[EUROPE_WORD_LANDMASS_10],[TRIUMPH_WORD_WREATH_544,SPRING_WORD_SEASONS_18],[CAR_WORD_DRIVING_49,AUTUMN_WORD_SEASONS_18],[CELLO_PIC_PLAY_12],[GUITAR_PIC_PLAY_12],[REVIEW_WORD_ARTICLES_147,LEMON_WORD_CITRUS_173],[DRUM_PIC_PLAY_12]]</t>
+  </si>
+  <si>
+    <t>[WORD_LANDMASS_10,PIC_PLAY_12,WORD_ARTICLES_147,WORD_WREATH_544,WORD_DRIVING_49]</t>
   </si>
   <si>
     <t>SORT_GAME_LEVEL_REWARD_6</t>
@@ -387,10 +387,10 @@
     <t>[2,3]</t>
   </si>
   <si>
-    <t>[[COMFY_WORD_COZY_58,BRICK_WORD_STREET_768],[ACE_OF_HEARTS_PIC_DECK_4,DNA_WORD_GENETICS_1060],[SKIING_WORD_SLIDING_339,CORNER_WORD_STREET_768],[JUDO_WORD_COMBAT_121,MYTH_WORD_LEGENDS_291],[AIR_BIKE_WORD_GYM_164,SAGA_WORD_LEGENDS_291],[YACHT_WORD_LUXURY_133],[DUMBBELL_WORD_GYM_164],[QUEEN_HEARTS_PIC_DECK_4],[SILAT_WORD_COMBAT_121],[LUGE_WORD_SLIDING_339,KUNG_FU_WORD_COMBAT_121],[KING_HEARTS_PIC_DECK_4,KARATE_WORD_COMBAT_121],[SLEDDING_WORD_SLIDING_339],[SAVATE_WORD_COMBAT_121],[SKATING_WORD_SLIDING_339,GAVEL_WORD_JUSTICE_310],[JEWELRY_WORD_LUXURY_133,SCALES_WORD_JUSTICE_310],[WARM_WORD_COZY_58,FALSIFY_WORD_LIE_492],[CAVIAR_WORD_LUXURY_133,MISLEAD_WORD_LIE_492],[COURT_WORD_JUSTICE_310,SEXTANT_WORD_NAVIGATE_230],[SKELETON_WORD_SLIDING_339],[COAL_WORD_FUELS_190],[SNUG_WORD_COZY_58],[SUMO_WORD_COMBAT_121],[LAW_WORD_JUSTICE_310],[BARBELL_WORD_GYM_164],[WATCH_WORD_LUXURY_133,GASOLINE_WORD_FUELS_190]]</t>
-  </si>
-  <si>
-    <t>[WORD_GYM_164,WORD_COZY_58,WORD_COMBAT_121,WORD_LUXURY_133,PIC_DECK_4,WORD_SLIDING_339,WORD_JUSTICE_310]</t>
+    <t>[[COMFY_WORD_COZY_58,BRICK_WORD_STREET_768],[ACE_OF_HEARTS_PIC_DECK_4,DNA_WORD_GENETICS_1060],[ANT_WORD_INSECTS_25,CORNER_WORD_STREET_768],[JUDO_WORD_COMBAT_121,MYTH_WORD_LEGENDS_291],[AIR_BIKE_WORD_GYM_164,SAGA_WORD_LEGENDS_291],[YACHT_WORD_LUXURY_133],[DUMBBELL_WORD_GYM_164],[QUEEN_HEARTS_PIC_DECK_4],[SILAT_WORD_COMBAT_121],[LADYBUG_WORD_INSECTS_25,KUNG_FU_WORD_COMBAT_121],[KING_HEARTS_PIC_DECK_4,KARATE_WORD_COMBAT_121],[MOSQUITO_WORD_INSECTS_25],[SAVATE_WORD_COMBAT_121],[COVER_WORD_BOOK_9,DRAGONFLY_WORD_INSECTS_25],[JEWELRY_WORD_LUXURY_133,MOTH_WORD_INSECTS_25],[WARM_WORD_COZY_58,ACTOR_WORD_JOBS_42],[CAVIAR_WORD_LUXURY_133,MISLEAD_WORD_LIE_492],[PAPER_WORD_BOOK_9,SEXTANT_WORD_NAVIGATE_230],[WASP_WORD_INSECTS_25],[COAL_WORD_FUELS_190],[SNUG_WORD_COZY_58],[SUMO_WORD_COMBAT_121],[PAGE_WORD_BOOK_9],[BARBELL_WORD_GYM_164],[WATCH_WORD_LUXURY_133,GASOLINE_WORD_FUELS_190]]</t>
+  </si>
+  <si>
+    <t>[WORD_BOOK_9,PIC_DECK_4,WORD_GYM_164,WORD_COZY_58,WORD_COMBAT_121,WORD_LUXURY_133,WORD_INSECTS_25]</t>
   </si>
   <si>
     <t>SORT_GAME_LEVEL_REWARD_10</t>
@@ -450,10 +450,10 @@
     <t>[6,9]</t>
   </si>
   <si>
-    <t>[[INQUIRY_WORD_QUEST_680,DRAMA_WORD_CINEMA_6],[WESTERN_WORD_CINEMA_6,SOHO_WORD_NEW_YORK_287],[HAVASU_WORD_WATER_152,COUNTRY_WORD_DIVISION_242],[SWAN_PIC_BIRD_16,TICKET_WORD_CINEMA_6],[HUNT_WORD_QUEST_680,STATE_WORD_DIVISION_242],[YOSEMITE_WORD_WATER_152],[LOBSTER_PIC_SEAFOOD_17,REGION_WORD_DIVISION_242],[ROSE_WORD_FLOWERS_4,BIBLE_WORD_PRIEST_1019],[MUSSEL_PIC_SEAFOOD_17],[PEONY_WORD_FLOWERS_4,CLERIC_WORD_PRIEST_1019],[TULIP_WORD_FLOWERS_4],[VICTORIA_WORD_WATER_152,MULBERRY_WORD_BERRY_116],[PERSEUS_WORD_PATTERN_188,RUNWAY_WORD_AIRPORT_29],[EAGLE_PIC_BIRD_16],[DRACO_WORD_PATTERN_188],[NIAGARA_WORD_WATER_152,HORROR_WORD_CINEMA_6],[SERPENS_WORD_PATTERN_188,ENGLISH_WORD_LANGUAGE_70],[POPCORN_WORD_CINEMA_6],[DOVE_PIC_BIRD_16,COMEDY_WORD_CINEMA_6],[OYSTER_PIC_SEAFOOD_17],[CYGNUS_WORD_PATTERN_188],[PURSUIT_WORD_QUEST_680],[LILY_WORD_FLOWERS_4],[SCORPIUS_WORD_PATTERN_188],[ORION_WORD_PATTERN_188,ITALIAN_WORD_LANGUAGE_70]]</t>
-  </si>
-  <si>
-    <t>[WORD_FLOWERS_4,WORD_CINEMA_6,WORD_QUEST_680,WORD_PATTERN_188,WORD_WATER_152,PIC_SEAFOOD_17,PIC_BIRD_16]</t>
+    <t>[[INQUIRY_WORD_QUEST_680,DRAMA_WORD_CINEMA_6],[WESTERN_WORD_CINEMA_6,DOG_WORD_PETS_2],[FLAG_DAY_WORD_HOLIDAY_163,COUNTRY_WORD_DIVISION_242],[SWAN_PIC_BIRD_16,TICKET_WORD_CINEMA_6],[HUNT_WORD_QUEST_680,STATE_WORD_DIVISION_242],[EASTER_WORD_HOLIDAY_163],[LOBSTER_PIC_SEAFOOD_17,REGION_WORD_DIVISION_242],[ROSE_WORD_FLOWERS_4,CAT_WORD_PETS_2],[MUSSEL_PIC_SEAFOOD_17],[PEONY_WORD_FLOWERS_4,CHEESE_WORD_BURGER_8],[TULIP_WORD_FLOWERS_4],[NEW_YEAR_WORD_HOLIDAY_163,MULBERRY_WORD_BERRY_116],[PERSEUS_WORD_PATTERN_188,RUNWAY_WORD_AIRPORT_29],[EAGLE_PIC_BIRD_16],[DRACO_WORD_PATTERN_188],[HORROR_WORD_CINEMA_6],[SERPENS_WORD_PATTERN_188,ENGLISH_WORD_LANGUAGE_70],[POPCORN_WORD_CINEMA_6],[DOVE_PIC_BIRD_16,COMEDY_WORD_CINEMA_6],[OYSTER_PIC_SEAFOOD_17],[CYGNUS_WORD_PATTERN_188],[PURSUIT_WORD_QUEST_680],[LILY_WORD_FLOWERS_4],[SCORPIUS_WORD_PATTERN_188],[ORION_WORD_PATTERN_188,ITALIAN_WORD_LANGUAGE_70]]</t>
+  </si>
+  <si>
+    <t>[WORD_FLOWERS_4,WORD_CINEMA_6,WORD_QUEST_680,WORD_PATTERN_188,WORD_HOLIDAY_163,PIC_SEAFOOD_17,PIC_BIRD_16]</t>
   </si>
   <si>
     <t>SORT_GAME_LEVEL_REWARD_14</t>
@@ -1565,7 +1565,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1594,9 +1594,6 @@
           <etc:displayText val="2"/>
         </ext>
       </extLst>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2093,7 +2090,7 @@
       <c r="M3" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="N3" s="9" t="s">
+      <c r="N3" s="8" t="s">
         <v>37</v>
       </c>
       <c r="O3" s="4" t="s">
@@ -2234,19 +2231,19 @@
       <c r="N6" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="O6" s="10" t="s">
+      <c r="O6" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="P6" s="11" t="s">
+      <c r="P6" s="10" t="s">
         <v>60</v>
       </c>
       <c r="Q6" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="R6" s="13">
+      <c r="R6" s="12">
         <v>105</v>
       </c>
-      <c r="S6" s="13">
+      <c r="S6" s="12">
         <v>2</v>
       </c>
     </row>
@@ -2285,19 +2282,19 @@
       <c r="N7" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="O7" s="10" t="s">
+      <c r="O7" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="P7" s="12" t="s">
+      <c r="P7" s="11" t="s">
         <v>67</v>
       </c>
       <c r="Q7" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="R7" s="13">
+      <c r="R7" s="12">
         <v>125</v>
       </c>
-      <c r="S7" s="13">
+      <c r="S7" s="12">
         <v>2</v>
       </c>
     </row>
@@ -2336,19 +2333,19 @@
       <c r="N8" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="O8" s="10" t="s">
+      <c r="O8" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="P8" s="12" t="s">
+      <c r="P8" s="11" t="s">
         <v>74</v>
       </c>
       <c r="Q8" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="R8" s="13">
+      <c r="R8" s="12">
         <v>130</v>
       </c>
-      <c r="S8" s="13">
+      <c r="S8" s="12">
         <v>2</v>
       </c>
     </row>
@@ -2387,19 +2384,19 @@
       <c r="N9" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="O9" s="10" t="s">
+      <c r="O9" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="P9" s="12" t="s">
+      <c r="P9" s="11" t="s">
         <v>81</v>
       </c>
       <c r="Q9" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="R9" s="13">
+      <c r="R9" s="12">
         <v>130</v>
       </c>
-      <c r="S9" s="13">
+      <c r="S9" s="12">
         <v>2</v>
       </c>
     </row>
@@ -2438,19 +2435,19 @@
       <c r="N10" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="O10" s="10" t="s">
+      <c r="O10" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="P10" s="12" t="s">
+      <c r="P10" s="11" t="s">
         <v>88</v>
       </c>
       <c r="Q10" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="R10" s="13">
+      <c r="R10" s="12">
         <v>145</v>
       </c>
-      <c r="S10" s="13">
+      <c r="S10" s="12">
         <v>3</v>
       </c>
     </row>
@@ -2489,19 +2486,19 @@
       <c r="N11" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="O11" s="10" t="s">
+      <c r="O11" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="P11" s="12" t="s">
+      <c r="P11" s="11" t="s">
         <v>94</v>
       </c>
       <c r="Q11" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="R11" s="13">
+      <c r="R11" s="12">
         <v>135</v>
       </c>
-      <c r="S11" s="13">
+      <c r="S11" s="12">
         <v>3</v>
       </c>
     </row>
@@ -2540,19 +2537,19 @@
       <c r="N12" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="O12" s="10" t="s">
+      <c r="O12" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="P12" s="12" t="s">
+      <c r="P12" s="11" t="s">
         <v>101</v>
       </c>
       <c r="Q12" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="R12" s="13">
+      <c r="R12" s="12">
         <v>125</v>
       </c>
-      <c r="S12" s="13">
+      <c r="S12" s="12">
         <v>3</v>
       </c>
     </row>
@@ -2591,19 +2588,19 @@
       <c r="N13" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="O13" s="10" t="s">
+      <c r="O13" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="P13" s="12" t="s">
+      <c r="P13" s="11" t="s">
         <v>108</v>
       </c>
       <c r="Q13" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="R13" s="13">
+      <c r="R13" s="12">
         <v>140</v>
       </c>
-      <c r="S13" s="13">
+      <c r="S13" s="12">
         <v>3</v>
       </c>
     </row>
@@ -2644,19 +2641,19 @@
       <c r="N14" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="O14" s="10" t="s">
+      <c r="O14" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="P14" s="12" t="s">
+      <c r="P14" s="11" t="s">
         <v>116</v>
       </c>
       <c r="Q14" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="R14" s="13">
+      <c r="R14" s="12">
         <v>125</v>
       </c>
-      <c r="S14" s="13">
+      <c r="S14" s="12">
         <v>3</v>
       </c>
     </row>
@@ -2702,10 +2699,10 @@
         <v>123</v>
       </c>
       <c r="Q15" s="6"/>
-      <c r="R15" s="13">
+      <c r="R15" s="12">
         <v>135</v>
       </c>
-      <c r="S15" s="13">
+      <c r="S15" s="12">
         <v>3</v>
       </c>
     </row>
@@ -2751,10 +2748,10 @@
         <v>123</v>
       </c>
       <c r="Q16" s="6"/>
-      <c r="R16" s="13">
+      <c r="R16" s="12">
         <v>90</v>
       </c>
-      <c r="S16" s="13">
+      <c r="S16" s="12">
         <v>3</v>
       </c>
     </row>
@@ -2800,10 +2797,10 @@
         <v>123</v>
       </c>
       <c r="Q17" s="6"/>
-      <c r="R17" s="13">
+      <c r="R17" s="12">
         <v>100</v>
       </c>
-      <c r="S17" s="13">
+      <c r="S17" s="12">
         <v>3</v>
       </c>
     </row>
@@ -2851,10 +2848,10 @@
         <v>123</v>
       </c>
       <c r="Q18" s="6"/>
-      <c r="R18" s="13">
+      <c r="R18" s="12">
         <v>115</v>
       </c>
-      <c r="S18" s="13">
+      <c r="S18" s="12">
         <v>3</v>
       </c>
     </row>
@@ -2900,10 +2897,10 @@
         <v>123</v>
       </c>
       <c r="Q19" s="6"/>
-      <c r="R19" s="13">
+      <c r="R19" s="12">
         <v>130</v>
       </c>
-      <c r="S19" s="13">
+      <c r="S19" s="12">
         <v>3</v>
       </c>
     </row>
@@ -2949,10 +2946,10 @@
         <v>123</v>
       </c>
       <c r="Q20" s="6"/>
-      <c r="R20" s="13">
+      <c r="R20" s="12">
         <v>150</v>
       </c>
-      <c r="S20" s="13">
+      <c r="S20" s="12">
         <v>3</v>
       </c>
     </row>
@@ -2998,10 +2995,10 @@
         <v>123</v>
       </c>
       <c r="Q21" s="6"/>
-      <c r="R21" s="13">
+      <c r="R21" s="12">
         <v>130</v>
       </c>
-      <c r="S21" s="13">
+      <c r="S21" s="12">
         <v>3</v>
       </c>
     </row>
@@ -3049,10 +3046,10 @@
         <v>123</v>
       </c>
       <c r="Q22" s="6"/>
-      <c r="R22" s="13">
+      <c r="R22" s="12">
         <v>130</v>
       </c>
-      <c r="S22" s="13">
+      <c r="S22" s="12">
         <v>3</v>
       </c>
     </row>
@@ -3098,10 +3095,10 @@
         <v>123</v>
       </c>
       <c r="Q23" s="6"/>
-      <c r="R23" s="13">
+      <c r="R23" s="12">
         <v>140</v>
       </c>
-      <c r="S23" s="13">
+      <c r="S23" s="12">
         <v>3</v>
       </c>
     </row>
@@ -3147,10 +3144,10 @@
         <v>123</v>
       </c>
       <c r="Q24" s="6"/>
-      <c r="R24" s="13">
+      <c r="R24" s="12">
         <v>155</v>
       </c>
-      <c r="S24" s="13">
+      <c r="S24" s="12">
         <v>3</v>
       </c>
     </row>
@@ -3196,10 +3193,10 @@
         <v>123</v>
       </c>
       <c r="Q25" s="6"/>
-      <c r="R25" s="13">
+      <c r="R25" s="12">
         <v>165</v>
       </c>
-      <c r="S25" s="13">
+      <c r="S25" s="12">
         <v>3</v>
       </c>
     </row>
@@ -3247,10 +3244,10 @@
         <v>123</v>
       </c>
       <c r="Q26" s="6"/>
-      <c r="R26" s="13">
+      <c r="R26" s="12">
         <v>140</v>
       </c>
-      <c r="S26" s="13">
+      <c r="S26" s="12">
         <v>3</v>
       </c>
     </row>
@@ -3296,10 +3293,10 @@
         <v>123</v>
       </c>
       <c r="Q27" s="6"/>
-      <c r="R27" s="13">
+      <c r="R27" s="12">
         <v>145</v>
       </c>
-      <c r="S27" s="13">
+      <c r="S27" s="12">
         <v>4</v>
       </c>
     </row>
@@ -3345,10 +3342,10 @@
         <v>123</v>
       </c>
       <c r="Q28" s="6"/>
-      <c r="R28" s="13">
+      <c r="R28" s="12">
         <v>150</v>
       </c>
-      <c r="S28" s="13">
+      <c r="S28" s="12">
         <v>4</v>
       </c>
     </row>
@@ -3394,10 +3391,10 @@
         <v>123</v>
       </c>
       <c r="Q29" s="6"/>
-      <c r="R29" s="13">
+      <c r="R29" s="12">
         <v>155</v>
       </c>
-      <c r="S29" s="13">
+      <c r="S29" s="12">
         <v>4</v>
       </c>
     </row>
@@ -3443,10 +3440,10 @@
         <v>123</v>
       </c>
       <c r="Q30" s="6"/>
-      <c r="R30" s="13">
+      <c r="R30" s="12">
         <v>165</v>
       </c>
-      <c r="S30" s="13">
+      <c r="S30" s="12">
         <v>4</v>
       </c>
     </row>
@@ -3494,10 +3491,10 @@
         <v>123</v>
       </c>
       <c r="Q31" s="6"/>
-      <c r="R31" s="13">
+      <c r="R31" s="12">
         <v>150</v>
       </c>
-      <c r="S31" s="13">
+      <c r="S31" s="12">
         <v>4</v>
       </c>
     </row>
@@ -3543,10 +3540,10 @@
         <v>123</v>
       </c>
       <c r="Q32" s="6"/>
-      <c r="R32" s="13">
+      <c r="R32" s="12">
         <v>135</v>
       </c>
-      <c r="S32" s="13">
+      <c r="S32" s="12">
         <v>4</v>
       </c>
     </row>
@@ -3592,10 +3589,10 @@
         <v>123</v>
       </c>
       <c r="Q33" s="6"/>
-      <c r="R33" s="13">
+      <c r="R33" s="12">
         <v>145</v>
       </c>
-      <c r="S33" s="13">
+      <c r="S33" s="12">
         <v>4</v>
       </c>
     </row>
@@ -3641,10 +3638,10 @@
         <v>123</v>
       </c>
       <c r="Q34" s="6"/>
-      <c r="R34" s="13">
+      <c r="R34" s="12">
         <v>160</v>
       </c>
-      <c r="S34" s="13">
+      <c r="S34" s="12">
         <v>4</v>
       </c>
     </row>
@@ -3690,10 +3687,10 @@
         <v>123</v>
       </c>
       <c r="Q35" s="6"/>
-      <c r="R35" s="13">
+      <c r="R35" s="12">
         <v>165</v>
       </c>
-      <c r="S35" s="13">
+      <c r="S35" s="12">
         <v>4</v>
       </c>
     </row>
@@ -3741,10 +3738,10 @@
         <v>123</v>
       </c>
       <c r="Q36" s="6"/>
-      <c r="R36" s="13">
+      <c r="R36" s="12">
         <v>130</v>
       </c>
-      <c r="S36" s="13">
+      <c r="S36" s="12">
         <v>5</v>
       </c>
     </row>
@@ -3790,10 +3787,10 @@
         <v>123</v>
       </c>
       <c r="Q37" s="6"/>
-      <c r="R37" s="13">
+      <c r="R37" s="12">
         <v>135</v>
       </c>
-      <c r="S37" s="13">
+      <c r="S37" s="12">
         <v>5</v>
       </c>
     </row>
@@ -3839,10 +3836,10 @@
         <v>123</v>
       </c>
       <c r="Q38" s="6"/>
-      <c r="R38" s="13">
+      <c r="R38" s="12">
         <v>145</v>
       </c>
-      <c r="S38" s="13">
+      <c r="S38" s="12">
         <v>5</v>
       </c>
     </row>
@@ -3888,10 +3885,10 @@
         <v>123</v>
       </c>
       <c r="Q39" s="6"/>
-      <c r="R39" s="13">
+      <c r="R39" s="12">
         <v>135</v>
       </c>
-      <c r="S39" s="13">
+      <c r="S39" s="12">
         <v>5</v>
       </c>
     </row>
@@ -3921,10 +3918,10 @@
       <c r="K40" s="5">
         <v>3</v>
       </c>
-      <c r="L40" s="8" t="s">
+      <c r="L40" s="5" t="s">
         <v>247</v>
       </c>
-      <c r="M40" s="8" t="s">
+      <c r="M40" s="5" t="s">
         <v>248</v>
       </c>
       <c r="N40" s="5" t="s">
@@ -3937,10 +3934,10 @@
         <v>123</v>
       </c>
       <c r="Q40" s="6"/>
-      <c r="R40" s="13">
+      <c r="R40" s="12">
         <v>140</v>
       </c>
-      <c r="S40" s="13">
+      <c r="S40" s="12">
         <v>5</v>
       </c>
     </row>
@@ -3988,10 +3985,10 @@
         <v>123</v>
       </c>
       <c r="Q41" s="6"/>
-      <c r="R41" s="13">
+      <c r="R41" s="12">
         <v>110</v>
       </c>
-      <c r="S41" s="13">
+      <c r="S41" s="12">
         <v>5</v>
       </c>
     </row>
@@ -4037,10 +4034,10 @@
         <v>123</v>
       </c>
       <c r="Q42" s="6"/>
-      <c r="R42" s="13">
+      <c r="R42" s="12">
         <v>115</v>
       </c>
-      <c r="S42" s="13">
+      <c r="S42" s="12">
         <v>5</v>
       </c>
     </row>
@@ -4086,10 +4083,10 @@
         <v>123</v>
       </c>
       <c r="Q43" s="6"/>
-      <c r="R43" s="13">
+      <c r="R43" s="12">
         <v>125</v>
       </c>
-      <c r="S43" s="13">
+      <c r="S43" s="12">
         <v>5</v>
       </c>
     </row>
@@ -4135,10 +4132,10 @@
         <v>123</v>
       </c>
       <c r="Q44" s="6"/>
-      <c r="R44" s="13">
+      <c r="R44" s="12">
         <v>135</v>
       </c>
-      <c r="S44" s="13">
+      <c r="S44" s="12">
         <v>5</v>
       </c>
     </row>
@@ -4184,10 +4181,10 @@
         <v>123</v>
       </c>
       <c r="Q45" s="6"/>
-      <c r="R45" s="13">
+      <c r="R45" s="12">
         <v>140</v>
       </c>
-      <c r="S45" s="13">
+      <c r="S45" s="12">
         <v>5</v>
       </c>
     </row>

--- a/config/level_config.xlsx
+++ b/config/level_config.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29400" windowHeight="12880"/>
+    <workbookView windowHeight="23960"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -198,10 +198,10 @@
     <t>[7]</t>
   </si>
   <si>
-    <t>[[PROPANE_WORD_FUELS_190],[PANTS_PIC_GARMENTS_7],[HOWDY_WORD_HELLO_295],[BIKE_WORD_STREET_768],[WALRUS_WORD_ARCTIC_180],[HEY_WORD_HELLO_295],[GLOVES_PIC_GARMENTS_7],[SNOWY_OWL_WORD_ARCTIC_180],[COUPLE_WORD_HEART_344],[DIESEL_WORD_FUELS_190],[GASOLINE_WORD_FUELS_190],[SHIRT_PIC_GARMENTS_7],[CORNER_WORD_STREET_768],[HI_WORD_HELLO_295],[OKAY_WORD_OK_SIGN_301],[BUTTER_WORD_DAIRY_30],[DRESS_PIC_GARMENTS_7],[DRIVER_WORD_STREET_768],[YOGURT_WORD_DAIRY_30],[KEROSENE_WORD_FUELS_190],[COAL_WORD_FUELS_190],[COAT_PIC_GARMENTS_7],[POLAR_BEAR_WORD_ARCTIC_180],[ROMANCE_WORD_HEART_344],[CREAM_WORD_DAIRY_30]]</t>
-  </si>
-  <si>
-    <t>[PIC_GARMENTS_7]</t>
+    <t>[[PROPANE_WORD_FUELS_190],[ASIA_WORD_LANDMASS_10,PANTS_PIC_GARMENTS_7],[HOWDY_WORD_HELLO_295],[BIKE_WORD_STREET_768],[WALRUS_WORD_ARCTIC_180],[HEY_WORD_HELLO_295],[AFRICA_WORD_LANDMASS_10,GLOVES_PIC_GARMENTS_7],[SNOWY_OWL_WORD_ARCTIC_180],[COUPLE_WORD_HEART_344],[DIESEL_WORD_FUELS_190],[GASOLINE_WORD_FUELS_190],[SHIRT_PIC_GARMENTS_7],[CORNER_WORD_STREET_768],[HI_WORD_HELLO_295],[OKAY_WORD_OK_SIGN_301],[BUTTER_WORD_DAIRY_30],[DRESS_PIC_GARMENTS_7],[DRIVER_WORD_STREET_768],[YOGURT_WORD_DAIRY_30],[KEROSENE_WORD_FUELS_190],[COAL_WORD_FUELS_190],[EUROPE_WORD_LANDMASS_10],[POLAR_BEAR_WORD_ARCTIC_180],[ROMANCE_WORD_HEART_344],[CREAM_WORD_DAIRY_30]]</t>
+  </si>
+  <si>
+    <t>[WORD_LANDMASS_10,PIC_GARMENTS_7]</t>
   </si>
   <si>
     <t>SORT_GAME_LEVEL_REWARD_1</t>
@@ -219,10 +219,10 @@
     <t>[12]</t>
   </si>
   <si>
-    <t>[[ORANGE_PIC_FRUITS_9],[KINGDOM_WORD_MEDIEVAL_228],[OILY_WORD_SKIN_380],[NORMAL_WORD_SKIN_380],[PEACH_PIC_FRUITS_9],[BURGER_WORD_FOOD_3],[ASSIST_WORD_HELP_183],[NEW_YEAR_WORD_HOLIDAY_163],[POMEGRANATE_PIC_FRUITS_9],[LORD_WORD_MEDIEVAL_228],[PINEAPPLE_PIC_FRUITS_9],[DONATE_WORD_HELP_183],[APPLE_PIC_FRUITS_9],[SUPPORT_WORD_HELP_183],[FALSIFY_WORD_LIE_492],[THAT_WORD_POINTING_379],[BANANA_PIC_FRUITS_9],[EASTER_WORD_HOLIDAY_163],[HOT_DOG_WORD_FOOD_3],[WATERMELON_PIC_FRUITS_9],[KIWI_PIC_FRUITS_9],[PIZZA_WORD_FOOD_3],[THIS_WORD_POINTING_379],[TALE_WORD_LEGENDS_291],[FRIES_WORD_FOOD_3]]</t>
-  </si>
-  <si>
-    <t>[PIC_FRUITS_9]</t>
+    <t>[[THOSE_WORD_POINTING_379,FABLE_WORD_LEGENDS_291],[MYTH_WORD_LEGENDS_291,KINGDOM_WORD_MEDIEVAL_228],[OILY_WORD_SKIN_380],[NORMAL_WORD_SKIN_380],[SUPPORT_WORD_HELP_183],[BURGER_WORD_FOOD_3],[BANANA_PIC_FRUITS_9],[NEW_YEAR_WORD_HOLIDAY_163],[FLAG_DAY_WORD_HOLIDAY_163],[LORD_WORD_MEDIEVAL_228],[FORCE_WORD_STRENGTH_401],[DONATE_WORD_HELP_183],[ASSIST_WORD_HELP_183],[ORANGE_PIC_FRUITS_9],[FALSIFY_WORD_LIE_492],[THAT_WORD_POINTING_379],[APPLE_PIC_FRUITS_9],[EASTER_WORD_HOLIDAY_163],[HOT_DOG_WORD_FOOD_3],[LEAGUE_WORD_UNITE_126],[KIWI_PIC_FRUITS_9],[PIZZA_WORD_FOOD_3],[THIS_WORD_POINTING_379],[TALE_WORD_LEGENDS_291],[FRIES_WORD_FOOD_3]]</t>
+  </si>
+  <si>
+    <t>[WORD_HOLIDAY_163,WORD_HELP_183,PIC_FRUITS_9]</t>
   </si>
   <si>
     <t>SORT_GAME_LEVEL_REWARD_2</t>
@@ -240,10 +240,10 @@
     <t>[10]</t>
   </si>
   <si>
-    <t>[[BURGER_WORD_FOOD_3],[DRY_WORD_SKIN_380],[NOW_WORD_PRESENT_470],[NORMAL_WORD_SKIN_380],[ROOK_PIC_CHESS_1],[KNIGHT_PIC_CHESS_1],[CONSENT_WORD_OK_SIGN_301],[COUPLE_WORD_HEART_344],[CODE_WORD_SECRET_471],[PAWN_PIC_CHESS_1],[HOWDY_WORD_HELLO_295],[THIS_WORD_POINTING_379],[BISHOP_PIC_CHESS_1],[LUNCH_WORD_MEALS_444],[HEY_WORD_HELLO_295],[MIGHT_WORD_STRENGTH_401],[LETTER_WORD_MESSAGE_407],[WORD_WORD_SECRET_471],[FRIES_WORD_FOOD_3],[YES_WORD_OK_SIGN_301],[THOSE_WORD_POINTING_379],[HI_WORD_HELLO_295],[ROMANCE_WORD_HEART_344],[TEXT_WORD_MESSAGE_407],[OKAY_WORD_OK_SIGN_301]]</t>
-  </si>
-  <si>
-    <t>[WORD_HELLO_295,WORD_OK_SIGN_301,PIC_CHESS_1]</t>
+    <t>[[NOW_WORD_PRESENT_470,BURGER_WORD_FOOD_3],[DRY_WORD_SKIN_380],[PAWN_PIC_CHESS_1],[NORMAL_WORD_SKIN_380],[ROOK_PIC_CHESS_1],[KNIGHT_PIC_CHESS_1],[CONSENT_WORD_OK_SIGN_301],[COUPLE_WORD_HEART_344],[CODE_WORD_SECRET_471],[ROMANCE_WORD_HEART_344],[HOWDY_WORD_HELLO_295],[THIS_WORD_POINTING_379],[BISHOP_PIC_CHESS_1],[LUNCH_WORD_MEALS_444],[HEY_WORD_HELLO_295],[MIGHT_WORD_STRENGTH_401],[LETTER_WORD_MESSAGE_407],[WORD_WORD_SECRET_471],[FRIES_WORD_FOOD_3],[PASSION_WORD_HEART_344],[THOSE_WORD_POINTING_379],[HI_WORD_HELLO_295],[YES_WORD_OK_SIGN_301],[TEXT_WORD_MESSAGE_407],[OKAY_WORD_OK_SIGN_301]]</t>
+  </si>
+  <si>
+    <t>[WORD_HELLO_295,WORD_HEART_344,WORD_OK_SIGN_301,PIC_CHESS_1]</t>
   </si>
   <si>
     <t>SORT_GAME_LEVEL_REWARD_3</t>
@@ -261,10 +261,10 @@
     <t>[3,6]</t>
   </si>
   <si>
-    <t>[[OILY_WORD_SKIN_380],[EMAIL_WORD_MESSAGE_407],[DINNER_WORD_MEALS_444],[FRIES_WORD_FOOD_3],[ESSAY_WORD_ARTICLES_147],[POWER_WORD_STRENGTH_401],[FORCE_WORD_STRENGTH_401],[CAR_WORD_DRIVING_49],[CODE_WORD_SECRET_471],[CHAIR_PIC_FURNITURE_3],[BURGER_WORD_FOOD_3],[NORMAL_WORD_SKIN_380],[MIGHT_WORD_STRENGTH_401],[SOFA_PIC_FURNITURE_3],[PIZZA_WORD_FOOD_3],[TABLE_PIC_FURNITURE_3],[SIGN_WORD_DRIVING_49],[SUCCESS_WORD_WREATH_544],[THAT_WORD_POINTING_379],[DESK_PIC_FURNITURE_3],[DRY_WORD_SKIN_380],[THIS_WORD_POINTING_379],[OPINION_WORD_ARTICLES_147],[HOT_DOG_WORD_FOOD_3],[ROAD_WORD_DRIVING_49]]</t>
-  </si>
-  <si>
-    <t>[WORD_FOOD_3,WORD_SKIN_380,WORD_STRENGTH_401,PIC_FURNITURE_3]</t>
+    <t>[[OILY_WORD_SKIN_380],[POWER_WORD_STRENGTH_401,EMAIL_WORD_MESSAGE_407],[DINNER_WORD_MEALS_444],[FRIES_WORD_FOOD_3],[ESSAY_WORD_ARTICLES_147],[THOSE_WORD_POINTING_379],[FORCE_WORD_STRENGTH_401],[CAR_WORD_DRIVING_49],[CODE_WORD_SECRET_471],[CHAIR_PIC_FURNITURE_3],[BURGER_WORD_FOOD_3],[NORMAL_WORD_SKIN_380],[MIGHT_WORD_STRENGTH_401],[SOFA_PIC_FURNITURE_3],[PIZZA_WORD_FOOD_3],[THAT_WORD_POINTING_379],[SIGN_WORD_DRIVING_49],[SUCCESS_WORD_WREATH_544],[TABLE_PIC_FURNITURE_3],[DESK_PIC_FURNITURE_3],[DRY_WORD_SKIN_380],[THIS_WORD_POINTING_379],[OPINION_WORD_ARTICLES_147],[HOT_DOG_WORD_FOOD_3],[ROAD_WORD_DRIVING_49]]</t>
+  </si>
+  <si>
+    <t>[WORD_FOOD_3,WORD_POINTING_379,WORD_SKIN_380,PIC_FURNITURE_3,WORD_STRENGTH_401]</t>
   </si>
   <si>
     <t>SORT_GAME_LEVEL_REWARD_4</t>
@@ -300,10 +300,10 @@
     <t>SORT_GAME_LEVEL_6_BOARD_1</t>
   </si>
   <si>
-    <t>[[SOLID_WORD_PHASE_57,BEACH_WORD_COAST_969],[OPINION_WORD_ARTICLES_147],[ROAD_WORD_DRIVING_49,KNEE_WORD_LEGS_322],[SUCCESS_WORD_WREATH_544],[VIOLIN_PIC_PLAY_12],[ORGAN_PIC_PLAY_12],[ASIA_WORD_LANDMASS_10],[AFRICA_WORD_LANDMASS_10],[SIGN_WORD_DRIVING_49],[LIQUID_WORD_PHASE_57],[BOBBER_WORD_FISHING_20],[TRAFFIC_WORD_DRIVING_49],[SUMMER_WORD_SEASONS_18],[PIANO_PIC_PLAY_12],[VICTORY_WORD_WREATH_544],[UKULELE_PIC_PLAY_12],[FLUTE_PIC_PLAY_12],[ESSAY_WORD_ARTICLES_147],[EUROPE_WORD_LANDMASS_10],[TRIUMPH_WORD_WREATH_544,SPRING_WORD_SEASONS_18],[CAR_WORD_DRIVING_49,AUTUMN_WORD_SEASONS_18],[CELLO_PIC_PLAY_12],[GUITAR_PIC_PLAY_12],[REVIEW_WORD_ARTICLES_147,LEMON_WORD_CITRUS_173],[DRUM_PIC_PLAY_12]]</t>
-  </si>
-  <si>
-    <t>[WORD_LANDMASS_10,PIC_PLAY_12,WORD_ARTICLES_147,WORD_WREATH_544,WORD_DRIVING_49]</t>
+    <t>[[SURF_WORD_COAST_969,BEACH_WORD_COAST_969],[OPINION_WORD_ARTICLES_147],[ROAD_WORD_DRIVING_49,KNEE_WORD_LEGS_322],[SUCCESS_WORD_WREATH_544],[VIOLIN_PIC_PLAY_12],[ORGAN_PIC_PLAY_12],[ICEBERG_WORD_SNOW_77],[FLAKE_WORD_SNOW_77],[SIGN_WORD_DRIVING_49],[CLIFF_WORD_COAST_969],[BOBBER_WORD_FISHING_20],[TRAFFIC_WORD_DRIVING_49],[SUMMER_WORD_SEASONS_18],[PIANO_PIC_PLAY_12],[VICTORY_WORD_WREATH_544],[UKULELE_PIC_PLAY_12],[FLUTE_PIC_PLAY_12],[ESSAY_WORD_ARTICLES_147],[SLEET_WORD_SNOW_77],[TRIUMPH_WORD_WREATH_544,SPRING_WORD_SEASONS_18],[CAR_WORD_DRIVING_49,AUTUMN_WORD_SEASONS_18],[CELLO_PIC_PLAY_12],[GUITAR_PIC_PLAY_12],[REVIEW_WORD_ARTICLES_147,LEMON_WORD_CITRUS_173],[DRUM_PIC_PLAY_12]]</t>
+  </si>
+  <si>
+    <t>[WORD_WREATH_544,WORD_ARTICLES_147,WORD_DRIVING_49,PIC_PLAY_12,WORD_SNOW_77]</t>
   </si>
   <si>
     <t>SORT_GAME_LEVEL_REWARD_6</t>
@@ -387,10 +387,10 @@
     <t>[2,3]</t>
   </si>
   <si>
-    <t>[[COMFY_WORD_COZY_58,BRICK_WORD_STREET_768],[ACE_OF_HEARTS_PIC_DECK_4,DNA_WORD_GENETICS_1060],[ANT_WORD_INSECTS_25,CORNER_WORD_STREET_768],[JUDO_WORD_COMBAT_121,MYTH_WORD_LEGENDS_291],[AIR_BIKE_WORD_GYM_164,SAGA_WORD_LEGENDS_291],[YACHT_WORD_LUXURY_133],[DUMBBELL_WORD_GYM_164],[QUEEN_HEARTS_PIC_DECK_4],[SILAT_WORD_COMBAT_121],[LADYBUG_WORD_INSECTS_25,KUNG_FU_WORD_COMBAT_121],[KING_HEARTS_PIC_DECK_4,KARATE_WORD_COMBAT_121],[MOSQUITO_WORD_INSECTS_25],[SAVATE_WORD_COMBAT_121],[COVER_WORD_BOOK_9,DRAGONFLY_WORD_INSECTS_25],[JEWELRY_WORD_LUXURY_133,MOTH_WORD_INSECTS_25],[WARM_WORD_COZY_58,ACTOR_WORD_JOBS_42],[CAVIAR_WORD_LUXURY_133,MISLEAD_WORD_LIE_492],[PAPER_WORD_BOOK_9,SEXTANT_WORD_NAVIGATE_230],[WASP_WORD_INSECTS_25],[COAL_WORD_FUELS_190],[SNUG_WORD_COZY_58],[SUMO_WORD_COMBAT_121],[PAGE_WORD_BOOK_9],[BARBELL_WORD_GYM_164],[WATCH_WORD_LUXURY_133,GASOLINE_WORD_FUELS_190]]</t>
-  </si>
-  <si>
-    <t>[WORD_BOOK_9,PIC_DECK_4,WORD_GYM_164,WORD_COZY_58,WORD_COMBAT_121,WORD_LUXURY_133,WORD_INSECTS_25]</t>
+    <t>[[COMFY_WORD_COZY_58,BRICK_WORD_STREET_768],[ACE_OF_HEARTS_PIC_DECK_4,DNA_WORD_GENETICS_1060],[SKIING_WORD_SLIDING_339,CORNER_WORD_STREET_768],[JUDO_WORD_COMBAT_121,MYTH_WORD_LEGENDS_291],[AIR_BIKE_WORD_GYM_164,SAGA_WORD_LEGENDS_291],[YACHT_WORD_LUXURY_133],[DUMBBELL_WORD_GYM_164],[QUEEN_HEARTS_PIC_DECK_4],[SILAT_WORD_COMBAT_121],[LUGE_WORD_SLIDING_339,KUNG_FU_WORD_COMBAT_121],[KING_HEARTS_PIC_DECK_4,KARATE_WORD_COMBAT_121],[SLEDDING_WORD_SLIDING_339],[SAVATE_WORD_COMBAT_121],[SKATING_WORD_SLIDING_339,GAVEL_WORD_JUSTICE_310],[JEWELRY_WORD_LUXURY_133,SCALES_WORD_JUSTICE_310],[WARM_WORD_COZY_58,FALSIFY_WORD_LIE_492],[CAVIAR_WORD_LUXURY_133,MISLEAD_WORD_LIE_492],[COURT_WORD_JUSTICE_310,SEXTANT_WORD_NAVIGATE_230],[SKELETON_WORD_SLIDING_339],[COAL_WORD_FUELS_190],[SNUG_WORD_COZY_58],[SUMO_WORD_COMBAT_121],[LAW_WORD_JUSTICE_310],[BARBELL_WORD_GYM_164],[WATCH_WORD_LUXURY_133,GASOLINE_WORD_FUELS_190]]</t>
+  </si>
+  <si>
+    <t>[WORD_GYM_164,WORD_COZY_58,WORD_COMBAT_121,WORD_LUXURY_133,PIC_DECK_4,WORD_SLIDING_339,WORD_JUSTICE_310]</t>
   </si>
   <si>
     <t>SORT_GAME_LEVEL_REWARD_10</t>
@@ -450,10 +450,10 @@
     <t>[6,9]</t>
   </si>
   <si>
-    <t>[[INQUIRY_WORD_QUEST_680,DRAMA_WORD_CINEMA_6],[WESTERN_WORD_CINEMA_6,DOG_WORD_PETS_2],[FLAG_DAY_WORD_HOLIDAY_163,COUNTRY_WORD_DIVISION_242],[SWAN_PIC_BIRD_16,TICKET_WORD_CINEMA_6],[HUNT_WORD_QUEST_680,STATE_WORD_DIVISION_242],[EASTER_WORD_HOLIDAY_163],[LOBSTER_PIC_SEAFOOD_17,REGION_WORD_DIVISION_242],[ROSE_WORD_FLOWERS_4,CAT_WORD_PETS_2],[MUSSEL_PIC_SEAFOOD_17],[PEONY_WORD_FLOWERS_4,CHEESE_WORD_BURGER_8],[TULIP_WORD_FLOWERS_4],[NEW_YEAR_WORD_HOLIDAY_163,MULBERRY_WORD_BERRY_116],[PERSEUS_WORD_PATTERN_188,RUNWAY_WORD_AIRPORT_29],[EAGLE_PIC_BIRD_16],[DRACO_WORD_PATTERN_188],[HORROR_WORD_CINEMA_6],[SERPENS_WORD_PATTERN_188,ENGLISH_WORD_LANGUAGE_70],[POPCORN_WORD_CINEMA_6],[DOVE_PIC_BIRD_16,COMEDY_WORD_CINEMA_6],[OYSTER_PIC_SEAFOOD_17],[CYGNUS_WORD_PATTERN_188],[PURSUIT_WORD_QUEST_680],[LILY_WORD_FLOWERS_4],[SCORPIUS_WORD_PATTERN_188],[ORION_WORD_PATTERN_188,ITALIAN_WORD_LANGUAGE_70]]</t>
-  </si>
-  <si>
-    <t>[WORD_FLOWERS_4,WORD_CINEMA_6,WORD_QUEST_680,WORD_PATTERN_188,WORD_HOLIDAY_163,PIC_SEAFOOD_17,PIC_BIRD_16]</t>
+    <t>[[INQUIRY_WORD_QUEST_680,DRAMA_WORD_CINEMA_6],[WESTERN_WORD_CINEMA_6,SOHO_WORD_NEW_YORK_287],[HAVASU_WORD_WATER_152,COUNTRY_WORD_DIVISION_242],[SWAN_PIC_BIRD_16,TICKET_WORD_CINEMA_6],[HUNT_WORD_QUEST_680,STATE_WORD_DIVISION_242],[YOSEMITE_WORD_WATER_152],[LOBSTER_PIC_SEAFOOD_17,REGION_WORD_DIVISION_242],[ROSE_WORD_FLOWERS_4,BIBLE_WORD_PRIEST_1019],[MUSSEL_PIC_SEAFOOD_17],[PEONY_WORD_FLOWERS_4,CLERIC_WORD_PRIEST_1019],[TULIP_WORD_FLOWERS_4],[VICTORIA_WORD_WATER_152,MULBERRY_WORD_BERRY_116],[PERSEUS_WORD_PATTERN_188,RUNWAY_WORD_AIRPORT_29],[EAGLE_PIC_BIRD_16],[DRACO_WORD_PATTERN_188],[NIAGARA_WORD_WATER_152,HORROR_WORD_CINEMA_6],[SERPENS_WORD_PATTERN_188,ENGLISH_WORD_LANGUAGE_70],[POPCORN_WORD_CINEMA_6],[DOVE_PIC_BIRD_16,COMEDY_WORD_CINEMA_6],[OYSTER_PIC_SEAFOOD_17],[CYGNUS_WORD_PATTERN_188],[PURSUIT_WORD_QUEST_680],[LILY_WORD_FLOWERS_4],[SCORPIUS_WORD_PATTERN_188],[ORION_WORD_PATTERN_188,ITALIAN_WORD_LANGUAGE_70]]</t>
+  </si>
+  <si>
+    <t>[WORD_FLOWERS_4,WORD_CINEMA_6,WORD_QUEST_680,WORD_PATTERN_188,WORD_WATER_152,PIC_SEAFOOD_17,PIC_BIRD_16]</t>
   </si>
   <si>
     <t>SORT_GAME_LEVEL_REWARD_14</t>
@@ -1565,7 +1565,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1594,6 +1594,9 @@
           <etc:displayText val="2"/>
         </ext>
       </extLst>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2090,7 +2093,7 @@
       <c r="M3" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="N3" s="8" t="s">
+      <c r="N3" s="9" t="s">
         <v>37</v>
       </c>
       <c r="O3" s="4" t="s">
@@ -2231,19 +2234,19 @@
       <c r="N6" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="O6" s="9" t="s">
+      <c r="O6" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="P6" s="10" t="s">
+      <c r="P6" s="11" t="s">
         <v>60</v>
       </c>
       <c r="Q6" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="R6" s="12">
+      <c r="R6" s="13">
         <v>105</v>
       </c>
-      <c r="S6" s="12">
+      <c r="S6" s="13">
         <v>2</v>
       </c>
     </row>
@@ -2282,19 +2285,19 @@
       <c r="N7" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="O7" s="9" t="s">
+      <c r="O7" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="P7" s="11" t="s">
+      <c r="P7" s="12" t="s">
         <v>67</v>
       </c>
       <c r="Q7" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="R7" s="12">
+      <c r="R7" s="13">
         <v>125</v>
       </c>
-      <c r="S7" s="12">
+      <c r="S7" s="13">
         <v>2</v>
       </c>
     </row>
@@ -2333,19 +2336,19 @@
       <c r="N8" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="O8" s="9" t="s">
+      <c r="O8" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="P8" s="11" t="s">
+      <c r="P8" s="12" t="s">
         <v>74</v>
       </c>
       <c r="Q8" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="R8" s="12">
+      <c r="R8" s="13">
         <v>130</v>
       </c>
-      <c r="S8" s="12">
+      <c r="S8" s="13">
         <v>2</v>
       </c>
     </row>
@@ -2384,19 +2387,19 @@
       <c r="N9" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="O9" s="9" t="s">
+      <c r="O9" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="P9" s="11" t="s">
+      <c r="P9" s="12" t="s">
         <v>81</v>
       </c>
       <c r="Q9" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="R9" s="12">
+      <c r="R9" s="13">
         <v>130</v>
       </c>
-      <c r="S9" s="12">
+      <c r="S9" s="13">
         <v>2</v>
       </c>
     </row>
@@ -2435,19 +2438,19 @@
       <c r="N10" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="O10" s="9" t="s">
+      <c r="O10" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="P10" s="11" t="s">
+      <c r="P10" s="12" t="s">
         <v>88</v>
       </c>
       <c r="Q10" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="R10" s="12">
+      <c r="R10" s="13">
         <v>145</v>
       </c>
-      <c r="S10" s="12">
+      <c r="S10" s="13">
         <v>3</v>
       </c>
     </row>
@@ -2486,19 +2489,19 @@
       <c r="N11" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="O11" s="9" t="s">
+      <c r="O11" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="P11" s="11" t="s">
+      <c r="P11" s="12" t="s">
         <v>94</v>
       </c>
       <c r="Q11" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="R11" s="12">
+      <c r="R11" s="13">
         <v>135</v>
       </c>
-      <c r="S11" s="12">
+      <c r="S11" s="13">
         <v>3</v>
       </c>
     </row>
@@ -2537,19 +2540,19 @@
       <c r="N12" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="O12" s="9" t="s">
+      <c r="O12" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="P12" s="11" t="s">
+      <c r="P12" s="12" t="s">
         <v>101</v>
       </c>
       <c r="Q12" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="R12" s="12">
+      <c r="R12" s="13">
         <v>125</v>
       </c>
-      <c r="S12" s="12">
+      <c r="S12" s="13">
         <v>3</v>
       </c>
     </row>
@@ -2588,19 +2591,19 @@
       <c r="N13" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="O13" s="9" t="s">
+      <c r="O13" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="P13" s="11" t="s">
+      <c r="P13" s="12" t="s">
         <v>108</v>
       </c>
       <c r="Q13" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="R13" s="12">
+      <c r="R13" s="13">
         <v>140</v>
       </c>
-      <c r="S13" s="12">
+      <c r="S13" s="13">
         <v>3</v>
       </c>
     </row>
@@ -2641,19 +2644,19 @@
       <c r="N14" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="O14" s="9" t="s">
+      <c r="O14" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="P14" s="11" t="s">
+      <c r="P14" s="12" t="s">
         <v>116</v>
       </c>
       <c r="Q14" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="R14" s="12">
+      <c r="R14" s="13">
         <v>125</v>
       </c>
-      <c r="S14" s="12">
+      <c r="S14" s="13">
         <v>3</v>
       </c>
     </row>
@@ -2699,10 +2702,10 @@
         <v>123</v>
       </c>
       <c r="Q15" s="6"/>
-      <c r="R15" s="12">
+      <c r="R15" s="13">
         <v>135</v>
       </c>
-      <c r="S15" s="12">
+      <c r="S15" s="13">
         <v>3</v>
       </c>
     </row>
@@ -2748,10 +2751,10 @@
         <v>123</v>
       </c>
       <c r="Q16" s="6"/>
-      <c r="R16" s="12">
+      <c r="R16" s="13">
         <v>90</v>
       </c>
-      <c r="S16" s="12">
+      <c r="S16" s="13">
         <v>3</v>
       </c>
     </row>
@@ -2797,10 +2800,10 @@
         <v>123</v>
       </c>
       <c r="Q17" s="6"/>
-      <c r="R17" s="12">
+      <c r="R17" s="13">
         <v>100</v>
       </c>
-      <c r="S17" s="12">
+      <c r="S17" s="13">
         <v>3</v>
       </c>
     </row>
@@ -2848,10 +2851,10 @@
         <v>123</v>
       </c>
       <c r="Q18" s="6"/>
-      <c r="R18" s="12">
+      <c r="R18" s="13">
         <v>115</v>
       </c>
-      <c r="S18" s="12">
+      <c r="S18" s="13">
         <v>3</v>
       </c>
     </row>
@@ -2897,10 +2900,10 @@
         <v>123</v>
       </c>
       <c r="Q19" s="6"/>
-      <c r="R19" s="12">
+      <c r="R19" s="13">
         <v>130</v>
       </c>
-      <c r="S19" s="12">
+      <c r="S19" s="13">
         <v>3</v>
       </c>
     </row>
@@ -2946,10 +2949,10 @@
         <v>123</v>
       </c>
       <c r="Q20" s="6"/>
-      <c r="R20" s="12">
+      <c r="R20" s="13">
         <v>150</v>
       </c>
-      <c r="S20" s="12">
+      <c r="S20" s="13">
         <v>3</v>
       </c>
     </row>
@@ -2995,10 +2998,10 @@
         <v>123</v>
       </c>
       <c r="Q21" s="6"/>
-      <c r="R21" s="12">
+      <c r="R21" s="13">
         <v>130</v>
       </c>
-      <c r="S21" s="12">
+      <c r="S21" s="13">
         <v>3</v>
       </c>
     </row>
@@ -3046,10 +3049,10 @@
         <v>123</v>
       </c>
       <c r="Q22" s="6"/>
-      <c r="R22" s="12">
+      <c r="R22" s="13">
         <v>130</v>
       </c>
-      <c r="S22" s="12">
+      <c r="S22" s="13">
         <v>3</v>
       </c>
     </row>
@@ -3095,10 +3098,10 @@
         <v>123</v>
       </c>
       <c r="Q23" s="6"/>
-      <c r="R23" s="12">
+      <c r="R23" s="13">
         <v>140</v>
       </c>
-      <c r="S23" s="12">
+      <c r="S23" s="13">
         <v>3</v>
       </c>
     </row>
@@ -3144,10 +3147,10 @@
         <v>123</v>
       </c>
       <c r="Q24" s="6"/>
-      <c r="R24" s="12">
+      <c r="R24" s="13">
         <v>155</v>
       </c>
-      <c r="S24" s="12">
+      <c r="S24" s="13">
         <v>3</v>
       </c>
     </row>
@@ -3193,10 +3196,10 @@
         <v>123</v>
       </c>
       <c r="Q25" s="6"/>
-      <c r="R25" s="12">
+      <c r="R25" s="13">
         <v>165</v>
       </c>
-      <c r="S25" s="12">
+      <c r="S25" s="13">
         <v>3</v>
       </c>
     </row>
@@ -3244,10 +3247,10 @@
         <v>123</v>
       </c>
       <c r="Q26" s="6"/>
-      <c r="R26" s="12">
+      <c r="R26" s="13">
         <v>140</v>
       </c>
-      <c r="S26" s="12">
+      <c r="S26" s="13">
         <v>3</v>
       </c>
     </row>
@@ -3293,10 +3296,10 @@
         <v>123</v>
       </c>
       <c r="Q27" s="6"/>
-      <c r="R27" s="12">
+      <c r="R27" s="13">
         <v>145</v>
       </c>
-      <c r="S27" s="12">
+      <c r="S27" s="13">
         <v>4</v>
       </c>
     </row>
@@ -3342,10 +3345,10 @@
         <v>123</v>
       </c>
       <c r="Q28" s="6"/>
-      <c r="R28" s="12">
+      <c r="R28" s="13">
         <v>150</v>
       </c>
-      <c r="S28" s="12">
+      <c r="S28" s="13">
         <v>4</v>
       </c>
     </row>
@@ -3391,10 +3394,10 @@
         <v>123</v>
       </c>
       <c r="Q29" s="6"/>
-      <c r="R29" s="12">
+      <c r="R29" s="13">
         <v>155</v>
       </c>
-      <c r="S29" s="12">
+      <c r="S29" s="13">
         <v>4</v>
       </c>
     </row>
@@ -3440,10 +3443,10 @@
         <v>123</v>
       </c>
       <c r="Q30" s="6"/>
-      <c r="R30" s="12">
+      <c r="R30" s="13">
         <v>165</v>
       </c>
-      <c r="S30" s="12">
+      <c r="S30" s="13">
         <v>4</v>
       </c>
     </row>
@@ -3491,10 +3494,10 @@
         <v>123</v>
       </c>
       <c r="Q31" s="6"/>
-      <c r="R31" s="12">
+      <c r="R31" s="13">
         <v>150</v>
       </c>
-      <c r="S31" s="12">
+      <c r="S31" s="13">
         <v>4</v>
       </c>
     </row>
@@ -3540,10 +3543,10 @@
         <v>123</v>
       </c>
       <c r="Q32" s="6"/>
-      <c r="R32" s="12">
+      <c r="R32" s="13">
         <v>135</v>
       </c>
-      <c r="S32" s="12">
+      <c r="S32" s="13">
         <v>4</v>
       </c>
     </row>
@@ -3589,10 +3592,10 @@
         <v>123</v>
       </c>
       <c r="Q33" s="6"/>
-      <c r="R33" s="12">
+      <c r="R33" s="13">
         <v>145</v>
       </c>
-      <c r="S33" s="12">
+      <c r="S33" s="13">
         <v>4</v>
       </c>
     </row>
@@ -3638,10 +3641,10 @@
         <v>123</v>
       </c>
       <c r="Q34" s="6"/>
-      <c r="R34" s="12">
+      <c r="R34" s="13">
         <v>160</v>
       </c>
-      <c r="S34" s="12">
+      <c r="S34" s="13">
         <v>4</v>
       </c>
     </row>
@@ -3687,10 +3690,10 @@
         <v>123</v>
       </c>
       <c r="Q35" s="6"/>
-      <c r="R35" s="12">
+      <c r="R35" s="13">
         <v>165</v>
       </c>
-      <c r="S35" s="12">
+      <c r="S35" s="13">
         <v>4</v>
       </c>
     </row>
@@ -3738,10 +3741,10 @@
         <v>123</v>
       </c>
       <c r="Q36" s="6"/>
-      <c r="R36" s="12">
+      <c r="R36" s="13">
         <v>130</v>
       </c>
-      <c r="S36" s="12">
+      <c r="S36" s="13">
         <v>5</v>
       </c>
     </row>
@@ -3787,10 +3790,10 @@
         <v>123</v>
       </c>
       <c r="Q37" s="6"/>
-      <c r="R37" s="12">
+      <c r="R37" s="13">
         <v>135</v>
       </c>
-      <c r="S37" s="12">
+      <c r="S37" s="13">
         <v>5</v>
       </c>
     </row>
@@ -3836,10 +3839,10 @@
         <v>123</v>
       </c>
       <c r="Q38" s="6"/>
-      <c r="R38" s="12">
+      <c r="R38" s="13">
         <v>145</v>
       </c>
-      <c r="S38" s="12">
+      <c r="S38" s="13">
         <v>5</v>
       </c>
     </row>
@@ -3885,10 +3888,10 @@
         <v>123</v>
       </c>
       <c r="Q39" s="6"/>
-      <c r="R39" s="12">
+      <c r="R39" s="13">
         <v>135</v>
       </c>
-      <c r="S39" s="12">
+      <c r="S39" s="13">
         <v>5</v>
       </c>
     </row>
@@ -3918,10 +3921,10 @@
       <c r="K40" s="5">
         <v>3</v>
       </c>
-      <c r="L40" s="5" t="s">
+      <c r="L40" s="8" t="s">
         <v>247</v>
       </c>
-      <c r="M40" s="5" t="s">
+      <c r="M40" s="8" t="s">
         <v>248</v>
       </c>
       <c r="N40" s="5" t="s">
@@ -3934,10 +3937,10 @@
         <v>123</v>
       </c>
       <c r="Q40" s="6"/>
-      <c r="R40" s="12">
+      <c r="R40" s="13">
         <v>140</v>
       </c>
-      <c r="S40" s="12">
+      <c r="S40" s="13">
         <v>5</v>
       </c>
     </row>
@@ -3985,10 +3988,10 @@
         <v>123</v>
       </c>
       <c r="Q41" s="6"/>
-      <c r="R41" s="12">
+      <c r="R41" s="13">
         <v>110</v>
       </c>
-      <c r="S41" s="12">
+      <c r="S41" s="13">
         <v>5</v>
       </c>
     </row>
@@ -4034,10 +4037,10 @@
         <v>123</v>
       </c>
       <c r="Q42" s="6"/>
-      <c r="R42" s="12">
+      <c r="R42" s="13">
         <v>115</v>
       </c>
-      <c r="S42" s="12">
+      <c r="S42" s="13">
         <v>5</v>
       </c>
     </row>
@@ -4083,10 +4086,10 @@
         <v>123</v>
       </c>
       <c r="Q43" s="6"/>
-      <c r="R43" s="12">
+      <c r="R43" s="13">
         <v>125</v>
       </c>
-      <c r="S43" s="12">
+      <c r="S43" s="13">
         <v>5</v>
       </c>
     </row>
@@ -4132,10 +4135,10 @@
         <v>123</v>
       </c>
       <c r="Q44" s="6"/>
-      <c r="R44" s="12">
+      <c r="R44" s="13">
         <v>135</v>
       </c>
-      <c r="S44" s="12">
+      <c r="S44" s="13">
         <v>5</v>
       </c>
     </row>
@@ -4181,10 +4184,10 @@
         <v>123</v>
       </c>
       <c r="Q45" s="6"/>
-      <c r="R45" s="12">
+      <c r="R45" s="13">
         <v>140</v>
       </c>
-      <c r="S45" s="12">
+      <c r="S45" s="13">
         <v>5</v>
       </c>
     </row>

--- a/config/level_config.xlsx
+++ b/config/level_config.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29400" windowHeight="12880"/>
+    <workbookView windowWidth="29400" windowHeight="12740"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -240,10 +240,10 @@
     <t>[10]</t>
   </si>
   <si>
-    <t>[[BURGER_WORD_FOOD_3],[DRY_WORD_SKIN_380],[NOW_WORD_PRESENT_470],[NORMAL_WORD_SKIN_380],[ROOK_PIC_CHESS_1],[KNIGHT_PIC_CHESS_1],[CONSENT_WORD_OK_SIGN_301],[COUPLE_WORD_HEART_344],[CODE_WORD_SECRET_471],[PAWN_PIC_CHESS_1],[HOWDY_WORD_HELLO_295],[THIS_WORD_POINTING_379],[BISHOP_PIC_CHESS_1],[LUNCH_WORD_MEALS_444],[HEY_WORD_HELLO_295],[MIGHT_WORD_STRENGTH_401],[LETTER_WORD_MESSAGE_407],[WORD_WORD_SECRET_471],[FRIES_WORD_FOOD_3],[YES_WORD_OK_SIGN_301],[THOSE_WORD_POINTING_379],[HI_WORD_HELLO_295],[ROMANCE_WORD_HEART_344],[TEXT_WORD_MESSAGE_407],[OKAY_WORD_OK_SIGN_301]]</t>
-  </si>
-  <si>
-    <t>[WORD_HELLO_295,WORD_OK_SIGN_301,PIC_CHESS_1]</t>
+    <t>[[BURGER_WORD_FOOD_3],[DRY_WORD_SKIN_380],[NOW_WORD_PRESENT_470],[NORMAL_WORD_SKIN_380],[ROOK_PIC_CHESS_1],[YES_WORD_OK_SIGN_301],[CONSENT_WORD_OK_SIGN_301],[COUPLE_WORD_HEART_344],[CODE_WORD_SECRET_471],[PAWN_PIC_CHESS_1],[OKAY_WORD_OK_SIGN_301],[THIS_WORD_POINTING_379],[BISHOP_PIC_CHESS_1],[LUNCH_WORD_MEALS_444],[HEY_WORD_HELLO_295],[MIGHT_WORD_STRENGTH_401],[LETTER_WORD_MESSAGE_407],[WORD_WORD_SECRET_471],[FRIES_WORD_FOOD_3],[KNIGHT_PIC_CHESS_1],[THOSE_WORD_POINTING_379],[HI_WORD_HELLO_295],[ROMANCE_WORD_HEART_344],[TEXT_WORD_MESSAGE_407],[HOWDY_WORD_HELLO_295]]</t>
+  </si>
+  <si>
+    <t>[PIC_CHESS_1,WORD_HELLO_295]</t>
   </si>
   <si>
     <t>SORT_GAME_LEVEL_REWARD_3</t>
@@ -258,13 +258,13 @@
     <t>SORT_GAME_LEVEL_4_BOARD_1</t>
   </si>
   <si>
-    <t>[3,6]</t>
-  </si>
-  <si>
-    <t>[[OILY_WORD_SKIN_380],[EMAIL_WORD_MESSAGE_407],[DINNER_WORD_MEALS_444],[FRIES_WORD_FOOD_3],[ESSAY_WORD_ARTICLES_147],[POWER_WORD_STRENGTH_401],[FORCE_WORD_STRENGTH_401],[CAR_WORD_DRIVING_49],[CODE_WORD_SECRET_471],[CHAIR_PIC_FURNITURE_3],[BURGER_WORD_FOOD_3],[NORMAL_WORD_SKIN_380],[MIGHT_WORD_STRENGTH_401],[SOFA_PIC_FURNITURE_3],[PIZZA_WORD_FOOD_3],[TABLE_PIC_FURNITURE_3],[SIGN_WORD_DRIVING_49],[SUCCESS_WORD_WREATH_544],[THAT_WORD_POINTING_379],[DESK_PIC_FURNITURE_3],[DRY_WORD_SKIN_380],[THIS_WORD_POINTING_379],[OPINION_WORD_ARTICLES_147],[HOT_DOG_WORD_FOOD_3],[ROAD_WORD_DRIVING_49]]</t>
-  </si>
-  <si>
-    <t>[WORD_FOOD_3,WORD_SKIN_380,WORD_STRENGTH_401,PIC_FURNITURE_3]</t>
+    <t>[3]</t>
+  </si>
+  <si>
+    <t>[[OILY_WORD_SKIN_380],[EMAIL_WORD_MESSAGE_407],[DINNER_WORD_MEALS_444],[FRIES_WORD_FOOD_3],[ESSAY_WORD_ARTICLES_147],[POWER_WORD_STRENGTH_401],[FORCE_WORD_STRENGTH_401],[CAR_WORD_DRIVING_49],[CODE_WORD_SECRET_471],[CHAIR_PIC_FURNITURE_3],[BURGER_WORD_FOOD_3],[TABLE_PIC_FURNITURE_3],[HOT_DOG_WORD_FOOD_3],[SOFA_PIC_FURNITURE_3],[PIZZA_WORD_FOOD_3],[NORMAL_WORD_SKIN_380],[SIGN_WORD_DRIVING_49],[SUCCESS_WORD_WREATH_544],[THAT_WORD_POINTING_379],[DESK_PIC_FURNITURE_3],[DRY_WORD_SKIN_380],[THIS_WORD_POINTING_379],[OPINION_WORD_ARTICLES_147],[MIGHT_WORD_STRENGTH_401],[ROAD_WORD_DRIVING_49]]</t>
+  </si>
+  <si>
+    <t>[WORD_FOOD_3,PIC_FURNITURE_3]</t>
   </si>
   <si>
     <t>SORT_GAME_LEVEL_REWARD_4</t>
@@ -282,10 +282,10 @@
     <t>[5,8]</t>
   </si>
   <si>
-    <t>[[SPRING_WORD_SEASONS_18,TRIUMPH_WORD_WREATH_544],[BOXING_PIC_SPORTS_2,LEMON_WORD_CITRUS_173],[CODE_WORD_SECRET_471],[TENNIS_PIC_SPORTS_2],[LETTER_WORD_MESSAGE_407],[RUGBY_PIC_SPORTS_2],[NOW_WORD_PRESENT_470],[CURLING_PIC_SPORTS_2],[TEXT_WORD_MESSAGE_407],[ROAD_WORD_DRIVING_49],[TODAY_WORD_PRESENT_470],[LUNCH_WORD_MEALS_444],[AGENT_WORD_SECRET_471],[BAIT_WORD_FISHING_20],[CURRENT_WORD_PRESENT_470],[WORD_WORD_SECRET_471],[SUCCESS_WORD_WREATH_544],[EMAIL_WORD_MESSAGE_407],[GOLF_PIC_SPORTS_2],[SOCCER_PIC_SPORTS_2],[FAX_WORD_MESSAGE_407],[HOCKEY_PIC_SPORTS_2],[TABLE_TENNIS_PIC_SPORTS_2],[SUPPER_WORD_MEALS_444],[DINNER_WORD_MEALS_444]]</t>
-  </si>
-  <si>
-    <t>[PIC_SPORTS_2,WORD_PRESENT_470,WORD_MEALS_444,WORD_MESSAGE_407,WORD_SECRET_471]</t>
+    <t>[[SPRING_WORD_SEASONS_18,TRIUMPH_WORD_WREATH_544],[LEMON_WORD_CITRUS_173],[BOXING_PIC_SPORTS_2],[TENNIS_PIC_SPORTS_2],[LETTER_WORD_MESSAGE_407],[CODE_WORD_SECRET_471],[NOW_WORD_PRESENT_470],[CURLING_PIC_SPORTS_2],[TEXT_WORD_MESSAGE_407],[ROAD_WORD_DRIVING_49],[TODAY_WORD_PRESENT_470],[LUNCH_WORD_MEALS_444],[RUGBY_PIC_SPORTS_2],[BAIT_WORD_FISHING_20],[CURRENT_WORD_PRESENT_470],[WORD_WORD_SECRET_471],[SUCCESS_WORD_WREATH_544],[TABLE_TENNIS_PIC_SPORTS_2],[GOLF_PIC_SPORTS_2],[SOCCER_PIC_SPORTS_2],[FAX_WORD_MESSAGE_407],[HOCKEY_PIC_SPORTS_2],[EMAIL_WORD_MESSAGE_407],[SUPPER_WORD_MEALS_444],[DINNER_WORD_MEALS_444]]</t>
+  </si>
+  <si>
+    <t>[PIC_SPORTS_2,WORD_MEALS_444,WORD_MESSAGE_407]</t>
   </si>
   <si>
     <t>SORT_GAME_LEVEL_REWARD_5</t>
@@ -300,10 +300,10 @@
     <t>SORT_GAME_LEVEL_6_BOARD_1</t>
   </si>
   <si>
-    <t>[[SOLID_WORD_PHASE_57,BEACH_WORD_COAST_969],[OPINION_WORD_ARTICLES_147],[ROAD_WORD_DRIVING_49,KNEE_WORD_LEGS_322],[SUCCESS_WORD_WREATH_544],[VIOLIN_PIC_PLAY_12],[ORGAN_PIC_PLAY_12],[ASIA_WORD_LANDMASS_10],[AFRICA_WORD_LANDMASS_10],[SIGN_WORD_DRIVING_49],[LIQUID_WORD_PHASE_57],[BOBBER_WORD_FISHING_20],[TRAFFIC_WORD_DRIVING_49],[SUMMER_WORD_SEASONS_18],[PIANO_PIC_PLAY_12],[VICTORY_WORD_WREATH_544],[UKULELE_PIC_PLAY_12],[FLUTE_PIC_PLAY_12],[ESSAY_WORD_ARTICLES_147],[EUROPE_WORD_LANDMASS_10],[TRIUMPH_WORD_WREATH_544,SPRING_WORD_SEASONS_18],[CAR_WORD_DRIVING_49,AUTUMN_WORD_SEASONS_18],[CELLO_PIC_PLAY_12],[GUITAR_PIC_PLAY_12],[REVIEW_WORD_ARTICLES_147,LEMON_WORD_CITRUS_173],[DRUM_PIC_PLAY_12]]</t>
-  </si>
-  <si>
-    <t>[WORD_LANDMASS_10,PIC_PLAY_12,WORD_ARTICLES_147,WORD_WREATH_544,WORD_DRIVING_49]</t>
+    <t>[[SOLID_WORD_PHASE_57,BEACH_WORD_COAST_969],[VIOLIN_PIC_PLAY_12],[ROAD_WORD_DRIVING_49,KNEE_WORD_LEGS_322],[SUCCESS_WORD_WREATH_544],[OPINION_WORD_ARTICLES_147],[ORGAN_PIC_PLAY_12],[ASIA_WORD_LANDMASS_10],[AFRICA_WORD_LANDMASS_10],[SIGN_WORD_DRIVING_49],[LIQUID_WORD_PHASE_57],[BOBBER_WORD_FISHING_20],[TRAFFIC_WORD_DRIVING_49],[SUMMER_WORD_SEASONS_18],[PIANO_PIC_PLAY_12],[VICTORY_WORD_WREATH_544],[UKULELE_PIC_PLAY_12],[FLUTE_PIC_PLAY_12],[ESSAY_WORD_ARTICLES_147],[EUROPE_WORD_LANDMASS_10],[TRIUMPH_WORD_WREATH_544,SPRING_WORD_SEASONS_18],[CAR_WORD_DRIVING_49,AUTUMN_WORD_SEASONS_18],[CELLO_PIC_PLAY_12],[GUITAR_PIC_PLAY_12],[REVIEW_WORD_ARTICLES_147,LEMON_WORD_CITRUS_173],[DRUM_PIC_PLAY_12]]</t>
+  </si>
+  <si>
+    <t>[WORD_WREATH_544,WORD_DRIVING_49,PIC_PLAY_12,WORD_LANDMASS_10]</t>
   </si>
   <si>
     <t>SORT_GAME_LEVEL_REWARD_6</t>
@@ -387,10 +387,10 @@
     <t>[2,3]</t>
   </si>
   <si>
-    <t>[[COMFY_WORD_COZY_58,BRICK_WORD_STREET_768],[ACE_OF_HEARTS_PIC_DECK_4,DNA_WORD_GENETICS_1060],[ANT_WORD_INSECTS_25,CORNER_WORD_STREET_768],[JUDO_WORD_COMBAT_121,MYTH_WORD_LEGENDS_291],[AIR_BIKE_WORD_GYM_164,SAGA_WORD_LEGENDS_291],[YACHT_WORD_LUXURY_133],[DUMBBELL_WORD_GYM_164],[QUEEN_HEARTS_PIC_DECK_4],[SILAT_WORD_COMBAT_121],[LADYBUG_WORD_INSECTS_25,KUNG_FU_WORD_COMBAT_121],[KING_HEARTS_PIC_DECK_4,KARATE_WORD_COMBAT_121],[MOSQUITO_WORD_INSECTS_25],[SAVATE_WORD_COMBAT_121],[COVER_WORD_BOOK_9,DRAGONFLY_WORD_INSECTS_25],[JEWELRY_WORD_LUXURY_133,MOTH_WORD_INSECTS_25],[WARM_WORD_COZY_58,ACTOR_WORD_JOBS_42],[CAVIAR_WORD_LUXURY_133,MISLEAD_WORD_LIE_492],[PAPER_WORD_BOOK_9,SEXTANT_WORD_NAVIGATE_230],[WASP_WORD_INSECTS_25],[COAL_WORD_FUELS_190],[SNUG_WORD_COZY_58],[SUMO_WORD_COMBAT_121],[PAGE_WORD_BOOK_9],[BARBELL_WORD_GYM_164],[WATCH_WORD_LUXURY_133,GASOLINE_WORD_FUELS_190]]</t>
-  </si>
-  <si>
-    <t>[WORD_BOOK_9,PIC_DECK_4,WORD_GYM_164,WORD_COZY_58,WORD_COMBAT_121,WORD_LUXURY_133,WORD_INSECTS_25]</t>
+    <t>[[COMFY_WORD_COZY_58],[ACE_OF_HEARTS_PIC_DECK_4],[CORNER_WORD_STREET_768],[MYTH_WORD_LEGENDS_291],[AIR_BIKE_WORD_GYM_164,KUNG_FU_WORD_COMBAT_121],[CONSENT_WORD_OK_SIGN_301,YACHT_WORD_LUXURY_133],[YES_WORD_OK_SIGN_301,DUMBBELL_WORD_GYM_164],[QUEEN_HEARTS_PIC_DECK_4],[WATCH_WORD_LUXURY_133],[ASSIST_WORD_HELP_183,BARBELL_WORD_GYM_164],[KING_HEARTS_PIC_DECK_4],[OKAY_WORD_OK_SIGN_301,CAVIAR_WORD_LUXURY_133],[PAPER_WORD_BOOK_9],[COVER_WORD_BOOK_9],[SUPPORT_WORD_HELP_183,JEWELRY_WORD_LUXURY_133],[WARM_WORD_COZY_58],[MISLEAD_WORD_LIE_492],[BRICK_WORD_STREET_768],[ACTOR_WORD_JOBS_42],[COAL_WORD_FUELS_190],[ANT_WORD_INSECTS_25],[DNA_WORD_GENETICS_1060],[PAGE_WORD_BOOK_9],[DONATE_WORD_HELP_183,MOTH_WORD_INSECTS_25],[GASOLINE_WORD_FUELS_190]]</t>
+  </si>
+  <si>
+    <t>[WORD_OK_SIGN_301,WORD_HELP_183,PIC_DECK_4,WORD_LUXURY_133,WORD_BOOK_9,WORD_GYM_164]</t>
   </si>
   <si>
     <t>SORT_GAME_LEVEL_REWARD_10</t>
@@ -2220,7 +2220,7 @@
         <v>55</v>
       </c>
       <c r="K6" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L6" s="5" t="s">
         <v>56</v>
@@ -2271,7 +2271,7 @@
         <v>62</v>
       </c>
       <c r="K7" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L7" s="5" t="s">
         <v>63</v>
@@ -2367,7 +2367,7 @@
       </c>
       <c r="H9" s="6"/>
       <c r="I9" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J9" s="5" t="s">
         <v>76</v>
